--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -21238,8 +21238,8 @@
     <col width="39" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -21318,14 +21318,12 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0.75</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>2;4;5;6;8;9;10;12;13;14</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -21363,14 +21361,12 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0.8722</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>3;4;6;7;9;10;12;14;15;17</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -21413,14 +21409,12 @@
           <t>repair_bay;radar_station</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F4" t="n">
+        <v>1.0414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>3;5;7;9;11;12;14;16;18;20</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -21463,14 +21457,12 @@
           <t>repair_bay;radar_station</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F5" t="n">
+        <v>1.1492</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>3;6;8;10;12;14;16;18;20;22</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -21513,14 +21505,12 @@
           <t>repair_bay;radar_station;ammo_depot</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1.3176</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>4;6;9;11;13;16;18;21;23;25</t>
         </is>
       </c>
       <c r="H6" t="n">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -5880,7 +5880,7 @@
       </c>
       <c r="EV22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[228]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[227]</t>
         </is>
       </c>
       <c r="EW22" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="EV31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[199]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[198]</t>
         </is>
       </c>
       <c r="EW31" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="EV55" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[201]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[200]</t>
         </is>
       </c>
       <c r="EW55" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="EV63" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[200]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[199]</t>
         </is>
       </c>
       <c r="EW63" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="EV76" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[217]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[216]</t>
         </is>
       </c>
       <c r="EW76" t="inlineStr">
@@ -27074,13 +27074,13 @@
         <v>49.33333333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>172.6666666666667</v>
+        <v>171.3333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>8.108317815021726</v>
+        <v>8.128617558994272</v>
       </c>
       <c r="I21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J21" t="n">
         <v>0.725</v>
@@ -27146,13 +27146,13 @@
         <v>66.66666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>172.6666666666667</v>
+        <v>171.3333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>8.108317815021726</v>
+        <v>8.128617558994272</v>
       </c>
       <c r="I22" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J22" t="n">
         <v>0.725</v>
@@ -27218,13 +27218,13 @@
         <v>65.56962025316457</v>
       </c>
       <c r="G23" t="n">
-        <v>172.6666666666667</v>
+        <v>171.3333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>8.108317815021726</v>
+        <v>8.128617558994272</v>
       </c>
       <c r="I23" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J23" t="n">
         <v>0.725</v>
@@ -33574,10 +33574,10 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2.938539575707716</v>
+        <v>2.961407587970033</v>
       </c>
       <c r="G2" t="n">
-        <v>1.545937170937171</v>
+        <v>1.557967810399717</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -33621,10 +33621,10 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.647842231913028</v>
+        <v>3.676230109204179</v>
       </c>
       <c r="G3" t="n">
-        <v>1.919094419094419</v>
+        <v>1.934029006013442</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -33668,10 +33668,10 @@
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>4.255815937231866</v>
+        <v>4.288935127404876</v>
       </c>
       <c r="G4" t="n">
-        <v>2.238943488943489</v>
+        <v>2.256367173682349</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -33715,10 +33715,10 @@
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.965118593437177</v>
+        <v>5.003757648639023</v>
       </c>
       <c r="G5" t="n">
-        <v>2.612100737100737</v>
+        <v>2.632428369296073</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -33762,10 +33762,10 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>5.573092298756015</v>
+        <v>5.61646266683972</v>
       </c>
       <c r="G6" t="n">
-        <v>2.931949806949807</v>
+        <v>2.954766536964981</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -33812,7 +33812,7 @@
         <v>3.519968168786019</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8529308529308528</v>
+        <v>0.8595684471170851</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -33859,7 +33859,7 @@
         <v>4.399960210982525</v>
       </c>
       <c r="G8" t="n">
-        <v>1.066163566163566</v>
+        <v>1.074460558896356</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -33906,7 +33906,7 @@
         <v>5.059954242629903</v>
       </c>
       <c r="G9" t="n">
-        <v>1.226088101088101</v>
+        <v>1.23562964273081</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -33953,7 +33953,7 @@
         <v>5.939946284826408</v>
       </c>
       <c r="G10" t="n">
-        <v>1.439320814320814</v>
+        <v>1.450521754510081</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -34000,7 +34000,7 @@
         <v>6.819938327022912</v>
       </c>
       <c r="G11" t="n">
-        <v>1.652553527553527</v>
+        <v>1.665413866289353</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -34279,13 +34279,13 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2.685152685152685</v>
+        <v>2.706048814998231</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9168463320463321</v>
+        <v>0.9239813229571986</v>
       </c>
       <c r="H17" t="n">
-        <v>0.938223938223938</v>
+        <v>0.9455252918287935</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -34326,13 +34326,13 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.685152685152685</v>
+        <v>2.706048814998231</v>
       </c>
       <c r="G18" t="n">
-        <v>1.701604633204633</v>
+        <v>1.714846692607004</v>
       </c>
       <c r="H18" t="n">
-        <v>1.133687258687259</v>
+        <v>1.142509727626459</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -34373,13 +34373,13 @@
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>2.685152685152685</v>
+        <v>2.706048814998231</v>
       </c>
       <c r="G19" t="n">
-        <v>2.447513513513514</v>
+        <v>2.466560311284047</v>
       </c>
       <c r="H19" t="n">
-        <v>1.407335907335907</v>
+        <v>1.41828793774319</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -34420,13 +34420,13 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>2.685152685152685</v>
+        <v>2.706048814998231</v>
       </c>
       <c r="G20" t="n">
-        <v>3.216732046332046</v>
+        <v>3.241764980544747</v>
       </c>
       <c r="H20" t="n">
-        <v>1.563706563706563</v>
+        <v>1.575875486381323</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -34467,13 +34467,13 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>2.685152685152685</v>
+        <v>2.706048814998231</v>
       </c>
       <c r="G21" t="n">
-        <v>4.102498841698842</v>
+        <v>4.134424902723735</v>
       </c>
       <c r="H21" t="n">
-        <v>1.680984555984556</v>
+        <v>1.694066147859922</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -68,7 +68,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Anh_can_cu'!$A$1:$X$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Anh_can_cu_vien'!$A$1:$G$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Anh_can_cu_mui_ten'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Hang_so_can_cu'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Hang_so_can_cu'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47534,15 +47534,15 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -47607,30 +47607,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bases.baseSystem.lookEvery</t>
+          <t>bases.balloon.radiusM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>baseSystem</t>
+          <t>balloon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lookEvery</t>
+          <t>radiusM</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.25</v>
+        <v>40</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>ban_kinh</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -47640,72 +47640,1622 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>BaseSystem.LookEvery</t>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:314)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.lookEvery</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.balloon.radiusM</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>{"value":0.25,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseSystem.LookEvery"}</t>
+          <t>{"value":40.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:314)"}</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>bases.balloon.scatterShare</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>balloon</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>scatterShare</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:314)</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.balloon.scatterShare</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>{"value":0.5,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:314)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bases.baseSystem.lookEvery</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>baseSystem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lookEvery</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BaseSystem.LookEvery</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.lookEvery</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>{"value":0.25,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseSystem.LookEvery"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bases.blastWall.coneDeg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>blastWall</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>coneDeg</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.coneDeg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{"value":50.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bases.blastWall.cutShare</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>blastWall</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cutShare</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.cutShare</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{"value":0.3,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bases.blastWall.radiusM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>blastWall</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.radiusM</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{"value":8.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bases.droneHunt.reachM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>droneHunt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>reachM</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.droneHunt.reachM</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bases.fireControl.damageShare</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>damageShare</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.damageShare</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bases.fireControl.focus</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>focus</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.focus</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{"value":2.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bases.fireControl.radiusM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.radiusM</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bases.flareTower.everySeconds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>everySeconds</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.everySeconds</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bases.flareTower.radiusM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.radiusM</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bases.flareTower.rangeM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>rangeM</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.rangeM</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{"value":40.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bases.flareTower.seconds</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.seconds</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>bases.gear.bulwarkShare</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>gear</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>bulwarkShare</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D16" t="n">
         <v>0.35</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>share</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>nguong</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Gear.BulwarkShare</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gear.bulwarkShare</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>{"value":0.35,"unit":"share","kind":"nguong","linh_vuc":"04","code":"Gear.BulwarkShare"}</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bases.hangar.alive</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.alive</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>{"value":2,"unit":"count","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bases.hangar.budget</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.budget</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>{"value":0.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bases.hangar.everySeconds</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>everySeconds</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.everySeconds</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bases.hangar.postM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>postM</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.postM</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>{"value":20.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bases.microwave.arcDeg</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>arcDeg</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.arcDeg</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bases.microwave.cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{"value":8.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bases.microwave.rangeM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>rangeM</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.rangeM</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bases.paradrop.baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>45</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>{"value":45.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bases.paradrop.fallSeconds</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>fallSeconds</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.fallSeconds</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>{"value":6.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bases.paradrop.heightM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>heightM</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.heightM</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bases.reconPass.seconds</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>reconPass</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.seconds</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>{"value":20.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bases.reconPass.widthM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>reconPass</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>widthM</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>60</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.widthM</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bases.searchlight.dazzleShare</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>searchlight</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dazzleShare</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.dazzleShare</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>{"value":0.2,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bases.searchlight.radiusM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>searchlight</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>35</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.radiusM</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>{"value":35.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bases.shelter.cutShare</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cutShare</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.cutShare</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>{"value":0.5,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>bases.shelter.radiusM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.radiusM</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>bases.sightJammer.closeM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sightJammer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>closeM</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.sightJammer.closeM</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>bases.sightJammer.radiusM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sightJammer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.sightJammer.radiusM</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{"value":35.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -34478,7 +34478,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>TC0111</t>
+          <t>TC0113</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -34551,7 +34551,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>TC0112</t>
+          <t>TC0114</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -34624,7 +34624,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>TC0113</t>
+          <t>TC0115</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>TC0114</t>
+          <t>TC0116</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -34912,7 +34912,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>TC0115</t>
+          <t>TC0117</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -35196,7 +35196,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>TC0116</t>
+          <t>TC0118</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -35269,7 +35269,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>TC0117</t>
+          <t>TC0119</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -35411,7 +35411,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>TC0118</t>
+          <t>TC0120</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -35484,7 +35484,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>TC0119</t>
+          <t>TC0121</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>TC0120</t>
+          <t>TC0122</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>TC0121</t>
+          <t>TC0123</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -36052,7 +36052,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>TC0122</t>
+          <t>TC0124</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -36194,7 +36194,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>TC0123</t>
+          <t>TC0125</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -40,7 +40,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Thap'!$A$1:$EN$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Thap_vu_khi'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Thap_vu_khi'!$A$1:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tuong'!$A$1:$CC$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tuong_luat'!$A$1:$H$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Nha_chinh'!$A$1:$CF$5</definedName>
@@ -517,7 +517,7 @@
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="21" customWidth="1" min="29" max="29"/>
     <col width="23" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="44" customWidth="1" min="31" max="31"/>
     <col width="9" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="14" customWidth="1" min="34" max="34"/>
@@ -543,7 +543,7 @@
     <col width="20" customWidth="1" min="54" max="54"/>
     <col width="18" customWidth="1" min="55" max="55"/>
     <col width="18" customWidth="1" min="56" max="56"/>
-    <col width="16" customWidth="1" min="57" max="57"/>
+    <col width="44" customWidth="1" min="57" max="57"/>
     <col width="27" customWidth="1" min="58" max="58"/>
     <col width="25" customWidth="1" min="59" max="59"/>
     <col width="17" customWidth="1" min="60" max="60"/>
@@ -2350,7 +2350,7 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
+          <t>aircraft_hangar</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="DG6" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
+          <t>aircraft_hangar</t>
         </is>
       </c>
       <c r="DH6" t="n">
-        <v>4</v>
+        <v>5.32</v>
       </c>
       <c r="DI6" t="n">
         <v>8</v>
       </c>
       <c r="DJ6" t="n">
-        <v>8</v>
+        <v>7.72</v>
       </c>
       <c r="DO6" t="n">
         <v>3.6</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>{"id":"aircraft_hangar","rebuildCp":8,"model":"drone_hangar","modelSize":[8.0,8.0,4.0],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_heli","recon_drone"],"every":60,"alive":2,"budget":12,"post":30},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"aircraft_hangar","rebuildCp":8,"model":"aircraft_hangar","modelSize":[8.0,7.72,5.32],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_heli","recon_drone"],"every":60,"alive":2,"budget":12,"post":30},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -9075,13 +9075,13 @@
         <v>5.5</v>
       </c>
       <c r="DH37" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="DI37" t="n">
         <v>6</v>
       </c>
       <c r="DJ37" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="DO37" t="n">
         <v>2.5</v>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="EN37" t="inlineStr">
         <is>
-          <t>{"id":"laser_ad_station","rebuildCp":5,"branches":["laser_ad_station.laser"],"modelSize":[6.0,4.0,4.6],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1136,"speed":0,"turnRate":1,"turretTurnRate":180,"radius":2.5,"length":5.5,"width":4.0,"cp":0,"vision":56,"weapon":"laser_50kw","aps":{"radius":40,"shells":0,"charges":1,"recharge":0.8,"rockets":true,"laser":true},"deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"laser_ad_station","rebuildCp":5,"branches":["laser_ad_station.laser"],"modelSize":[6.0,3.85,6.6],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1136,"speed":0,"turnRate":1,"turretTurnRate":180,"radius":2.5,"length":5.5,"width":4.0,"cp":0,"vision":56,"weapon":"laser_50kw","aps":{"radius":40,"shells":0,"charges":1,"recharge":0.8,"rockets":true,"laser":true},"deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,11 @@
           <t>bunker_hmg</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>bunker_pkm;bunker_pkm;bunker_pkm;bunker_pkm</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr">
         <is>
@@ -9642,6 +9646,12 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr">
+        <is>
+          <t>bunker_pkm;bunker_pkm;bunker_pkm;bunker_pkm</t>
+        </is>
+      </c>
       <c r="BF40" t="n">
         <v>1</v>
       </c>
@@ -9740,7 +9750,6 @@
       <c r="DP40" t="n">
         <v>6</v>
       </c>
-      <c r="DW40" t="inlineStr"/>
       <c r="DZ40" t="n">
         <v>0</v>
       </c>
@@ -9771,7 +9780,7 @@
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker","outgoingDamageMult":0.6086,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1500,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","secondary":[],"deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"}}</t>
+          <t>{"id":"mg_bunker","outgoingDamageMult":0.6086,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1500,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"},"secondary":[{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}]}</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10084,11 @@
           <t>bunker_hmg_twin</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>bunker_pkm;bunker_pkm;bunker_pkm;bunker_pkm</t>
+        </is>
+      </c>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr">
         <is>
@@ -10092,6 +10105,12 @@
       <c r="AK42" t="inlineStr">
         <is>
           <t>doi</t>
+        </is>
+      </c>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr">
+        <is>
+          <t>bunker_pkm;bunker_pkm;bunker_pkm;bunker_pkm</t>
         </is>
       </c>
       <c r="BF42" t="n">
@@ -13328,7 +13347,7 @@
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
+          <t>vehicle_hangar_base</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13420,17 +13439,17 @@
       </c>
       <c r="DG57" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
+          <t>vehicle_hangar_base</t>
         </is>
       </c>
       <c r="DH57" t="n">
-        <v>4</v>
+        <v>4.93</v>
       </c>
       <c r="DI57" t="n">
         <v>8</v>
       </c>
       <c r="DJ57" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="DO57" t="n">
         <v>3.6</v>
@@ -13468,7 +13487,7 @@
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>{"id":"vehicle_hangar","rebuildCp":8,"model":"drone_hangar","modelSize":[8.0,8.0,4.0],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_jeep","armored_car","light_tank"],"every":60,"alive":2,"budget":5,"post":20},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"vehicle_hangar","rebuildCp":8,"model":"vehicle_hangar_base","modelSize":[8.0,7.5,4.93],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_jeep","armored_car","light_tank"],"every":60,"alive":2,"budget":5,"post":20},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -21823,7 +21842,7 @@
         <v>0.63</v>
       </c>
       <c r="F30" t="n">
-        <v>55.42607142857143</v>
+        <v>68.31672538673928</v>
       </c>
       <c r="G30" t="n">
         <v>220</v>
@@ -21967,7 +21986,7 @@
         <v>0.63</v>
       </c>
       <c r="F32" t="n">
-        <v>54.98027197854819</v>
+        <v>65.64693864521485</v>
       </c>
       <c r="G32" t="n">
         <v>220</v>
@@ -22724,11 +22743,13 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22759,15 +22780,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>arc_deg_center_deg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>arc_deg_half_deg</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>slot</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>nguon</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>raw_json</t>
         </is>
@@ -22797,17 +22828,17 @@
           <t>Turret</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>missile</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[70].secondary[0]</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>{"weapon":"sam","slot":"missile","aim":"Turret"}</t>
         </is>
@@ -22837,17 +22868,17 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>gun</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[0]</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
         </is>
@@ -22877,24 +22908,208 @@
           <t>Free</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>gun</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[1]</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mg_bunker/0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[0]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mg_bunker/1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[1]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mg_bunker/2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[2]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mg_bunker/3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[3]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -7621,7 +7621,7 @@
         <v>5</v>
       </c>
       <c r="EB30" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="EC30" t="n">
         <v>0.15</v>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="EN30" t="inlineStr">
         <is>
-          <t>{"id":"guard_tower.watch","rebuildCp":5,"towerRole":"observation_reach","art":"guard_tower_a","inherits":"guard_tower","branchOf":"guard_tower","vision":78,"towerRangeAura":{"radius":30,"range":0.15}}</t>
+          <t>{"id":"guard_tower.watch","rebuildCp":5,"towerRole":"observation_reach","art":"guard_tower_a","inherits":"guard_tower","branchOf":"guard_tower","vision":78,"towerRangeAura":{"radius":35,"range":0.15}}</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>258</v>
+        <v>369</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -19189,7 +19189,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>258</v>
+        <v>369</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -19208,7 +19208,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>240</v>
+        <v>343</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -19227,7 +19227,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240</v>
+        <v>343</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -19246,7 +19246,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320</v>
+        <v>457</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -20162,7 +20162,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H5" t="n">
-        <v>9.678493163172465</v>
+        <v>9.804349614137468</v>
       </c>
       <c r="I5" t="n">
         <v>46</v>
@@ -20234,7 +20234,7 @@
         <v>328.4901960784314</v>
       </c>
       <c r="H6" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I6" t="n">
         <v>14</v>
@@ -20306,7 +20306,7 @@
         <v>328.4901960784314</v>
       </c>
       <c r="H7" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I7" t="n">
         <v>14</v>
@@ -20378,7 +20378,7 @@
         <v>328.4901960784314</v>
       </c>
       <c r="H8" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I8" t="n">
         <v>14</v>
@@ -20696,7 +20696,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H13" t="n">
-        <v>9.678493163172465</v>
+        <v>9.804349614137468</v>
       </c>
       <c r="I13" t="n">
         <v>46</v>
@@ -20768,7 +20768,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H14" t="n">
-        <v>9.678493163172465</v>
+        <v>9.804349614137468</v>
       </c>
       <c r="I14" t="n">
         <v>46</v>
@@ -20840,7 +20840,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H15" t="n">
-        <v>9.678493163172465</v>
+        <v>9.804349614137468</v>
       </c>
       <c r="I15" t="n">
         <v>46</v>
@@ -21284,13 +21284,13 @@
         <v>0.75</v>
       </c>
       <c r="F22" t="n">
-        <v>77.08333333333334</v>
+        <v>77.12080700048615</v>
       </c>
       <c r="G22" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H22" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I22" t="n">
         <v>14</v>
@@ -21428,13 +21428,13 @@
         <v>0.75</v>
       </c>
       <c r="F24" t="n">
-        <v>67.69230769230769</v>
+        <v>67.72572249147372</v>
       </c>
       <c r="G24" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H24" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -21500,13 +21500,13 @@
         <v>0.51</v>
       </c>
       <c r="F25" t="n">
-        <v>50.00000000000001</v>
+        <v>50.04729474082482</v>
       </c>
       <c r="G25" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H25" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
@@ -21572,13 +21572,13 @@
         <v>0.51</v>
       </c>
       <c r="F26" t="n">
-        <v>87.78906506654879</v>
+        <v>87.8363598073736</v>
       </c>
       <c r="G26" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H26" t="n">
-        <v>7.677395967178945</v>
+        <v>7.673242140110352</v>
       </c>
       <c r="I26" t="n">
         <v>14</v>
@@ -21644,13 +21644,13 @@
         <v>0.51</v>
       </c>
       <c r="F27" t="n">
-        <v>51.01607937050976</v>
+        <v>49.96776191754897</v>
       </c>
       <c r="G27" t="n">
         <v>126.6920634920635</v>
       </c>
       <c r="H27" t="n">
-        <v>8.795927624837997</v>
+        <v>8.921784075803</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
@@ -22280,7 +22280,7 @@
         <v>126.6920634920635</v>
       </c>
       <c r="H36" t="n">
-        <v>8.795927624837997</v>
+        <v>8.921784075803</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
@@ -22352,7 +22352,7 @@
         <v>126.6920634920635</v>
       </c>
       <c r="H37" t="n">
-        <v>8.795927624837997</v>
+        <v>8.921784075803</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -22424,7 +22424,7 @@
         <v>126.6920634920635</v>
       </c>
       <c r="H38" t="n">
-        <v>8.795927624837997</v>
+        <v>8.921784075803</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
@@ -22685,7 +22685,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H42" t="n">
-        <v>9.678493163172465</v>
+        <v>9.804349614137468</v>
       </c>
       <c r="I42" t="n">
         <v>46</v>
@@ -25546,7 +25546,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2.778157694147336</v>
+        <v>2.721315755988609</v>
       </c>
       <c r="G2" t="n">
         <v>1.477624011502516</v>
@@ -25593,7 +25593,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.448747482389797</v>
+        <v>3.378185076399653</v>
       </c>
       <c r="G3" t="n">
         <v>1.834291876347951</v>
@@ -25640,7 +25640,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>4.023538729454764</v>
+        <v>3.941215922466261</v>
       </c>
       <c r="G4" t="n">
         <v>2.14000718907261</v>
@@ -25687,7 +25687,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.694128517697224</v>
+        <v>4.598085242877305</v>
       </c>
       <c r="G5" t="n">
         <v>2.496675053918044</v>
@@ -25734,7 +25734,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>5.268919764762191</v>
+        <v>5.161116088943914</v>
       </c>
       <c r="G6" t="n">
         <v>2.802390366642703</v>
@@ -25781,7 +25781,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>3.992535323913624</v>
+        <v>4.548638458315877</v>
       </c>
       <c r="G7" t="n">
         <v>0.8152408339324227</v>
@@ -25828,7 +25828,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>4.990669154892029</v>
+        <v>5.685798072894848</v>
       </c>
       <c r="G8" t="n">
         <v>1.019051042415528</v>
@@ -25875,7 +25875,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>5.739269528125835</v>
+        <v>6.538667783829075</v>
       </c>
       <c r="G9" t="n">
         <v>1.171908698777858</v>
@@ -25922,7 +25922,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>6.73740335910424</v>
+        <v>7.675827398408043</v>
       </c>
       <c r="G10" t="n">
         <v>1.375718907260963</v>
@@ -25969,7 +25969,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>7.735537190082646</v>
+        <v>8.812987012987012</v>
       </c>
       <c r="G11" t="n">
         <v>1.579529115744069</v>
@@ -35101,7 +35101,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.420007143</v>
+        <v>6.314507143</v>
       </c>
       <c r="F13">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$13,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$13,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -35385,7 +35385,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.9</v>
+        <v>5.571</v>
       </c>
       <c r="F17">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$17,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$17,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -35458,7 +35458,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.88</v>
+        <v>4.113996429</v>
       </c>
       <c r="F18">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$18,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$18,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -35600,7 +35600,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.55</v>
+        <v>7.929</v>
       </c>
       <c r="F20">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$20,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$20,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -35673,7 +35673,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.55</v>
+        <v>7.929</v>
       </c>
       <c r="F21">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$21,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$21,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -36241,7 +36241,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6.67</v>
+        <v>9.529</v>
       </c>
       <c r="F29">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$29,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$29,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -36265,11 +36265,7 @@
         <f>IF(ISNUMBER($H$29),AND(NOT($J$29),OR($G$29&lt;$H$29,$G$29&gt;$I$29)),FALSE)</f>
         <v/>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>TC0124</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_spg_9</t>
@@ -36409,7 +36405,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>TC0125</t>
+          <t>TC0124</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -36525,7 +36521,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.209997143</v>
+        <v>7.443</v>
       </c>
       <c r="F33">
         <f>60/INDEX(cc_input_nhip_that!$B$2:$B$31,MATCH($P$33,cc_input_nhip_that!$A$2:$A$31,0))/IF(INDEX(cc_input_nhip_that!$C$2:$C$31,MATCH($P$33,cc_input_nhip_that!$A$2:$A$31,0))="gun",0.7,1)</f>
@@ -37461,11 +37457,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.607833</v>
+        <v>0.86835</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>LECH_DOT_1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -37608,11 +37604,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.206267</v>
+        <v>0.294677</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>NHANH_QUA;LECH_DOT_1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -37629,11 +37625,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.259</v>
+        <v>0.37002</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>NHANH_QUA;LECH_DOT_1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -37650,11 +37646,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.259</v>
+        <v>0.37002</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>NHANH_QUA;LECH_DOT_1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -37839,11 +37835,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4669</v>
+        <v>0.66703</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -38007,11 +38003,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2688</v>
+        <v>0.383973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>NHANH_QUA;LECH_DOT_1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -38028,11 +38024,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.364</v>
+        <v>0.51996</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NHANH_QUA</t>
+          <t>NHANH_QUA;LECH_DOT_1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -25,18 +25,19 @@
     <sheet name="cc_input_vu_khi" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="cc_input_vu_khi_suy_ra" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="cc_input_bang_xuyen_giap" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Thap_gia_cong_thuc" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Tuong_duong_xe_cong_trinh" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Nha_chinh_so_sanh" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Can_cu_AI_cap" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Can_cu_tham_chieu" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Can_cu_so_sanh_that" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="cc_input_nhip_that" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="cc_input_ty_le_nhip" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Anh_can_cu" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Anh_can_cu_vien" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Anh_can_cu_mui_ten" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Hang_so_can_cu" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="cc_input_bang_danh_noc" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Thap_gia_cong_thuc" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Tuong_duong_xe_cong_trinh" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nha_chinh_so_sanh" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Can_cu_AI_cap" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Can_cu_tham_chieu" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Can_cu_so_sanh_that" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="cc_input_nhip_that" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="cc_input_ty_le_nhip" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Anh_can_cu" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Anh_can_cu_vien" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Anh_can_cu_mui_ten" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Hang_so_can_cu" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Thap'!$A$1:$EN$57</definedName>
@@ -54,21 +55,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Can_cu_luat'!$A$1:$H$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Dot_phong_thu'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'Can_cu_AI_kieu'!$A$1:$F$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'cc_input_vu_khi'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'cc_input_vu_khi'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'cc_input_vu_khi_suy_ra'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'cc_input_bang_xuyen_giap'!$A$1:$D$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Thap_gia_cong_thuc'!$A$1:$V$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Tuong_duong_xe_cong_trinh'!$A$1:$M$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Nha_chinh_so_sanh'!$A$1:$M$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Can_cu_AI_cap'!$A$1:$H$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Can_cu_tham_chieu'!$A$1:$AH$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Can_cu_so_sanh_that'!$A$1:$R$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'cc_input_nhip_that'!$A$1:$F$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'cc_input_ty_le_nhip'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'Anh_can_cu'!$A$1:$X$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Anh_can_cu_vien'!$A$1:$G$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Anh_can_cu_mui_ten'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Hang_so_can_cu'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'cc_input_bang_xuyen_giap'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'cc_input_bang_danh_noc'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Thap_gia_cong_thuc'!$A$1:$V$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Tuong_duong_xe_cong_trinh'!$A$1:$M$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'Nha_chinh_so_sanh'!$A$1:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Can_cu_AI_cap'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Can_cu_tham_chieu'!$A$1:$AH$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'Can_cu_so_sanh_that'!$A$1:$R$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'cc_input_nhip_that'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'cc_input_ty_le_nhip'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Anh_can_cu'!$A$1:$X$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Anh_can_cu_vien'!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Anh_can_cu_mui_ten'!$A$1:$J$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Hang_so_can_cu'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19132,8 +19134,9 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19154,10 +19157,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>danh_noc</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>nguon</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>raw_json</t>
         </is>
@@ -19175,12 +19183,15 @@
       <c r="C2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id gun_105_wheeled)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19194,12 +19205,15 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id gun_105_wheeled_he)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19213,12 +19227,15 @@
       <c r="C4" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id gun_120_twin_he)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19232,12 +19249,15 @@
       <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id gun_120mm_he)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19251,12 +19271,15 @@
       <c r="C6" t="n">
         <v>4</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id gun_152)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19270,12 +19293,15 @@
       <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id ifv_30)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19289,12 +19315,15 @@
       <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id mlrs_rockets)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19308,12 +19337,15 @@
       <c r="C9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id recoilless_106)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19327,12 +19359,15 @@
       <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id technical_rockets)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19346,15 +19381,18 @@
       <c r="C11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>01_chien_dau/Vu_khi (id thermobaric_rockets)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E11"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19420,7 +19458,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -19442,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -19464,7 +19502,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -19486,7 +19524,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -19508,7 +19546,7 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -19530,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -19552,7 +19590,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -19574,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -19596,7 +19634,7 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -19724,7 +19762,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -19740,7 +19778,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -19756,7 +19794,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -19765,13 +19803,565 @@
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>buoc_6</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_xuyen_giap (id buoc_6)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>he_so</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>nguon</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>raw_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>buoc_0</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_0)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>buoc_1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_1)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>buoc_2</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_2)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>buoc_3</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_3)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>buoc_4</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_4)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>buoc_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_5)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>buoc_6</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>01_chien_dau/Bang_danh_noc (id buoc_6)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>thap_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>thu_tu</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>weapon</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>aim</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>arc_deg_center_deg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>arc_deg_half_deg</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nguon</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>raw_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aa_turret/0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sam</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Turret</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>missile</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[70].secondary[0]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{"weapon":"sam","slot":"missile","aim":"Turret"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>heavy_turret.bastion/0</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>heavy_turret.bastion</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>hmg_roof</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>gun</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[0]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>heavy_turret.bastion/1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>heavy_turret.bastion</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>hmg_roof</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>gun</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[1]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mg_bunker/0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-30</v>
+      </c>
+      <c r="G5" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[0]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mg_bunker/1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[1]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mg_bunker/2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G7" t="n">
+        <v>40</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[2]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mg_bunker/3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mg_bunker</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bunker_pkm</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>90</v>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[3]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19937,16 +20527,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9375</v>
+        <v>0.9775</v>
       </c>
       <c r="F2" t="n">
-        <v>219.4167303643507</v>
+        <v>227.8558353783642</v>
       </c>
       <c r="G2" t="n">
-        <v>173.8</v>
+        <v>158</v>
       </c>
       <c r="H2" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I2" t="n">
         <v>7</v>
@@ -20009,16 +20599,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9375</v>
+        <v>0.9775</v>
       </c>
       <c r="F3" t="n">
-        <v>240.3845953002611</v>
+        <v>249.6301566579635</v>
       </c>
       <c r="G3" t="n">
-        <v>173.8</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
@@ -20081,16 +20671,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9375</v>
+        <v>0.9775</v>
       </c>
       <c r="F4" t="n">
-        <v>49.64061096136568</v>
+        <v>51.54986522911052</v>
       </c>
       <c r="G4" t="n">
-        <v>173.8</v>
+        <v>158</v>
       </c>
       <c r="H4" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I4" t="n">
         <v>7</v>
@@ -20153,7 +20743,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -20162,7 +20752,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H5" t="n">
-        <v>9.804349614137468</v>
+        <v>11.53569659348897</v>
       </c>
       <c r="I5" t="n">
         <v>46</v>
@@ -20225,16 +20815,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>76.66666666666667</v>
+        <v>99.66666666666667</v>
       </c>
       <c r="G6" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H6" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I6" t="n">
         <v>14</v>
@@ -20297,16 +20887,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F7" t="n">
-        <v>65.16666666666667</v>
+        <v>84.71666666666668</v>
       </c>
       <c r="G7" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H7" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I7" t="n">
         <v>14</v>
@@ -20369,16 +20959,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F8" t="n">
-        <v>81.82692307692308</v>
+        <v>117.875</v>
       </c>
       <c r="G8" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H8" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I8" t="n">
         <v>14</v>
@@ -20687,16 +21277,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F13" t="n">
-        <v>44.66666666666667</v>
+        <v>69.33333333333334</v>
       </c>
       <c r="G13" t="n">
         <v>172.8789682539683</v>
       </c>
       <c r="H13" t="n">
-        <v>9.804349614137468</v>
+        <v>11.53569659348897</v>
       </c>
       <c r="I13" t="n">
         <v>46</v>
@@ -20759,16 +21349,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F14" t="n">
-        <v>64.16666666666667</v>
+        <v>94.25</v>
       </c>
       <c r="G14" t="n">
         <v>172.8789682539683</v>
       </c>
       <c r="H14" t="n">
-        <v>9.804349614137468</v>
+        <v>11.53569659348897</v>
       </c>
       <c r="I14" t="n">
         <v>46</v>
@@ -20831,16 +21421,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F15" t="n">
-        <v>59.36708860759494</v>
+        <v>92.15189873417722</v>
       </c>
       <c r="G15" t="n">
         <v>172.8789682539683</v>
       </c>
       <c r="H15" t="n">
-        <v>9.804349614137468</v>
+        <v>11.53569659348897</v>
       </c>
       <c r="I15" t="n">
         <v>46</v>
@@ -21065,16 +21655,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="F19" t="n">
-        <v>64.59999999999999</v>
+        <v>77.52</v>
       </c>
       <c r="G19" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I19" t="n">
         <v>7</v>
@@ -21137,16 +21727,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="F20" t="n">
-        <v>66.66666666666667</v>
+        <v>80</v>
       </c>
       <c r="G20" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I20" t="n">
         <v>7</v>
@@ -21209,16 +21799,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="F21" t="n">
-        <v>66.89159454305413</v>
+        <v>80.26991345166496</v>
       </c>
       <c r="G21" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
@@ -21281,16 +21871,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="F22" t="n">
-        <v>77.12080700048615</v>
+        <v>92.54496840058339</v>
       </c>
       <c r="G22" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H22" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I22" t="n">
         <v>14</v>
@@ -21353,16 +21943,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="F23" t="n">
-        <v>77.77777777777777</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="G23" t="n">
         <v>183.3333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I23" t="n">
         <v>7</v>
@@ -21425,16 +22015,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.75</v>
+        <v>1.04</v>
       </c>
       <c r="F24" t="n">
-        <v>67.72572249147372</v>
+        <v>81.27086698976845</v>
       </c>
       <c r="G24" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H24" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -21497,16 +22087,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.51</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>50.04729474082482</v>
+        <v>60.05675368898979</v>
       </c>
       <c r="G25" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H25" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
@@ -21569,16 +22159,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.51</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>87.8363598073736</v>
+        <v>123.5423830007917</v>
       </c>
       <c r="G26" t="n">
         <v>328.4901960784314</v>
       </c>
       <c r="H26" t="n">
-        <v>7.673242140110352</v>
+        <v>10.81329019942361</v>
       </c>
       <c r="I26" t="n">
         <v>14</v>
@@ -21641,16 +22231,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.51</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>49.96776191754897</v>
+        <v>51.67730052048679</v>
       </c>
       <c r="G27" t="n">
         <v>126.6920634920635</v>
       </c>
       <c r="H27" t="n">
-        <v>8.921784075803</v>
+        <v>10.16857873849875</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
@@ -21839,16 +22429,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.63</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>68.31672538673928</v>
+        <v>86.62070588902758</v>
       </c>
       <c r="G30" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I30" t="n">
         <v>7</v>
@@ -21911,16 +22501,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.63</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>55.21599999999999</v>
+        <v>49.69439999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
@@ -21983,16 +22573,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.63</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>65.64693864521485</v>
+        <v>82.61632637425784</v>
       </c>
       <c r="G32" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>20.84288116757437</v>
+        <v>27.07964301109967</v>
       </c>
       <c r="I32" t="n">
         <v>7</v>
@@ -22055,16 +22645,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F33" t="n">
-        <v>276.25</v>
+        <v>286.875</v>
       </c>
       <c r="G33" t="n">
         <v>144.8333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I33" t="n">
         <v>7</v>
@@ -22127,16 +22717,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F34" t="n">
-        <v>226.6666666666667</v>
+        <v>235.3846153846154</v>
       </c>
       <c r="G34" t="n">
         <v>144.8333333333333</v>
       </c>
       <c r="H34" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
@@ -22199,16 +22789,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F35" t="n">
-        <v>139.7014925373134</v>
+        <v>145.0746268656716</v>
       </c>
       <c r="G35" t="n">
         <v>144.8333333333333</v>
       </c>
       <c r="H35" t="n">
-        <v>36.01866666666667</v>
+        <v>37.404</v>
       </c>
       <c r="I35" t="n">
         <v>7</v>
@@ -22271,16 +22861,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F36" t="n">
-        <v>57.04054054054053</v>
+        <v>60.39729729729729</v>
       </c>
       <c r="G36" t="n">
         <v>126.6920634920635</v>
       </c>
       <c r="H36" t="n">
-        <v>8.921784075803</v>
+        <v>10.16857873849875</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
@@ -22343,16 +22933,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>51.14732142857143</v>
+        <v>54.15727040816327</v>
       </c>
       <c r="G37" t="n">
         <v>126.6920634920635</v>
       </c>
       <c r="H37" t="n">
-        <v>8.921784075803</v>
+        <v>10.16857873849875</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -22415,16 +23005,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F38" t="n">
-        <v>37.5</v>
+        <v>39</v>
       </c>
       <c r="G38" t="n">
         <v>126.6920634920635</v>
       </c>
       <c r="H38" t="n">
-        <v>8.921784075803</v>
+        <v>10.16857873849875</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
@@ -22676,7 +23266,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1.275</v>
+        <v>1.36</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -22685,7 +23275,7 @@
         <v>172.8789682539683</v>
       </c>
       <c r="H42" t="n">
-        <v>9.804349614137468</v>
+        <v>11.53569659348897</v>
       </c>
       <c r="I42" t="n">
         <v>46</v>
@@ -22732,389 +23322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>thap_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>thu_tu</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>weapon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aim</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>arc_deg_center_deg</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>arc_deg_half_deg</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>slot</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>nguon</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>raw_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>aa_turret/0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sam</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Turret</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>missile</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[70].secondary[0]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>{"weapon":"sam","slot":"missile","aim":"Turret"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>heavy_turret.bastion/0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>heavy_turret.bastion</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>hmg_roof</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>gun</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[0]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>heavy_turret.bastion/1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>heavy_turret.bastion</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>hmg_roof</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>gun</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[98].secondary[1]</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>{"weapon":"hmg_roof","slot":"gun","aim":"Free"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mg_bunker/0</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>bunker_pkm</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G5" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[0]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>mg_bunker/1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>bunker_pkm</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>30</v>
-      </c>
-      <c r="G6" t="n">
-        <v>40</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[1]</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>mg_bunker/2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>bunker_pkm</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>-90</v>
-      </c>
-      <c r="G7" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[2]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mg_bunker/3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>mg_bunker</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>bunker_pkm</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>90</v>
-      </c>
-      <c r="G8" t="n">
-        <v>40</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[105].secondary[3]</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23224,7 +23432,7 @@
         </is>
       </c>
       <c r="E2">
-        <f>IF($D$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F2" t="inlineStr">
@@ -23233,7 +23441,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>IF($F$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H2" t="inlineStr">
@@ -23242,7 +23450,7 @@
         </is>
       </c>
       <c r="I2">
-        <f>IF($H$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J2" t="inlineStr">
@@ -23251,7 +23459,7 @@
         </is>
       </c>
       <c r="K2">
-        <f>IF($J$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$3))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$2="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$3/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$3,Thap!$K$3)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$2,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L2" t="inlineStr">
@@ -23281,7 +23489,7 @@
         </is>
       </c>
       <c r="E3">
-        <f>IF($D$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F3" t="inlineStr">
@@ -23290,7 +23498,7 @@
         </is>
       </c>
       <c r="G3">
-        <f>IF($F$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H3" t="inlineStr">
@@ -23299,7 +23507,7 @@
         </is>
       </c>
       <c r="I3">
-        <f>IF($H$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J3" t="inlineStr">
@@ -23308,7 +23516,7 @@
         </is>
       </c>
       <c r="K3">
-        <f>IF($J$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$4))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$3="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$4/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$4,Thap!$K$4)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$3,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L3" t="inlineStr">
@@ -23338,7 +23546,7 @@
         </is>
       </c>
       <c r="E4">
-        <f>IF($D$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F4" t="inlineStr">
@@ -23347,7 +23555,7 @@
         </is>
       </c>
       <c r="G4">
-        <f>IF($F$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H4" t="inlineStr">
@@ -23356,7 +23564,7 @@
         </is>
       </c>
       <c r="I4">
-        <f>IF($H$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J4" t="inlineStr">
@@ -23365,7 +23573,7 @@
         </is>
       </c>
       <c r="K4">
-        <f>IF($J$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$5))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$4="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$5/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$5,Thap!$K$5)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$4,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L4" t="inlineStr">
@@ -23395,7 +23603,7 @@
         </is>
       </c>
       <c r="E5">
-        <f>IF($D$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F5" t="inlineStr">
@@ -23404,12 +23612,12 @@
         </is>
       </c>
       <c r="G5">
-        <f>IF($F$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5">
-        <f>IF($H$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J5" t="inlineStr">
@@ -23418,7 +23626,7 @@
         </is>
       </c>
       <c r="K5">
-        <f>IF($J$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$6))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$5="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$6/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$6,Thap!$K$6)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$5,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L5" t="inlineStr">
@@ -23448,7 +23656,7 @@
         </is>
       </c>
       <c r="E6">
-        <f>IF($D$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F6" t="inlineStr">
@@ -23457,12 +23665,12 @@
         </is>
       </c>
       <c r="G6">
-        <f>IF($F$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6">
-        <f>IF($H$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J6" t="inlineStr">
@@ -23471,7 +23679,7 @@
         </is>
       </c>
       <c r="K6">
-        <f>IF($J$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$7))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$6="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$7/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$7,Thap!$K$7)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$6,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L6" t="inlineStr">
@@ -23501,7 +23709,7 @@
         </is>
       </c>
       <c r="E7">
-        <f>IF($D$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F7" t="inlineStr">
@@ -23510,12 +23718,12 @@
         </is>
       </c>
       <c r="G7">
-        <f>IF($F$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7">
-        <f>IF($H$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J7" t="inlineStr">
@@ -23524,7 +23732,7 @@
         </is>
       </c>
       <c r="K7">
-        <f>IF($J$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$8))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$7="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$8/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$8,Thap!$K$8)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$7,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L7" t="inlineStr">
@@ -23554,7 +23762,7 @@
         </is>
       </c>
       <c r="E8">
-        <f>IF($D$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F8" t="inlineStr">
@@ -23563,12 +23771,12 @@
         </is>
       </c>
       <c r="G8">
-        <f>IF($F$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8">
-        <f>IF($H$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J8" t="inlineStr">
@@ -23577,7 +23785,7 @@
         </is>
       </c>
       <c r="K8">
-        <f>IF($J$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$9))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$8="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$9/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$9,Thap!$K$9)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$8,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L8" t="inlineStr">
@@ -23607,7 +23815,7 @@
         </is>
       </c>
       <c r="E9">
-        <f>IF($D$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F9" t="inlineStr">
@@ -23616,12 +23824,12 @@
         </is>
       </c>
       <c r="G9">
-        <f>IF($F$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9">
-        <f>IF($H$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J9" t="inlineStr">
@@ -23630,7 +23838,7 @@
         </is>
       </c>
       <c r="K9">
-        <f>IF($J$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$14))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$9="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$14/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$14,Thap!$K$14)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$9,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L9" t="inlineStr">
@@ -23660,7 +23868,7 @@
         </is>
       </c>
       <c r="E10">
-        <f>IF($D$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F10" t="inlineStr">
@@ -23669,12 +23877,12 @@
         </is>
       </c>
       <c r="G10">
-        <f>IF($F$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10">
-        <f>IF($H$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J10" t="inlineStr">
@@ -23683,7 +23891,7 @@
         </is>
       </c>
       <c r="K10">
-        <f>IF($J$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$15))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$10="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$15/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$15,Thap!$K$15)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$10,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L10" t="inlineStr">
@@ -23713,7 +23921,7 @@
         </is>
       </c>
       <c r="E11">
-        <f>IF($D$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F11" t="inlineStr">
@@ -23722,12 +23930,12 @@
         </is>
       </c>
       <c r="G11">
-        <f>IF($F$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11">
-        <f>IF($H$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J11" t="inlineStr">
@@ -23736,7 +23944,7 @@
         </is>
       </c>
       <c r="K11">
-        <f>IF($J$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$16))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$11="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$16/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$16,Thap!$K$16)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$11,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L11" t="inlineStr">
@@ -23766,7 +23974,7 @@
         </is>
       </c>
       <c r="E12">
-        <f>IF($D$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F12" t="inlineStr">
@@ -23775,7 +23983,7 @@
         </is>
       </c>
       <c r="G12">
-        <f>IF($F$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H12" t="inlineStr">
@@ -23784,7 +23992,7 @@
         </is>
       </c>
       <c r="I12">
-        <f>IF($H$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J12" t="inlineStr">
@@ -23793,7 +24001,7 @@
         </is>
       </c>
       <c r="K12">
-        <f>IF($J$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$18))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$12="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$18/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$18,Thap!$K$18)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$12,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L12" t="inlineStr">
@@ -23823,7 +24031,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>IF($D$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F13" t="inlineStr">
@@ -23832,12 +24040,12 @@
         </is>
       </c>
       <c r="G13">
-        <f>IF($F$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13">
-        <f>IF($H$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J13" t="inlineStr">
@@ -23846,7 +24054,7 @@
         </is>
       </c>
       <c r="K13">
-        <f>IF($J$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$19))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$13="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$19/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$19,Thap!$K$19)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$13,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L13" t="inlineStr">
@@ -23876,7 +24084,7 @@
         </is>
       </c>
       <c r="E14">
-        <f>IF($D$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F14" t="inlineStr">
@@ -23885,12 +24093,12 @@
         </is>
       </c>
       <c r="G14">
-        <f>IF($F$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14">
-        <f>IF($H$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J14" t="inlineStr">
@@ -23899,7 +24107,7 @@
         </is>
       </c>
       <c r="K14">
-        <f>IF($J$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$20))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$14="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$20/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$20,Thap!$K$20)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$14,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L14" t="inlineStr">
@@ -23929,7 +24137,7 @@
         </is>
       </c>
       <c r="E15">
-        <f>IF($D$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F15" t="inlineStr">
@@ -23938,12 +24146,12 @@
         </is>
       </c>
       <c r="G15">
-        <f>IF($F$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15">
-        <f>IF($H$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J15" t="inlineStr">
@@ -23952,7 +24160,7 @@
         </is>
       </c>
       <c r="K15">
-        <f>IF($J$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$21))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$15="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$21/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$21,Thap!$K$21)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$15,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L15" t="inlineStr">
@@ -23982,7 +24190,7 @@
         </is>
       </c>
       <c r="E16">
-        <f>IF($D$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F16" t="inlineStr">
@@ -23991,7 +24199,7 @@
         </is>
       </c>
       <c r="G16">
-        <f>IF($F$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H16" t="inlineStr">
@@ -24000,7 +24208,7 @@
         </is>
       </c>
       <c r="I16">
-        <f>IF($H$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J16" t="inlineStr">
@@ -24009,7 +24217,7 @@
         </is>
       </c>
       <c r="K16">
-        <f>IF($J$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$23))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$16="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$23/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$23,Thap!$K$23)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$16,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L16" t="inlineStr">
@@ -24039,7 +24247,7 @@
         </is>
       </c>
       <c r="E17">
-        <f>IF($D$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F17" t="inlineStr">
@@ -24048,7 +24256,7 @@
         </is>
       </c>
       <c r="G17">
-        <f>IF($F$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H17" t="inlineStr">
@@ -24057,7 +24265,7 @@
         </is>
       </c>
       <c r="I17">
-        <f>IF($H$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J17" t="inlineStr">
@@ -24066,7 +24274,7 @@
         </is>
       </c>
       <c r="K17">
-        <f>IF($J$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$24))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$17="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$24/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$24,Thap!$K$24)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$17,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L17" t="inlineStr">
@@ -24096,7 +24304,7 @@
         </is>
       </c>
       <c r="E18">
-        <f>IF($D$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F18" t="inlineStr">
@@ -24105,7 +24313,7 @@
         </is>
       </c>
       <c r="G18">
-        <f>IF($F$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H18" t="inlineStr">
@@ -24114,7 +24322,7 @@
         </is>
       </c>
       <c r="I18">
-        <f>IF($H$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J18" t="inlineStr">
@@ -24123,7 +24331,7 @@
         </is>
       </c>
       <c r="K18">
-        <f>IF($J$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$25))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$18="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$25/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$25,Thap!$K$25)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$18,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L18" t="inlineStr">
@@ -24153,7 +24361,7 @@
         </is>
       </c>
       <c r="E19">
-        <f>IF($D$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F19" t="inlineStr">
@@ -24162,7 +24370,7 @@
         </is>
       </c>
       <c r="G19">
-        <f>IF($F$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H19" t="inlineStr">
@@ -24171,7 +24379,7 @@
         </is>
       </c>
       <c r="I19">
-        <f>IF($H$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J19" t="inlineStr">
@@ -24180,7 +24388,7 @@
         </is>
       </c>
       <c r="K19">
-        <f>IF($J$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$28))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$19="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$28/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$28,Thap!$K$28)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$19,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L19" t="inlineStr">
@@ -24210,7 +24418,7 @@
         </is>
       </c>
       <c r="E20">
-        <f>IF($D$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F20" t="inlineStr">
@@ -24219,7 +24427,7 @@
         </is>
       </c>
       <c r="G20">
-        <f>IF($F$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H20" t="inlineStr">
@@ -24228,7 +24436,7 @@
         </is>
       </c>
       <c r="I20">
-        <f>IF($H$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J20" t="inlineStr">
@@ -24237,7 +24445,7 @@
         </is>
       </c>
       <c r="K20">
-        <f>IF($J$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$29))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$20="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$29/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$29,Thap!$K$29)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$20,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L20" t="inlineStr">
@@ -24267,7 +24475,7 @@
         </is>
       </c>
       <c r="E21">
-        <f>IF($D$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F21" t="inlineStr">
@@ -24276,7 +24484,7 @@
         </is>
       </c>
       <c r="G21">
-        <f>IF($F$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H21" t="inlineStr">
@@ -24285,7 +24493,7 @@
         </is>
       </c>
       <c r="I21">
-        <f>IF($H$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J21" t="inlineStr">
@@ -24294,7 +24502,7 @@
         </is>
       </c>
       <c r="K21">
-        <f>IF($J$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$30))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$21="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$30/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$30,Thap!$K$30)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$21,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L21" t="inlineStr">
@@ -24324,7 +24532,7 @@
         </is>
       </c>
       <c r="E22">
-        <f>IF($D$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F22" t="inlineStr">
@@ -24333,12 +24541,12 @@
         </is>
       </c>
       <c r="G22">
-        <f>IF($F$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22">
-        <f>IF($H$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J22" t="inlineStr">
@@ -24347,7 +24555,7 @@
         </is>
       </c>
       <c r="K22">
-        <f>IF($J$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$31))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$22="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$31/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$31,Thap!$K$31)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$22,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L22" t="inlineStr">
@@ -24377,7 +24585,7 @@
         </is>
       </c>
       <c r="E23">
-        <f>IF($D$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F23" t="inlineStr">
@@ -24386,12 +24594,12 @@
         </is>
       </c>
       <c r="G23">
-        <f>IF($F$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23">
-        <f>IF($H$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J23" t="inlineStr">
@@ -24400,7 +24608,7 @@
         </is>
       </c>
       <c r="K23">
-        <f>IF($J$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$32))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$23="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$32/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$32,Thap!$K$32)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$23,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L23" t="inlineStr">
@@ -24430,7 +24638,7 @@
         </is>
       </c>
       <c r="E24">
-        <f>IF($D$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F24" t="inlineStr">
@@ -24439,12 +24647,12 @@
         </is>
       </c>
       <c r="G24">
-        <f>IF($F$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24">
-        <f>IF($H$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J24" t="inlineStr">
@@ -24453,7 +24661,7 @@
         </is>
       </c>
       <c r="K24">
-        <f>IF($J$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$33))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$24="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$33/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$33,Thap!$K$33)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$24,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L24" t="inlineStr">
@@ -24483,7 +24691,7 @@
         </is>
       </c>
       <c r="E25">
-        <f>IF($D$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F25" t="inlineStr">
@@ -24492,12 +24700,12 @@
         </is>
       </c>
       <c r="G25">
-        <f>IF($F$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25">
-        <f>IF($H$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J25" t="inlineStr">
@@ -24506,7 +24714,7 @@
         </is>
       </c>
       <c r="K25">
-        <f>IF($J$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$34))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$25="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$34/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$34,Thap!$K$34)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$25,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L25" t="inlineStr">
@@ -24536,7 +24744,7 @@
         </is>
       </c>
       <c r="E26">
-        <f>IF($D$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F26" t="inlineStr">
@@ -24545,12 +24753,12 @@
         </is>
       </c>
       <c r="G26">
-        <f>IF($F$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26">
-        <f>IF($H$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J26" t="inlineStr">
@@ -24559,7 +24767,7 @@
         </is>
       </c>
       <c r="K26">
-        <f>IF($J$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$35))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$26="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$35/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$35,Thap!$K$35)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$26,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L26" t="inlineStr">
@@ -24589,7 +24797,7 @@
         </is>
       </c>
       <c r="E27">
-        <f>IF($D$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F27" t="inlineStr">
@@ -24598,12 +24806,12 @@
         </is>
       </c>
       <c r="G27">
-        <f>IF($F$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27">
-        <f>IF($H$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J27" t="inlineStr">
@@ -24612,7 +24820,7 @@
         </is>
       </c>
       <c r="K27">
-        <f>IF($J$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$36))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$27="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$36/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$36,Thap!$K$36)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$27,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L27" t="inlineStr">
@@ -24642,7 +24850,7 @@
         </is>
       </c>
       <c r="E28">
-        <f>IF($D$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F28" t="inlineStr">
@@ -24651,12 +24859,12 @@
         </is>
       </c>
       <c r="G28">
-        <f>IF($F$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28">
-        <f>IF($H$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J28" t="inlineStr">
@@ -24665,7 +24873,7 @@
         </is>
       </c>
       <c r="K28">
-        <f>IF($J$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$37))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$28="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$37/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$37,Thap!$K$37)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$28,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L28" t="inlineStr">
@@ -24695,7 +24903,7 @@
         </is>
       </c>
       <c r="E29">
-        <f>IF($D$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F29" t="inlineStr">
@@ -24704,12 +24912,12 @@
         </is>
       </c>
       <c r="G29">
-        <f>IF($F$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29">
-        <f>IF($H$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J29" t="inlineStr">
@@ -24718,7 +24926,7 @@
         </is>
       </c>
       <c r="K29">
-        <f>IF($J$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$38))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$29="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$38/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$38,Thap!$K$38)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$29,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L29" t="inlineStr">
@@ -24748,7 +24956,7 @@
         </is>
       </c>
       <c r="E30">
-        <f>IF($D$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F30" t="inlineStr">
@@ -24757,7 +24965,7 @@
         </is>
       </c>
       <c r="G30">
-        <f>IF($F$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H30" t="inlineStr">
@@ -24766,7 +24974,7 @@
         </is>
       </c>
       <c r="I30">
-        <f>IF($H$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J30" t="inlineStr">
@@ -24775,7 +24983,7 @@
         </is>
       </c>
       <c r="K30">
-        <f>IF($J$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$40))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$30="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$40/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$40,Thap!$K$40)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$30,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L30" t="inlineStr">
@@ -24805,7 +25013,7 @@
         </is>
       </c>
       <c r="E31">
-        <f>IF($D$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F31" t="inlineStr">
@@ -24814,7 +25022,7 @@
         </is>
       </c>
       <c r="G31">
-        <f>IF($F$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H31" t="inlineStr">
@@ -24823,7 +25031,7 @@
         </is>
       </c>
       <c r="I31">
-        <f>IF($H$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J31" t="inlineStr">
@@ -24832,7 +25040,7 @@
         </is>
       </c>
       <c r="K31">
-        <f>IF($J$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$41))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$31="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$41/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$41,Thap!$K$41)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$31,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L31" t="inlineStr">
@@ -24862,7 +25070,7 @@
         </is>
       </c>
       <c r="E32">
-        <f>IF($D$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F32" t="inlineStr">
@@ -24871,7 +25079,7 @@
         </is>
       </c>
       <c r="G32">
-        <f>IF($F$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H32" t="inlineStr">
@@ -24880,7 +25088,7 @@
         </is>
       </c>
       <c r="I32">
-        <f>IF($H$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J32" t="inlineStr">
@@ -24889,7 +25097,7 @@
         </is>
       </c>
       <c r="K32">
-        <f>IF($J$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$42))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$32="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$42/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$42,Thap!$K$42)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$32,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L32" t="inlineStr">
@@ -24919,7 +25127,7 @@
         </is>
       </c>
       <c r="E33">
-        <f>IF($D$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F33" t="inlineStr">
@@ -24928,12 +25136,12 @@
         </is>
       </c>
       <c r="G33">
-        <f>IF($F$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33">
-        <f>IF($H$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J33" t="inlineStr">
@@ -24942,7 +25150,7 @@
         </is>
       </c>
       <c r="K33">
-        <f>IF($J$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$43))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$33="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$43/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$43,Thap!$K$43)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$33,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L33" t="inlineStr">
@@ -24972,7 +25180,7 @@
         </is>
       </c>
       <c r="E34">
-        <f>IF($D$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F34" t="inlineStr">
@@ -24981,12 +25189,12 @@
         </is>
       </c>
       <c r="G34">
-        <f>IF($F$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34">
-        <f>IF($H$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J34" t="inlineStr">
@@ -24995,7 +25203,7 @@
         </is>
       </c>
       <c r="K34">
-        <f>IF($J$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$44))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$34="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$44/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$44,Thap!$K$44)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$34,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L34" t="inlineStr">
@@ -25025,7 +25233,7 @@
         </is>
       </c>
       <c r="E35">
-        <f>IF($D$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F35" t="inlineStr">
@@ -25034,12 +25242,12 @@
         </is>
       </c>
       <c r="G35">
-        <f>IF($F$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35">
-        <f>IF($H$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J35" t="inlineStr">
@@ -25048,7 +25256,7 @@
         </is>
       </c>
       <c r="K35">
-        <f>IF($J$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$45))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$35="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$45/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$45,Thap!$K$45)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$35,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L35" t="inlineStr">
@@ -25078,7 +25286,7 @@
         </is>
       </c>
       <c r="E36">
-        <f>IF($D$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F36" t="inlineStr">
@@ -25087,12 +25295,12 @@
         </is>
       </c>
       <c r="G36">
-        <f>IF($F$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36">
-        <f>IF($H$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J36" t="inlineStr">
@@ -25101,7 +25309,7 @@
         </is>
       </c>
       <c r="K36">
-        <f>IF($J$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$48))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$36="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$48/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$48,Thap!$K$48)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$36,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L36" t="inlineStr">
@@ -25131,7 +25339,7 @@
         </is>
       </c>
       <c r="E37">
-        <f>IF($D$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F37" t="inlineStr">
@@ -25140,12 +25348,12 @@
         </is>
       </c>
       <c r="G37">
-        <f>IF($F$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37">
-        <f>IF($H$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J37" t="inlineStr">
@@ -25154,7 +25362,7 @@
         </is>
       </c>
       <c r="K37">
-        <f>IF($J$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$49))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$37="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$49/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$49,Thap!$K$49)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$37,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L37" t="inlineStr">
@@ -25184,7 +25392,7 @@
         </is>
       </c>
       <c r="E38">
-        <f>IF($D$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F38" t="inlineStr">
@@ -25193,12 +25401,12 @@
         </is>
       </c>
       <c r="G38">
-        <f>IF($F$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38">
-        <f>IF($H$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J38" t="inlineStr">
@@ -25207,7 +25415,7 @@
         </is>
       </c>
       <c r="K38">
-        <f>IF($J$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$50))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$38="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$50/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$50,Thap!$K$50)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$38,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L38" t="inlineStr">
@@ -25237,7 +25445,7 @@
         </is>
       </c>
       <c r="E39">
-        <f>IF($D$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F39" t="inlineStr">
@@ -25246,12 +25454,12 @@
         </is>
       </c>
       <c r="G39">
-        <f>IF($F$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39">
-        <f>IF($H$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J39" t="inlineStr">
@@ -25260,7 +25468,7 @@
         </is>
       </c>
       <c r="K39">
-        <f>IF($J$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$51))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$39="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$51/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$51,Thap!$K$51)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$39,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L39" t="inlineStr">
@@ -25290,7 +25498,7 @@
         </is>
       </c>
       <c r="E40">
-        <f>IF($D$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F40" t="inlineStr">
@@ -25299,12 +25507,12 @@
         </is>
       </c>
       <c r="G40">
-        <f>IF($F$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40">
-        <f>IF($H$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J40" t="inlineStr">
@@ -25313,7 +25521,7 @@
         </is>
       </c>
       <c r="K40">
-        <f>IF($J$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$52))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$40="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$52/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$52,Thap!$K$52)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$40,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L40" t="inlineStr">
@@ -25343,7 +25551,7 @@
         </is>
       </c>
       <c r="E41">
-        <f>IF($D$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F41" t="inlineStr">
@@ -25352,12 +25560,12 @@
         </is>
       </c>
       <c r="G41">
-        <f>IF($F$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41">
-        <f>IF($H$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J41" t="inlineStr">
@@ -25366,7 +25574,7 @@
         </is>
       </c>
       <c r="K41">
-        <f>IF($J$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$53))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$41="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$53/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$53,Thap!$K$53)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$41,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L41" t="inlineStr">
@@ -25396,7 +25604,7 @@
         </is>
       </c>
       <c r="E42">
-        <f>IF($D$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($D$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($D$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="F42" t="inlineStr">
@@ -25405,12 +25613,12 @@
         </is>
       </c>
       <c r="G42">
-        <f>IF($F$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($F$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($F$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42">
-        <f>IF($H$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($H$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($H$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="J42" t="inlineStr">
@@ -25419,7 +25627,7 @@
         </is>
       </c>
       <c r="K42">
-        <f>IF($J$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))*INDEX(cc_input_bang_xuyen_giap!$B$2:$B$7,MIN(6,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57)),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-Thap!$K$57))+1)))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
+        <f>IF($J$42="","",IF(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))&gt;0,CEILING(Thap!$J$57/(INDEX(cc_input_vu_khi!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))*IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),INDEX(cc_input_bang_danh_noc!$B$2:$B$8,MIN(7,MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))+1))),INDEX(cc_input_bang_xuyen_giap!$B$2:$B$8,MIN(7,MAX(1,IF(INDEX(cc_input_vu_khi_suy_ra!$B$2:$B$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0)),MAX(1,2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57))),2-(INDEX(cc_input_vu_khi!$C$2:$C$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0))-IF(INDEX(cc_input_vu_khi!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi!$A$2:$A$11,0)),Thap!$N$57,Thap!$K$57)))+1))))*INDEX(cc_input_vu_khi_suy_ra!$D$2:$D$11,MATCH($J$42,cc_input_vu_khi_suy_ra!$A$2:$A$11,0))),1),""))</f>
         <v/>
       </c>
       <c r="L42" t="inlineStr">
@@ -25435,7 +25643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25546,7 +25754,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>2.721315755988609</v>
+        <v>3.029381260557367</v>
       </c>
       <c r="G2" t="n">
         <v>1.477624011502516</v>
@@ -25593,7 +25801,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.378185076399653</v>
+        <v>3.760611220002248</v>
       </c>
       <c r="G3" t="n">
         <v>1.834291876347951</v>
@@ -25640,7 +25848,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>3.941215922466261</v>
+        <v>4.387379756669289</v>
       </c>
       <c r="G4" t="n">
         <v>2.14000718907261</v>
@@ -25687,7 +25895,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.598085242877305</v>
+        <v>5.118609716114171</v>
       </c>
       <c r="G5" t="n">
         <v>2.496675053918044</v>
@@ -25734,7 +25942,7 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>5.161116088943914</v>
+        <v>5.745378252781214</v>
       </c>
       <c r="G6" t="n">
         <v>2.802390366642703</v>
@@ -25781,7 +25989,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.548638458315877</v>
+        <v>4.723586091328027</v>
       </c>
       <c r="G7" t="n">
         <v>0.8152408339324227</v>
@@ -25828,7 +26036,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.685798072894848</v>
+        <v>5.904482614160034</v>
       </c>
       <c r="G8" t="n">
         <v>1.019051042415528</v>
@@ -25875,7 +26083,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>6.538667783829075</v>
+        <v>6.790155006284038</v>
       </c>
       <c r="G9" t="n">
         <v>1.171908698777858</v>
@@ -25922,7 +26130,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.675827398408043</v>
+        <v>7.971051529116045</v>
       </c>
       <c r="G10" t="n">
         <v>1.375718907260963</v>
@@ -25969,7 +26177,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>8.812987012987012</v>
+        <v>9.151948051948052</v>
       </c>
       <c r="G11" t="n">
         <v>1.579529115744069</v>
@@ -26471,7 +26679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26661,7 +26869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -34168,7 +34376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -36574,7 +36782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37408,7 +37616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38086,7 +38294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40048,7 +40256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44506,2164 +44714,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G143"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>anh_can_cu_id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>thu_tu</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>at_x_m</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>at_z_m</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dir_x_m</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dir_z_m</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>routes</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>nguon</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>raw_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ashfield/0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ashfield</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-90.97499999999999</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-56.486</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-0.339</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.9409999999999999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/ashfield.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-90.975,"z":-56.486},"dir":{"x":-0.339,"z":-0.941},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ashfield/1</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ashfield</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-70.77800000000001</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-81.89400000000001</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.8120000000000001</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.584</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/ashfield.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-70.778,"z":-81.894},"dir":{"x":-0.812,"z":-0.584},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>borderbridge/0</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>borderbridge</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-116.811</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-24.154</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-116.811,"z":-24.154},"dir":{"x":0.026,"z":-1.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>borderbridge/1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>borderbridge</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-65.396</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-68.11799999999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-0.723</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.6909999999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-65.396,"z":-68.118},"dir":{"x":-0.723,"z":-0.691},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>borderbridge/2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>borderbridge</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-41.635</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-104.857</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.998</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-41.635,"z":-104.857},"dir":{"x":-0.998,"z":-0.06},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>capital/0</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>capital</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-54.224</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-107.234</v>
-      </c>
-      <c r="F7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/capital.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-54.224,"z":-107.234},"dir":{"x":-1.0,"z":-0.024},"routes":4}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>coralisles/0</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>coralisles</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-109.237</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-57.584</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-109.237,"z":-57.584},"dir":{"x":-0.025,"z":-1.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>coralisles/1</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>coralisles</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="n">
-        <v>-85.541</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-67.465</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.516</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.856</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-85.541,"z":-67.465},"dir":{"x":-0.516,"z":-0.856},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>coralisles/2</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>coralisles</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-55.408</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-107</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-55.408,"z":-107.0},"dir":{"x":-1.0,"z":0.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>dunebreak/0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>dunebreak</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-87.642</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-51.02</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-0.405</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-0.914</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-87.642,"z":-51.02},"dir":{"x":-0.405,"z":-0.914},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>dunebreak/1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>dunebreak</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-70.432</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-66.205</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-0.658</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-0.753</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-70.432,"z":-66.205},"dir":{"x":-0.658,"z":-0.753},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>dunebreak/2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>dunebreak</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-48.921</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-106.964</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.017</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-48.921,"z":-106.964},"dir":{"x":-1.0,"z":-0.017},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>emberridge/0</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>emberridge</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-102.664</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-50.93</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-0.982</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-102.664,"z":-50.93},"dir":{"x":-0.19,"z":-0.982},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>emberridge/1</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>emberridge</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-68.651</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-68.858</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.6879999999999999</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-0.725</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-68.651,"z":-68.858},"dir":{"x":-0.688,"z":-0.725},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>emberridge/2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>emberridge</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-58.279</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-92.937</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.972</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-0.234</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-58.279,"z":-92.937},"dir":{"x":-0.972,"z":-0.234},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>frostpeak/0</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>frostpeak</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>-106.739</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-41.846</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-106.739,"z":-41.846},"dir":{"x":0.008,"z":-1.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>frostpeak/1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>frostpeak</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-72.36199999999999</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-72.36199999999999</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-0.707</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-0.707</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-72.362,"z":-72.362},"dir":{"x":-0.707,"z":-0.707},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>frostpeak/2</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>frostpeak</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-49.756</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-93.084</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-49.756,"z":-93.084},"dir":{"x":-0.98,"z":-0.2},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>greenvale/0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>greenvale</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-81.807</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-65.919</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.598</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.801</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/greenvale.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-81.807,"z":-65.919},"dir":{"x":-0.598,"z":-0.801},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>greenvale/1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>greenvale</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-47.677</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-94.29600000000001</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.957</v>
-      </c>
-      <c r="G21" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/greenvale.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-47.677,"z":-94.296},"dir":{"x":-0.957,"z":-0.29},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>hydrodam/0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>hydrodam</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-68.33799999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-57.064</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.604</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.797</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/hydrodam.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-68.338,"z":-57.064},"dir":{"x":-0.604,"z":-0.797},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>hydrodam/1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>hydrodam</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>-52.951</v>
-      </c>
-      <c r="E23" t="n">
-        <v>-104.629</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-0.996</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.091</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/hydrodam.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-52.951,"z":-104.629},"dir":{"x":-0.996,"z":-0.091},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ironport/0</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ironport</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>-92.798</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-50.717</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-0.246</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-0.969</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-92.798,"z":-50.717},"dir":{"x":-0.246,"z":-0.969},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>ironport/1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ironport</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-71.315</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-72.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-0.766</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-0.643</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-71.315,"z":-72.2},"dir":{"x":-0.766,"z":-0.643},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>ironport/2</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ironport</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-48.669</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-98.61199999999999</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.986</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.164</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-48.669,"z":-98.612},"dir":{"x":-0.986,"z":-0.164},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>junglepass/0</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>junglepass</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-90.337</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-57.233</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-0.301</v>
-      </c>
-      <c r="G27" t="n">
-        <v>-0.954</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-90.337,"z":-57.233},"dir":{"x":-0.301,"z":-0.954},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>junglepass/1</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>junglepass</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-69.256</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-72.42100000000001</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-0.698</v>
-      </c>
-      <c r="G28" t="n">
-        <v>-0.716</v>
-      </c>
-      <c r="H28" t="n">
-        <v>2</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-69.256,"z":-72.421},"dir":{"x":-0.698,"z":-0.716},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>junglepass/2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>junglepass</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-51.535</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-86.42</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-0.952</v>
-      </c>
-      <c r="G29" t="n">
-        <v>-0.307</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-51.535,"z":-86.42},"dir":{"x":-0.952,"z":-0.307},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>landingbeach/0</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>landingbeach</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>-103.472</v>
-      </c>
-      <c r="E30" t="n">
-        <v>-31.79</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-0.271</v>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.963</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-103.472,"z":-31.79},"dir":{"x":-0.271,"z":-0.963},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>landingbeach/1</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>landingbeach</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>-59.058</v>
-      </c>
-      <c r="E31" t="n">
-        <v>-67.801</v>
-      </c>
-      <c r="F31" t="n">
-        <v>-0.523</v>
-      </c>
-      <c r="G31" t="n">
-        <v>-0.853</v>
-      </c>
-      <c r="H31" t="n">
-        <v>2</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-59.058,"z":-67.801},"dir":{"x":-0.523,"z":-0.853},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>landingbeach/2</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>landingbeach</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>-35.801</v>
-      </c>
-      <c r="E32" t="n">
-        <v>-100.78</v>
-      </c>
-      <c r="F32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-35.801,"z":-100.78},"dir":{"x":-1.0,"z":0.025},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>launchsite/0</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>launchsite</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-73.45</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-66.065</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-0.658</v>
-      </c>
-      <c r="G33" t="n">
-        <v>-0.753</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/launchsite.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-73.45,"z":-66.065},"dir":{"x":-0.658,"z":-0.753},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>launchsite/1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>launchsite</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-57.546</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-102.554</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-0.984</v>
-      </c>
-      <c r="G34" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/launchsite.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-57.546,"z":-102.554},"dir":{"x":-0.984,"z":-0.179},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>metrocity/0</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>metrocity</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-96.42100000000001</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-55.611</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-0.236</v>
-      </c>
-      <c r="G35" t="n">
-        <v>-0.972</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-96.421,"z":-55.611},"dir":{"x":-0.236,"z":-0.972},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>metrocity/1</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>metrocity</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="n">
-        <v>-63.694</v>
-      </c>
-      <c r="E36" t="n">
-        <v>-62.349</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.723</v>
-      </c>
-      <c r="G36" t="n">
-        <v>-0.6909999999999999</v>
-      </c>
-      <c r="H36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-63.694,"z":-62.349},"dir":{"x":-0.723,"z":-0.691},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>metrocity/2</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>metrocity</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-50.107</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-92.721</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-50.107,"z":-92.721},"dir":{"x":-1.0,"z":0.003},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>redrock/0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>redrock</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-119</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-31.629</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-119.0,"z":-31.629},"dir":{"x":0.0,"z":-1.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>redrock/1</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>redrock</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-57.983</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-58.867</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.754</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-0.657</v>
-      </c>
-      <c r="H39" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-57.983,"z":-58.867},"dir":{"x":-0.754,"z":-0.657},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>redrock/2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>redrock</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2</v>
-      </c>
-      <c r="D40" t="n">
-        <v>-67.372</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-117.463</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-0.982</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-67.372,"z":-117.463},"dir":{"x":-0.982,"z":0.19},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>rustyard/0</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>rustyard</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-93.34699999999999</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-56.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-0.258</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-0.966</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-93.347,"z":-56.8},"dir":{"x":-0.258,"z":-0.966},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>rustyard/1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>rustyard</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-69.797</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-65.994</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-0.702</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-0.712</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-69.797,"z":-65.994},"dir":{"x":-0.702,"z":-0.712},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>rustyard/2</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>rustyard</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>2</v>
-      </c>
-      <c r="D43" t="n">
-        <v>-44.359</v>
-      </c>
-      <c r="E43" t="n">
-        <v>-105</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-44.359,"z":-105.0},"dir":{"x":-1.0,"z":0.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>saltflat/0</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>saltflat</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-92.25700000000001</v>
-      </c>
-      <c r="E44" t="n">
-        <v>-41.313</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-0.976</v>
-      </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-92.257,"z":-41.313},"dir":{"x":-0.22,"z":-0.976},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>saltflat/1</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>saltflat</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="n">
-        <v>-68.68600000000001</v>
-      </c>
-      <c r="E45" t="n">
-        <v>-68.68600000000001</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-0.707</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-0.707</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-68.686,"z":-68.686},"dir":{"x":-0.707,"z":-0.707},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>saltflat/2</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>saltflat</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>2</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-48.771</v>
-      </c>
-      <c r="E46" t="n">
-        <v>-98.628</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-0.986</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-0.164</v>
-      </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-48.771,"z":-98.628},"dir":{"x":-0.986,"z":-0.164},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>skyhold/0</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>skyhold</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>-81.69</v>
-      </c>
-      <c r="E47" t="n">
-        <v>-70.42100000000001</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-0.5639999999999999</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-0.825</v>
-      </c>
-      <c r="H47" t="n">
-        <v>2</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/skyhold.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-81.69,"z":-70.421},"dir":{"x":-0.564,"z":-0.825},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>swamp/0</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>swamp</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-107</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-49.284</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-107.0,"z":-49.284},"dir":{"x":0.0,"z":-1.0},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>swamp/1</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>swamp</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-82.364</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-61.767</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.536</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.844</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-82.364,"z":-61.767},"dir":{"x":-0.536,"z":-0.844},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>swamp/2</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>swamp</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-56.01</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-106.638</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.984</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-0.179</v>
-      </c>
-      <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-56.01,"z":-106.638},"dir":{"x":-0.984,"z":-0.179},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>whiteout/0</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>whiteout</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>-102.67</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-53.364</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-0.165</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-0.986</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[0]</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-102.67,"z":-53.364},"dir":{"x":-0.165,"z":-0.986},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>whiteout/1</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>whiteout</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-71.431</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-71.497</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.722</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-0.6919999999999999</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[1]</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-71.431,"z":-71.497},"dir":{"x":-0.722,"z":-0.692},"routes":2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>whiteout/2</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>whiteout</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-49</v>
-      </c>
-      <c r="E53" t="n">
-        <v>-99.364</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.989</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[2]</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>{"at":{"x":-49.0,"z":-99.364},"dir":{"x":-0.989,"z":-0.15},"routes":1}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -47738,6 +45788,2164 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>anh_can_cu_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>thu_tu</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>at_x_m</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>at_z_m</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dir_x_m</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dir_z_m</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>routes</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>nguon</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>raw_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ashfield/0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ashfield</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-90.97499999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-56.486</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.339</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.9409999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/ashfield.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-90.975,"z":-56.486},"dir":{"x":-0.339,"z":-0.941},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ashfield/1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ashfield</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-70.77800000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-81.89400000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.8120000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.584</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/ashfield.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-70.778,"z":-81.894},"dir":{"x":-0.812,"z":-0.584},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>borderbridge/0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>borderbridge</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-116.811</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-24.154</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-116.811,"z":-24.154},"dir":{"x":0.026,"z":-1.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>borderbridge/1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>borderbridge</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-65.396</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-68.11799999999999</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.723</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.6909999999999999</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-65.396,"z":-68.118},"dir":{"x":-0.723,"z":-0.691},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>borderbridge/2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>borderbridge</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-41.635</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-104.857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.998</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/borderbridge.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-41.635,"z":-104.857},"dir":{"x":-0.998,"z":-0.06},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>capital/0</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>capital</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-54.224</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-107.234</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/capital.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-54.224,"z":-107.234},"dir":{"x":-1.0,"z":-0.024},"routes":4}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>coralisles/0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>coralisles</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-109.237</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-57.584</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-109.237,"z":-57.584},"dir":{"x":-0.025,"z":-1.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>coralisles/1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>coralisles</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-85.541</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-67.465</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.516</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.856</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-85.541,"z":-67.465},"dir":{"x":-0.516,"z":-0.856},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>coralisles/2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>coralisles</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-55.408</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-107</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/coralisles.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-55.408,"z":-107.0},"dir":{"x":-1.0,"z":0.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>dunebreak/0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dunebreak</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-87.642</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-51.02</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.405</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.914</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-87.642,"z":-51.02},"dir":{"x":-0.405,"z":-0.914},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dunebreak/1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>dunebreak</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-70.432</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-66.205</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.753</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-70.432,"z":-66.205},"dir":{"x":-0.658,"z":-0.753},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>dunebreak/2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dunebreak</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-48.921</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-106.964</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/dunebreak.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-48.921,"z":-106.964},"dir":{"x":-1.0,"z":-0.017},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>emberridge/0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>emberridge</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-102.664</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-50.93</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0.982</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-102.664,"z":-50.93},"dir":{"x":-0.19,"z":-0.982},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>emberridge/1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>emberridge</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-68.651</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-68.858</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.6879999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0.725</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-68.651,"z":-68.858},"dir":{"x":-0.688,"z":-0.725},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>emberridge/2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>emberridge</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-58.279</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-92.937</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.972</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.234</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/emberridge.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-58.279,"z":-92.937},"dir":{"x":-0.972,"z":-0.234},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>frostpeak/0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>frostpeak</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-106.739</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-41.846</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-106.739,"z":-41.846},"dir":{"x":0.008,"z":-1.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>frostpeak/1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>frostpeak</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-72.36199999999999</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-72.36199999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.707</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.707</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-72.362,"z":-72.362},"dir":{"x":-0.707,"z":-0.707},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>frostpeak/2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>frostpeak</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-49.756</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-93.084</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/frostpeak.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-49.756,"z":-93.084},"dir":{"x":-0.98,"z":-0.2},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>greenvale/0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>greenvale</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-81.807</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-65.919</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.598</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.801</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/greenvale.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-81.807,"z":-65.919},"dir":{"x":-0.598,"z":-0.801},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>greenvale/1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>greenvale</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-47.677</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-94.29600000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.957</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/greenvale.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-47.677,"z":-94.296},"dir":{"x":-0.957,"z":-0.29},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>hydrodam/0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>hydrodam</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-68.33799999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-57.064</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.604</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.797</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/hydrodam.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-68.338,"z":-57.064},"dir":{"x":-0.604,"z":-0.797},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>hydrodam/1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>hydrodam</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-52.951</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-104.629</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.996</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/hydrodam.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-52.951,"z":-104.629},"dir":{"x":-0.996,"z":-0.091},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ironport/0</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ironport</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-92.798</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-50.717</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.246</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.969</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-92.798,"z":-50.717},"dir":{"x":-0.246,"z":-0.969},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ironport/1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ironport</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-71.315</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-72.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.766</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.643</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-71.315,"z":-72.2},"dir":{"x":-0.766,"z":-0.643},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ironport/2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ironport</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-48.669</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-98.61199999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.986</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.164</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/ironport.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-48.669,"z":-98.612},"dir":{"x":-0.986,"z":-0.164},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>junglepass/0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>junglepass</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-90.337</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-57.233</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-0.301</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.954</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-90.337,"z":-57.233},"dir":{"x":-0.301,"z":-0.954},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>junglepass/1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>junglepass</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-69.256</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-72.42100000000001</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.698</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.716</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-69.256,"z":-72.421},"dir":{"x":-0.698,"z":-0.716},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>junglepass/2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>junglepass</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-51.535</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-86.42</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.952</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-0.307</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/junglepass.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-51.535,"z":-86.42},"dir":{"x":-0.952,"z":-0.307},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>landingbeach/0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>landingbeach</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-103.472</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-31.79</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-0.271</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.963</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-103.472,"z":-31.79},"dir":{"x":-0.271,"z":-0.963},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>landingbeach/1</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>landingbeach</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-59.058</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-67.801</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-0.523</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-0.853</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-59.058,"z":-67.801},"dir":{"x":-0.523,"z":-0.853},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>landingbeach/2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>landingbeach</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-35.801</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-100.78</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/landingbeach.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-35.801,"z":-100.78},"dir":{"x":-1.0,"z":0.025},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>launchsite/0</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>launchsite</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-73.45</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-66.065</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-0.658</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-0.753</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/launchsite.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-73.45,"z":-66.065},"dir":{"x":-0.658,"z":-0.753},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>launchsite/1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>launchsite</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-57.546</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-102.554</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-0.984</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/launchsite.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-57.546,"z":-102.554},"dir":{"x":-0.984,"z":-0.179},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>metrocity/0</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>metrocity</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-96.42100000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-55.611</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.236</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.972</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-96.421,"z":-55.611},"dir":{"x":-0.236,"z":-0.972},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>metrocity/1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>metrocity</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-63.694</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-62.349</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.723</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.6909999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-63.694,"z":-62.349},"dir":{"x":-0.723,"z":-0.691},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>metrocity/2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>metrocity</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-50.107</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-92.721</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/metrocity.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-50.107,"z":-92.721},"dir":{"x":-1.0,"z":0.003},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>redrock/0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>redrock</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-119</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-31.629</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-119.0,"z":-31.629},"dir":{"x":0.0,"z":-1.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>redrock/1</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>redrock</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-57.983</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-58.867</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.754</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.657</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-57.983,"z":-58.867},"dir":{"x":-0.754,"z":-0.657},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>redrock/2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>redrock</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-67.372</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-117.463</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-0.982</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/redrock.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-67.372,"z":-117.463},"dir":{"x":-0.982,"z":0.19},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>rustyard/0</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>rustyard</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>-93.34699999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-56.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.258</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.966</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-93.347,"z":-56.8},"dir":{"x":-0.258,"z":-0.966},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>rustyard/1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>rustyard</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>-69.797</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-65.994</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-0.702</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.712</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-69.797,"z":-65.994},"dir":{"x":-0.702,"z":-0.712},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>rustyard/2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>rustyard</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>-44.359</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-105</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/rustyard.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-44.359,"z":-105.0},"dir":{"x":-1.0,"z":0.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>saltflat/0</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>saltflat</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-92.25700000000001</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-41.313</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.976</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-92.257,"z":-41.313},"dir":{"x":-0.22,"z":-0.976},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>saltflat/1</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>saltflat</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>-68.68600000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-68.68600000000001</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.707</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.707</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-68.686,"z":-68.686},"dir":{"x":-0.707,"z":-0.707},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>saltflat/2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>saltflat</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-48.771</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-98.628</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.986</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-0.164</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/saltflat.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-48.771,"z":-98.628},"dir":{"x":-0.986,"z":-0.164},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>skyhold/0</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>skyhold</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>-81.69</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-70.42100000000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.5639999999999999</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.825</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/skyhold.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-81.69,"z":-70.421},"dir":{"x":-0.564,"z":-0.825},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>swamp/0</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>swamp</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>-107</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-49.284</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-107.0,"z":-49.284},"dir":{"x":0.0,"z":-1.0},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>swamp/1</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>swamp</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-82.364</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-61.767</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.536</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.844</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-82.364,"z":-61.767},"dir":{"x":-0.536,"z":-0.844},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>swamp/2</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>swamp</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-56.01</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-106.638</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.984</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-0.179</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/swamp.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-56.01,"z":-106.638},"dir":{"x":-0.984,"z":-0.179},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>whiteout/0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>whiteout</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-102.67</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-53.364</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-0.986</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[0]</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-102.67,"z":-53.364},"dir":{"x":-0.165,"z":-0.986},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>whiteout/1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>whiteout</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-71.431</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-71.497</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-0.722</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.6919999999999999</v>
+      </c>
+      <c r="H52" t="n">
+        <v>2</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[1]</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-71.431,"z":-71.497},"dir":{"x":-0.722,"z":-0.692},"routes":2}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>whiteout/2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>whiteout</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>-49</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-99.364</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.989</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/UI/Bases/whiteout.json: arrows[2]</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>{"at":{"x":-49.0,"z":-99.364},"dir":{"x":-0.989,"z":-0.15},"routes":1}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J53"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -19269,7 +19269,7 @@
         <v>457</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -22087,10 +22087,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.6400000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>60.05675368898979</v>
+        <v>71.41884222474461</v>
       </c>
       <c r="G25" t="n">
         <v>328.4901960784314</v>
@@ -22159,10 +22159,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.6400000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="F26" t="n">
-        <v>123.5423830007917</v>
+        <v>134.9044715365465</v>
       </c>
       <c r="G26" t="n">
         <v>328.4901960784314</v>
@@ -22231,7 +22231,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.6400000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="F27" t="n">
         <v>51.67730052048679</v>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -525,7 +525,7 @@
     <col width="9" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="13" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
     <col width="24" customWidth="1" min="36" max="36"/>
     <col width="16" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
@@ -559,9 +559,9 @@
     <col width="20" customWidth="1" min="66" max="66"/>
     <col width="15" customWidth="1" min="67" max="67"/>
     <col width="15" customWidth="1" min="68" max="68"/>
-    <col width="9" customWidth="1" min="69" max="69"/>
-    <col width="24" customWidth="1" min="70" max="70"/>
-    <col width="17" customWidth="1" min="71" max="71"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
+    <col width="16" customWidth="1" min="70" max="70"/>
+    <col width="16" customWidth="1" min="71" max="71"/>
     <col width="8" customWidth="1" min="72" max="72"/>
     <col width="14" customWidth="1" min="73" max="73"/>
     <col width="13" customWidth="1" min="74" max="74"/>
@@ -1498,15 +1498,19 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>aa_gun_tower</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT2" t="n">
         <v>2</v>
       </c>
@@ -1728,15 +1732,19 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT3" t="n">
         <v>2</v>
       </c>
@@ -1969,17 +1977,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>aa_turret</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>giam_dps_giu_mau</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2188,15 +2196,19 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>aa_turret</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY5" t="inlineStr">
         <is>
           <t>aa_turret_b</t>
@@ -2387,15 +2399,19 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>aircraft_hangar</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT6" t="n">
         <v>2</v>
       </c>
@@ -2637,15 +2653,19 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>atgm_tower</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT7" t="n">
         <v>2</v>
       </c>
@@ -2874,15 +2894,19 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>atgm_tower</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY8" t="inlineStr">
         <is>
           <t>atgm_tower_b</t>
@@ -3069,15 +3093,19 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>atgm_tower</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY9" t="inlineStr">
         <is>
           <t>atgm_tower_a</t>
@@ -3256,15 +3284,19 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>barrage_balloon</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT10" t="n">
         <v>0</v>
       </c>
@@ -3476,15 +3508,19 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>blast_wall</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT11" t="n">
         <v>3</v>
       </c>
@@ -3693,15 +3729,19 @@
       <c r="BP12" t="inlineStr"/>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>bulwark_post</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT12" t="n">
         <v>1</v>
       </c>
@@ -3917,15 +3957,19 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>bunker_shelter_tower</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT13" t="n">
         <v>3</v>
       </c>
@@ -4143,15 +4187,19 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>c_ram</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT14" t="n">
         <v>1</v>
       </c>
@@ -4379,15 +4427,19 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>c_ram</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY15" t="inlineStr">
         <is>
           <t>c_ram_a</t>
@@ -4571,15 +4623,19 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>c_ram</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY16" t="inlineStr">
         <is>
           <t>c_ram_b</t>
@@ -4755,15 +4811,19 @@
       <c r="BP17" t="inlineStr"/>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>coastal_battery</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BU17" t="n">
         <v>4</v>
       </c>
@@ -4996,15 +5056,19 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>cp_relay</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT18" t="n">
         <v>1</v>
       </c>
@@ -5232,15 +5296,19 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT19" t="n">
         <v>2</v>
       </c>
@@ -5474,15 +5542,19 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY20" t="inlineStr">
         <is>
           <t>drone_hangar_a</t>
@@ -5669,15 +5741,19 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>drone_hangar</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY21" t="inlineStr">
         <is>
           <t>drone_hangar_b</t>
@@ -5856,15 +5932,19 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>drone_net_tower</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT22" t="n">
         <v>0</v>
       </c>
@@ -6075,15 +6155,19 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>ew_tower</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT23" t="n">
         <v>1</v>
       </c>
@@ -6310,15 +6394,19 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>ew_tower</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY24" t="inlineStr">
         <is>
           <t>ew_tower_a</t>
@@ -6503,15 +6591,19 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>ew_tower</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY25" t="inlineStr">
         <is>
           <t>ew_tower_b</t>
@@ -6660,8 +6752,10 @@
       <c r="AH26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="n">
-        <v>0</v>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -6698,15 +6792,19 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>flare_searchlight_tower</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT26" t="n">
         <v>1</v>
       </c>
@@ -6894,8 +6992,10 @@
       <c r="AH27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="n">
-        <v>0</v>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -6932,15 +7032,19 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>flare_tower</t>
-        </is>
-      </c>
-      <c r="BS27" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT27" t="n">
         <v>1</v>
       </c>
@@ -7157,15 +7261,19 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="BS28" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT28" t="n">
         <v>1</v>
       </c>
@@ -7399,15 +7507,19 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY29" t="inlineStr">
         <is>
           <t>guard_tower_b</t>
@@ -7597,15 +7709,19 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>guard_tower</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY30" t="inlineStr">
         <is>
           <t>guard_tower_a</t>
@@ -7788,15 +7904,19 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>gun_turret</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS31" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT31" t="n">
         <v>3</v>
       </c>
@@ -8021,15 +8141,19 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>gun_turret</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS32" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY32" t="inlineStr">
         <is>
           <t>gun_turret_b</t>
@@ -8216,15 +8340,19 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>gun_turret</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS33" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY33" t="inlineStr">
         <is>
           <t>gun_turret_a</t>
@@ -8403,15 +8531,19 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>heavy_turret</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS34" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BU34" t="n">
         <v>4</v>
       </c>
@@ -8649,15 +8781,19 @@
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
         <is>
-          <t>heavy_turret</t>
-        </is>
-      </c>
-      <c r="BS35" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS35" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY35" t="inlineStr">
         <is>
           <t>heavy_turret_b</t>
@@ -8842,15 +8978,19 @@
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
         <is>
-          <t>heavy_turret</t>
-        </is>
-      </c>
-      <c r="BS36" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS36" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY36" t="inlineStr">
         <is>
           <t>heavy_turret_a</t>
@@ -9033,15 +9173,19 @@
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>laser_ad_station</t>
-        </is>
-      </c>
-      <c r="BS37" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS37" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT37" t="n">
         <v>1</v>
       </c>
@@ -9278,15 +9422,19 @@
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
         <is>
-          <t>laser_ad_station</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS38" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="CE38" t="inlineStr">
         <is>
           <t>laser_ad_station</t>
@@ -9455,15 +9603,19 @@
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>manpads_tower</t>
-        </is>
-      </c>
-      <c r="BS39" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS39" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT39" t="n">
         <v>1</v>
       </c>
@@ -9687,17 +9839,17 @@
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>Starter</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>mg_bunker</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>giam_dps_giu_mau</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BU40" t="n">
@@ -9941,17 +10093,17 @@
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>mg_bunker</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>giam_dps_giu_mau</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
@@ -10160,17 +10312,17 @@
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>mg_bunker</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>giam_dps_giu_mau</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
@@ -10354,15 +10506,19 @@
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>missile_battery</t>
-        </is>
-      </c>
-      <c r="BS43" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS43" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT43" t="n">
         <v>1</v>
       </c>
@@ -10590,15 +10746,19 @@
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
         <is>
-          <t>missile_battery</t>
-        </is>
-      </c>
-      <c r="BS44" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS44" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY44" t="inlineStr">
         <is>
           <t>missile_battery_b</t>
@@ -10793,15 +10953,19 @@
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>missile_battery</t>
-        </is>
-      </c>
-      <c r="BS45" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY45" t="inlineStr">
         <is>
           <t>missile_battery_a</t>
@@ -10980,15 +11144,19 @@
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>one_shot_atgm_tower</t>
-        </is>
-      </c>
-      <c r="BS46" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT46" t="n">
         <v>2</v>
       </c>
@@ -11210,15 +11378,19 @@
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
         <is>
-          <t>recoilless_gun_tower</t>
-        </is>
-      </c>
-      <c r="BS47" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS47" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT47" t="n">
         <v>1</v>
       </c>
@@ -11440,15 +11612,19 @@
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
-          <t>rocket_turret</t>
-        </is>
-      </c>
-      <c r="BS48" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS48" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT48" t="n">
         <v>1</v>
       </c>
@@ -11673,15 +11849,19 @@
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>rocket_turret</t>
-        </is>
-      </c>
-      <c r="BS49" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS49" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY49" t="inlineStr">
         <is>
           <t>rocket_turret_a</t>
@@ -11868,15 +12048,19 @@
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
         <is>
-          <t>rocket_turret</t>
-        </is>
-      </c>
-      <c r="BS50" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS50" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY50" t="inlineStr">
         <is>
           <t>rocket_turret_b</t>
@@ -12058,15 +12242,19 @@
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
         <is>
-          <t>shield_tower</t>
-        </is>
-      </c>
-      <c r="BS51" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS51" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT51" t="n">
         <v>2</v>
       </c>
@@ -12299,15 +12487,19 @@
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>shield_tower</t>
-        </is>
-      </c>
-      <c r="BS52" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS52" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BY52" t="inlineStr">
         <is>
           <t>shield_tower_a</t>
@@ -12494,15 +12686,19 @@
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>shield_tower</t>
-        </is>
-      </c>
-      <c r="BS53" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS53" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT53" t="n">
         <v>2</v>
       </c>
@@ -12736,15 +12932,19 @@
       <c r="BP54" t="inlineStr"/>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
         <is>
-          <t>spawn_bastion</t>
-        </is>
-      </c>
-      <c r="BS54" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS54" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BU54" t="n">
         <v>4</v>
       </c>
@@ -12950,15 +13150,19 @@
       <c r="BP55" t="inlineStr"/>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
         <is>
-          <t>super_gun</t>
-        </is>
-      </c>
-      <c r="BS55" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS55" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT55" t="n">
         <v>3</v>
       </c>
@@ -13168,15 +13372,19 @@
       <c r="BP56" t="inlineStr"/>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
         <is>
-          <t>targeting_station</t>
-        </is>
-      </c>
-      <c r="BS56" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS56" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT56" t="n">
         <v>1</v>
       </c>
@@ -13384,15 +13592,19 @@
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>Campaign</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
         <is>
-          <t>vehicle_hangar</t>
-        </is>
-      </c>
-      <c r="BS57" t="inlineStr"/>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
+      <c r="BS57" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
+      </c>
       <c r="BT57" t="n">
         <v>2</v>
       </c>
@@ -16174,8 +16386,8 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -16254,12 +16466,14 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0.75</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2;4;5;6;8;9;10;12;13;14</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -16297,12 +16511,14 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>0.8722</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3;4;6;7;9;10;12;14;15;17</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -16345,12 +16561,14 @@
           <t>repair_bay;logistics_station</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1.0414</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3;5;7;9;11;12;14;16;18;20</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -16393,12 +16611,14 @@
           <t>repair_bay;logistics_station</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1.1887</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4;6;8;10;12;14;16;19;21;23</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -16441,12 +16661,14 @@
           <t>repair_bay;logistics_station;airfield</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1.3554</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NEED_CODE_CHECK</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4;7;9;11;14;16;19;21;24;26</t>
+          <t>NEED_CODE_CHECK</t>
         </is>
       </c>
       <c r="H6" t="n">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -525,7 +525,7 @@
     <col width="9" customWidth="1" min="32" max="32"/>
     <col width="8" customWidth="1" min="33" max="33"/>
     <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="24" customWidth="1" min="36" max="36"/>
     <col width="16" customWidth="1" min="37" max="37"/>
     <col width="15" customWidth="1" min="38" max="38"/>
@@ -559,9 +559,9 @@
     <col width="20" customWidth="1" min="66" max="66"/>
     <col width="15" customWidth="1" min="67" max="67"/>
     <col width="15" customWidth="1" min="68" max="68"/>
-    <col width="16" customWidth="1" min="69" max="69"/>
-    <col width="16" customWidth="1" min="70" max="70"/>
-    <col width="16" customWidth="1" min="71" max="71"/>
+    <col width="9" customWidth="1" min="69" max="69"/>
+    <col width="24" customWidth="1" min="70" max="70"/>
+    <col width="17" customWidth="1" min="71" max="71"/>
     <col width="8" customWidth="1" min="72" max="72"/>
     <col width="14" customWidth="1" min="73" max="73"/>
     <col width="13" customWidth="1" min="74" max="74"/>
@@ -1498,19 +1498,15 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>aa_gun_tower</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="n">
         <v>2</v>
       </c>
@@ -1732,19 +1728,15 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
         <v>2</v>
       </c>
@@ -1977,17 +1969,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>aa_turret</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>giam_dps_giu_mau</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
@@ -2196,19 +2188,15 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>aa_turret</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr"/>
       <c r="BY5" t="inlineStr">
         <is>
           <t>aa_turret_b</t>
@@ -2399,19 +2387,15 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>aircraft_hangar</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr"/>
       <c r="BT6" t="n">
         <v>2</v>
       </c>
@@ -2653,19 +2637,15 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>atgm_tower</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr"/>
       <c r="BT7" t="n">
         <v>2</v>
       </c>
@@ -2894,19 +2874,15 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>atgm_tower</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr"/>
       <c r="BY8" t="inlineStr">
         <is>
           <t>atgm_tower_b</t>
@@ -3093,19 +3069,15 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>atgm_tower</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr"/>
       <c r="BY9" t="inlineStr">
         <is>
           <t>atgm_tower_a</t>
@@ -3284,19 +3256,15 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>barrage_balloon</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr"/>
       <c r="BT10" t="n">
         <v>0</v>
       </c>
@@ -3508,19 +3476,15 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>blast_wall</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr"/>
       <c r="BT11" t="n">
         <v>3</v>
       </c>
@@ -3729,19 +3693,15 @@
       <c r="BP12" t="inlineStr"/>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>bulwark_post</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr"/>
       <c r="BT12" t="n">
         <v>1</v>
       </c>
@@ -3957,19 +3917,15 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>bunker_shelter_tower</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr"/>
       <c r="BT13" t="n">
         <v>3</v>
       </c>
@@ -4187,19 +4143,15 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>c_ram</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr"/>
       <c r="BT14" t="n">
         <v>1</v>
       </c>
@@ -4427,19 +4379,15 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>c_ram</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr"/>
       <c r="BY15" t="inlineStr">
         <is>
           <t>c_ram_a</t>
@@ -4623,19 +4571,15 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>c_ram</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr"/>
       <c r="BY16" t="inlineStr">
         <is>
           <t>c_ram_b</t>
@@ -4811,19 +4755,15 @@
       <c r="BP17" t="inlineStr"/>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>coastal_battery</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr"/>
       <c r="BU17" t="n">
         <v>4</v>
       </c>
@@ -5056,19 +4996,15 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>cp_relay</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr"/>
       <c r="BT18" t="n">
         <v>1</v>
       </c>
@@ -5296,19 +5232,15 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>drone_hangar</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr"/>
       <c r="BT19" t="n">
         <v>2</v>
       </c>
@@ -5542,19 +5474,15 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>drone_hangar</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr"/>
       <c r="BY20" t="inlineStr">
         <is>
           <t>drone_hangar_a</t>
@@ -5741,19 +5669,15 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>drone_hangar</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr"/>
       <c r="BY21" t="inlineStr">
         <is>
           <t>drone_hangar_b</t>
@@ -5932,19 +5856,15 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>drone_net_tower</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr"/>
       <c r="BT22" t="n">
         <v>0</v>
       </c>
@@ -6155,19 +6075,15 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>ew_tower</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr"/>
       <c r="BT23" t="n">
         <v>1</v>
       </c>
@@ -6394,19 +6310,15 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS24" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>ew_tower</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr"/>
       <c r="BY24" t="inlineStr">
         <is>
           <t>ew_tower_a</t>
@@ -6591,19 +6503,15 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>ew_tower</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr"/>
       <c r="BY25" t="inlineStr">
         <is>
           <t>ew_tower_b</t>
@@ -6752,10 +6660,8 @@
       <c r="AH26" t="n">
         <v>0</v>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="AI26" t="n">
+        <v>0</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -6792,19 +6698,15 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS26" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>flare_searchlight_tower</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr"/>
       <c r="BT26" t="n">
         <v>1</v>
       </c>
@@ -6992,10 +6894,8 @@
       <c r="AH27" t="n">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="AI27" t="n">
+        <v>0</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -7032,19 +6932,15 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS27" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>flare_tower</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr"/>
       <c r="BT27" t="n">
         <v>1</v>
       </c>
@@ -7261,19 +7157,15 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS28" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="BS28" t="inlineStr"/>
       <c r="BT28" t="n">
         <v>1</v>
       </c>
@@ -7507,19 +7399,15 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS29" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="BS29" t="inlineStr"/>
       <c r="BY29" t="inlineStr">
         <is>
           <t>guard_tower_b</t>
@@ -7709,19 +7597,15 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS30" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>guard_tower</t>
+        </is>
+      </c>
+      <c r="BS30" t="inlineStr"/>
       <c r="BY30" t="inlineStr">
         <is>
           <t>guard_tower_a</t>
@@ -7904,19 +7788,15 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS31" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>gun_turret</t>
+        </is>
+      </c>
+      <c r="BS31" t="inlineStr"/>
       <c r="BT31" t="n">
         <v>3</v>
       </c>
@@ -8141,19 +8021,15 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS32" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>gun_turret</t>
+        </is>
+      </c>
+      <c r="BS32" t="inlineStr"/>
       <c r="BY32" t="inlineStr">
         <is>
           <t>gun_turret_b</t>
@@ -8340,19 +8216,15 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS33" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>gun_turret</t>
+        </is>
+      </c>
+      <c r="BS33" t="inlineStr"/>
       <c r="BY33" t="inlineStr">
         <is>
           <t>gun_turret_a</t>
@@ -8531,19 +8403,15 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>heavy_turret</t>
+        </is>
+      </c>
+      <c r="BS34" t="inlineStr"/>
       <c r="BU34" t="n">
         <v>4</v>
       </c>
@@ -8781,19 +8649,15 @@
       </c>
       <c r="BQ35" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR35" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS35" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>heavy_turret</t>
+        </is>
+      </c>
+      <c r="BS35" t="inlineStr"/>
       <c r="BY35" t="inlineStr">
         <is>
           <t>heavy_turret_b</t>
@@ -8978,19 +8842,15 @@
       </c>
       <c r="BQ36" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR36" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS36" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>heavy_turret</t>
+        </is>
+      </c>
+      <c r="BS36" t="inlineStr"/>
       <c r="BY36" t="inlineStr">
         <is>
           <t>heavy_turret_a</t>
@@ -9173,19 +9033,15 @@
       </c>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS37" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>laser_ad_station</t>
+        </is>
+      </c>
+      <c r="BS37" t="inlineStr"/>
       <c r="BT37" t="n">
         <v>1</v>
       </c>
@@ -9422,19 +9278,15 @@
       </c>
       <c r="BQ38" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR38" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS38" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>laser_ad_station</t>
+        </is>
+      </c>
+      <c r="BS38" t="inlineStr"/>
       <c r="CE38" t="inlineStr">
         <is>
           <t>laser_ad_station</t>
@@ -9603,19 +9455,15 @@
       </c>
       <c r="BQ39" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR39" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS39" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>manpads_tower</t>
+        </is>
+      </c>
+      <c r="BS39" t="inlineStr"/>
       <c r="BT39" t="n">
         <v>1</v>
       </c>
@@ -9839,17 +9687,17 @@
       </c>
       <c r="BQ40" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Starter</t>
         </is>
       </c>
       <c r="BR40" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>mg_bunker</t>
         </is>
       </c>
       <c r="BS40" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>giam_dps_giu_mau</t>
         </is>
       </c>
       <c r="BU40" t="n">
@@ -10093,17 +9941,17 @@
       </c>
       <c r="BQ41" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR41" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>mg_bunker</t>
         </is>
       </c>
       <c r="BS41" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>giam_dps_giu_mau</t>
         </is>
       </c>
       <c r="BY41" t="inlineStr">
@@ -10312,17 +10160,17 @@
       </c>
       <c r="BQ42" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR42" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>mg_bunker</t>
         </is>
       </c>
       <c r="BS42" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>giam_dps_giu_mau</t>
         </is>
       </c>
       <c r="BY42" t="inlineStr">
@@ -10506,19 +10354,15 @@
       </c>
       <c r="BQ43" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS43" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>missile_battery</t>
+        </is>
+      </c>
+      <c r="BS43" t="inlineStr"/>
       <c r="BT43" t="n">
         <v>1</v>
       </c>
@@ -10746,19 +10590,15 @@
       </c>
       <c r="BQ44" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR44" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS44" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>missile_battery</t>
+        </is>
+      </c>
+      <c r="BS44" t="inlineStr"/>
       <c r="BY44" t="inlineStr">
         <is>
           <t>missile_battery_b</t>
@@ -10953,19 +10793,15 @@
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS45" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>missile_battery</t>
+        </is>
+      </c>
+      <c r="BS45" t="inlineStr"/>
       <c r="BY45" t="inlineStr">
         <is>
           <t>missile_battery_a</t>
@@ -11144,19 +10980,15 @@
       </c>
       <c r="BQ46" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR46" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS46" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>one_shot_atgm_tower</t>
+        </is>
+      </c>
+      <c r="BS46" t="inlineStr"/>
       <c r="BT46" t="n">
         <v>2</v>
       </c>
@@ -11378,19 +11210,15 @@
       </c>
       <c r="BQ47" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR47" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS47" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>recoilless_gun_tower</t>
+        </is>
+      </c>
+      <c r="BS47" t="inlineStr"/>
       <c r="BT47" t="n">
         <v>1</v>
       </c>
@@ -11612,19 +11440,15 @@
       </c>
       <c r="BQ48" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR48" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS48" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>rocket_turret</t>
+        </is>
+      </c>
+      <c r="BS48" t="inlineStr"/>
       <c r="BT48" t="n">
         <v>1</v>
       </c>
@@ -11849,19 +11673,15 @@
       </c>
       <c r="BQ49" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR49" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS49" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>rocket_turret</t>
+        </is>
+      </c>
+      <c r="BS49" t="inlineStr"/>
       <c r="BY49" t="inlineStr">
         <is>
           <t>rocket_turret_a</t>
@@ -12048,19 +11868,15 @@
       </c>
       <c r="BQ50" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR50" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS50" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>rocket_turret</t>
+        </is>
+      </c>
+      <c r="BS50" t="inlineStr"/>
       <c r="BY50" t="inlineStr">
         <is>
           <t>rocket_turret_b</t>
@@ -12242,19 +12058,15 @@
       </c>
       <c r="BQ51" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR51" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS51" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>shield_tower</t>
+        </is>
+      </c>
+      <c r="BS51" t="inlineStr"/>
       <c r="BT51" t="n">
         <v>2</v>
       </c>
@@ -12487,19 +12299,15 @@
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS52" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>shield_tower</t>
+        </is>
+      </c>
+      <c r="BS52" t="inlineStr"/>
       <c r="BY52" t="inlineStr">
         <is>
           <t>shield_tower_a</t>
@@ -12686,19 +12494,15 @@
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS53" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>shield_tower</t>
+        </is>
+      </c>
+      <c r="BS53" t="inlineStr"/>
       <c r="BT53" t="n">
         <v>2</v>
       </c>
@@ -12932,19 +12736,15 @@
       <c r="BP54" t="inlineStr"/>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS54" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>spawn_bastion</t>
+        </is>
+      </c>
+      <c r="BS54" t="inlineStr"/>
       <c r="BU54" t="n">
         <v>4</v>
       </c>
@@ -13150,19 +12950,15 @@
       <c r="BP55" t="inlineStr"/>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS55" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>super_gun</t>
+        </is>
+      </c>
+      <c r="BS55" t="inlineStr"/>
       <c r="BT55" t="n">
         <v>3</v>
       </c>
@@ -13372,19 +13168,15 @@
       <c r="BP56" t="inlineStr"/>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS56" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>targeting_station</t>
+        </is>
+      </c>
+      <c r="BS56" t="inlineStr"/>
       <c r="BT56" t="n">
         <v>1</v>
       </c>
@@ -13592,19 +13384,15 @@
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>Campaign</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
-      <c r="BS57" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
-      </c>
+          <t>vehicle_hangar</t>
+        </is>
+      </c>
+      <c r="BS57" t="inlineStr"/>
       <c r="BT57" t="n">
         <v>2</v>
       </c>
@@ -16386,8 +16174,8 @@
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
@@ -16466,14 +16254,12 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F2" t="n">
+        <v>0.75</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>2;4;5;6;8;9;10;12;13;14</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -16511,14 +16297,12 @@
           <t>repair_bay</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F3" t="n">
+        <v>0.8722</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>3;4;6;7;9;10;12;14;15;17</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -16561,14 +16345,12 @@
           <t>repair_bay;logistics_station</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F4" t="n">
+        <v>1.0414</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>3;5;7;9;11;12;14;16;18;20</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -16611,14 +16393,12 @@
           <t>repair_bay;logistics_station</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F5" t="n">
+        <v>1.1887</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>4;6;8;10;12;14;16;19;21;23</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -16661,14 +16441,12 @@
           <t>repair_bay;logistics_station;airfield</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NEED_CODE_CHECK</t>
-        </is>
+      <c r="F6" t="n">
+        <v>1.3554</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>NEED_CODE_CHECK</t>
+          <t>4;7;9;11;14;16;19;21;24;26</t>
         </is>
       </c>
       <c r="H6" t="n">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -1387,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1273</v>
+        <v>1591</v>
       </c>
       <c r="J2" t="n">
-        <v>2800.6</v>
+        <v>3500.2</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -1470,8 +1470,14 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1591</v>
       </c>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr"/>
@@ -1533,7 +1539,7 @@
         </is>
       </c>
       <c r="DA2" t="n">
-        <v>1273</v>
+        <v>1591</v>
       </c>
       <c r="DD2" t="n">
         <v>5</v>
@@ -1581,7 +1587,7 @@
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>{"id":"aa_gun_tower","modelSize":[5.5,5.5,3.2],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1273,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.4,"length":5.0,"width":5.0,"cp":0,"vision":56,"weapon":"bofors_l70","secondary":[],"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"aa_gun_tower","modelSize":[5.5,5.5,3.2],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1591,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.4,"length":5.0,"width":5.0,"cp":0,"vision":56,"weapon":"bofors_l70","secondary":[],"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -1613,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1100</v>
+        <v>1320</v>
       </c>
       <c r="J3" t="n">
-        <v>2420</v>
+        <v>2904</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -1700,8 +1706,14 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1320</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
@@ -1768,7 +1780,7 @@
         </is>
       </c>
       <c r="DA3" t="n">
-        <v>1100</v>
+        <v>1320</v>
       </c>
       <c r="DD3" t="n">
         <v>4.5</v>
@@ -1812,7 +1824,7 @@
       </c>
       <c r="EN3" t="inlineStr">
         <is>
-          <t>{"id":"aa_turret","outgoingDamageMult":1,"rebuildCp":6,"branches":["aa_turret.flak","aa_turret.sam"],"fort":{"size":"Small"},"static":true,"armour":2,"hp":1100,"speed":0,"turnRate":1,"turretTurnRate":200,"radius":2.3,"length":4.5,"width":4.5,"cp":0,"vision":60,"weapon":"tower_flak_30","secondary":[{"weapon":"sam","slot":"missile","aim":"Turret"}],"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"aa_turret","outgoingDamageMult":1,"rebuildCp":6,"branches":["aa_turret.flak","aa_turret.sam"],"fort":{"size":"Small"},"static":true,"armour":2,"hp":1320,"speed":0,"turnRate":1,"turretTurnRate":200,"radius":2.3,"length":4.5,"width":4.5,"cp":0,"vision":60,"weapon":"tower_flak_30","secondary":[{"weapon":"sam","slot":"missile","aim":"Turret"}],"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -1840,10 +1852,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1100</v>
+        <v>1320</v>
       </c>
       <c r="J4" t="n">
-        <v>2420</v>
+        <v>2904</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -1926,6 +1938,12 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="AN4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1320</v>
+      </c>
       <c r="BF4" t="n">
         <v>1</v>
       </c>
@@ -2049,10 +2067,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1100</v>
+        <v>1320</v>
       </c>
       <c r="J5" t="n">
-        <v>2420</v>
+        <v>2904</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -2134,6 +2152,12 @@
         <is>
           <t>doi</t>
         </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1320</v>
       </c>
       <c r="AZ5" t="n">
         <v>64</v>
@@ -2276,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
       <c r="J6" t="n">
-        <v>3960</v>
+        <v>4752</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -2439,7 +2463,7 @@
         </is>
       </c>
       <c r="DA6" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
       <c r="DD6" t="n">
         <v>8</v>
@@ -2494,7 +2518,7 @@
       </c>
       <c r="EN6" t="inlineStr">
         <is>
-          <t>{"id":"aircraft_hangar","rebuildCp":8,"model":"aircraft_hangar","modelSize":[8.0,7.72,5.32],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_heli","recon_drone"],"every":60,"alive":2,"budget":12,"post":30},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"aircraft_hangar","rebuildCp":8,"model":"aircraft_hangar","modelSize":[8.0,7.72,5.32],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":2160,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_heli","recon_drone"],"every":60,"alive":2,"budget":12,"post":30},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -2526,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="J7" t="n">
-        <v>1980</v>
+        <v>2475</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -2586,7 +2610,7 @@
         <v>3.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -2609,8 +2633,20 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>900</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
@@ -2677,7 +2713,7 @@
         </is>
       </c>
       <c r="DA7" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="DD7" t="n">
         <v>4.8</v>
@@ -2687,6 +2723,9 @@
           <t>missile</t>
         </is>
       </c>
+      <c r="DM7" t="n">
+        <v>1.1</v>
+      </c>
       <c r="DO7" t="n">
         <v>2.3</v>
       </c>
@@ -2723,7 +2762,7 @@
       </c>
       <c r="EN7" t="inlineStr">
         <is>
-          <t>{"id":"atgm_tower","rebuildCp":7,"branches":["atgm_tower.top","atgm_tower.multi"],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":900,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.8,"width":4.8,"cp":0,"vision":55,"weapon":"tower_kornet","mainSlot":"missile","deathExplosion":{"damage":90,"radius":6,"delay":0.3,"tier":"Large"}}</t>
+          <t>{"id":"atgm_tower","outgoingDamageMult":1.1,"rebuildCp":7,"branches":["atgm_tower.top","atgm_tower.multi"],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1125,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.8,"width":4.8,"cp":0,"vision":55,"weapon":"tower_kornet","mainSlot":"missile","deathExplosion":{"damage":90,"radius":6,"delay":0.3,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -2751,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="J8" t="n">
-        <v>1980</v>
+        <v>2475</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -2811,7 +2850,7 @@
         <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -2834,8 +2873,20 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
@@ -2946,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>900</v>
+        <v>1125</v>
       </c>
       <c r="J9" t="n">
-        <v>1980</v>
+        <v>2475</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -3006,7 +3057,7 @@
         <v>3.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -3029,8 +3080,20 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1125</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
@@ -3145,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="J10" t="n">
-        <v>800.8</v>
+        <v>921.8</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -3228,8 +3291,14 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>364</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>419</v>
       </c>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
@@ -3283,7 +3352,7 @@
         </is>
       </c>
       <c r="DA10" t="n">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="DD10" t="n">
         <v>4</v>
@@ -3333,7 +3402,7 @@
       </c>
       <c r="EN10" t="inlineStr">
         <is>
-          <t>{"id":"barrage_balloon","modelSize":[9.0,4.0,16.0],"fort":{"size":"Small"},"static":true,"armour":0,"hp":364,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":2.0,"length":4.0,"width":4.0,"cp":0,"vision":1,"weapon":"none","balloon":{"radius":40,"scatter":0.5},"revealAir":45}</t>
+          <t>{"id":"barrage_balloon","modelSize":[9.0,4.0,16.0],"fort":{"size":"Small"},"static":true,"armour":0,"hp":419,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":2.0,"length":4.0,"width":4.0,"cp":0,"vision":1,"weapon":"none","balloon":{"radius":40,"scatter":0.5},"revealAir":45}</t>
         </is>
       </c>
     </row>
@@ -4028,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="J14" t="n">
-        <v>2860</v>
+        <v>3289</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -4115,8 +4184,14 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1495</v>
       </c>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
@@ -4183,7 +4258,7 @@
         </is>
       </c>
       <c r="DA14" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="DD14" t="n">
         <v>5.5</v>
@@ -4224,7 +4299,7 @@
       </c>
       <c r="EN14" t="inlineStr">
         <is>
-          <t>{"id":"c_ram","rebuildCp":5,"branches":["c_ram.centurion","c_ram.dome"],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1300,"speed":0,"turnRate":1,"turretTurnRate":240,"radius":2.5,"length":5.5,"width":5.5,"cp":0,"vision":60,"weapon":"c_ram_gatling","aps":{"radius":35,"charges":4,"recharge":0.6,"rockets":true,"shells":0.3,"burst":0.5},"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"c_ram","rebuildCp":5,"branches":["c_ram.centurion","c_ram.dome"],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1495,"speed":0,"turnRate":1,"turretTurnRate":240,"radius":2.5,"length":5.5,"width":5.5,"cp":0,"vision":60,"weapon":"c_ram_gatling","aps":{"radius":35,"charges":4,"recharge":0.6,"rockets":true,"shells":0.3,"burst":0.5},"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4327,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="J15" t="n">
-        <v>2860</v>
+        <v>3289</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -4339,8 +4414,14 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1495</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
@@ -4446,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1300</v>
+        <v>1495</v>
       </c>
       <c r="J16" t="n">
-        <v>2860</v>
+        <v>3289</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -4531,8 +4612,14 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN16" t="n">
+        <v>1300</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1495</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
@@ -4877,10 +4964,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="J18" t="n">
-        <v>1320</v>
+        <v>1584</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
@@ -4960,8 +5047,14 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>600</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>720</v>
       </c>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -5031,7 +5124,7 @@
         </is>
       </c>
       <c r="DA18" t="n">
-        <v>600</v>
+        <v>720</v>
       </c>
       <c r="DD18" t="n">
         <v>4</v>
@@ -5089,7 +5182,7 @@
       </c>
       <c r="EN18" t="inlineStr">
         <is>
-          <t>{"id":"cp_relay","rebuildCp":6,"towerRole":"cp_income","noBranch":true,"fort":{"size":"Small"},"static":true,"armour":1,"hp":600,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":1.8,"length":4,"width":4,"cp":0,"vision":30,"weapon":"none","relay":{"income":0.1,"second":0.06,"quiet":5},"deathExplosion":{"damage":50,"radius":5,"delay":0.3,"tier":"Large"}}</t>
+          <t>{"id":"cp_relay","rebuildCp":6,"towerRole":"cp_income","noBranch":true,"fort":{"size":"Small"},"static":true,"armour":1,"hp":720,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":1.8,"length":4,"width":4,"cp":0,"vision":30,"weapon":"none","relay":{"income":0.1,"second":0.06,"quiet":5},"deathExplosion":{"damage":50,"radius":5,"delay":0.3,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -5121,10 +5214,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2200</v>
+        <v>2860</v>
       </c>
       <c r="J19" t="n">
-        <v>4840</v>
+        <v>6292</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -5181,7 +5274,7 @@
         <v>3.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -5204,8 +5297,20 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>2860</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr"/>
@@ -5272,7 +5377,7 @@
         </is>
       </c>
       <c r="DA19" t="n">
-        <v>2200</v>
+        <v>2860</v>
       </c>
       <c r="DD19" t="n">
         <v>8</v>
@@ -5287,6 +5392,9 @@
           <t>door_l</t>
         </is>
       </c>
+      <c r="DM19" t="n">
+        <v>1.1</v>
+      </c>
       <c r="DO19" t="n">
         <v>3.6</v>
       </c>
@@ -5323,7 +5431,7 @@
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>{"id":"drone_hangar","rebuildCp":12,"branches":["drone_hangar.lancet","drone_hangar.swarm"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2200,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":60,"weapon":"fpv_hangar","mainSlot":"door_l","mainAim":"Hull","deathExplosion":{"damage":160,"radius":10,"delay":0.4,"tier":"Ultimate"}}</t>
+          <t>{"id":"drone_hangar","outgoingDamageMult":1.1,"rebuildCp":12,"branches":["drone_hangar.lancet","drone_hangar.swarm"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2860,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":60,"weapon":"fpv_hangar","mainSlot":"door_l","mainAim":"Hull","deathExplosion":{"damage":160,"radius":10,"delay":0.4,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -5351,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2200</v>
+        <v>2860</v>
       </c>
       <c r="J20" t="n">
-        <v>4840</v>
+        <v>6292</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -5411,7 +5519,7 @@
         <v>3.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -5434,8 +5542,20 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN20" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>2860</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
@@ -5546,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2200</v>
+        <v>2860</v>
       </c>
       <c r="J21" t="n">
-        <v>4840</v>
+        <v>6292</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -5606,7 +5726,7 @@
         <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -5629,8 +5749,20 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN21" t="n">
+        <v>2200</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2860</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
@@ -5745,10 +5877,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="J22" t="n">
-        <v>800.8</v>
+        <v>921.8</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -5828,8 +5960,14 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>364</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>419</v>
       </c>
       <c r="BH22" t="inlineStr"/>
       <c r="BI22" t="inlineStr"/>
@@ -5877,7 +6015,7 @@
         </is>
       </c>
       <c r="DA22" t="n">
-        <v>364</v>
+        <v>419</v>
       </c>
       <c r="DD22" t="n">
         <v>3</v>
@@ -5932,7 +6070,7 @@
       </c>
       <c r="EN22" t="inlineStr">
         <is>
-          <t>{"id":"drone_net_tower","model":"drone_net_tower","modelSize":[6.0,4.0,4.6],"fort":{"size":"Small"},"static":true,"passable":true,"armour":0,"hp":364,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":1.6,"length":3.0,"width":8.0,"cp":0,"vision":20,"weapon":"net_zap"}</t>
+          <t>{"id":"drone_net_tower","model":"drone_net_tower","modelSize":[6.0,4.0,4.6],"fort":{"size":"Small"},"static":true,"passable":true,"armour":0,"hp":419,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":1.6,"length":3.0,"width":8.0,"cp":0,"vision":20,"weapon":"net_zap"}</t>
         </is>
       </c>
     </row>
@@ -5964,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>800</v>
+        <v>920</v>
       </c>
       <c r="J23" t="n">
-        <v>1760</v>
+        <v>2024</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -6047,8 +6185,14 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN23" t="n">
+        <v>800</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>920</v>
       </c>
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr"/>
@@ -6115,7 +6259,7 @@
         </is>
       </c>
       <c r="DA23" t="n">
-        <v>800</v>
+        <v>920</v>
       </c>
       <c r="DC23" t="n">
         <v>30</v>
@@ -6159,7 +6303,7 @@
       </c>
       <c r="EN23" t="inlineStr">
         <is>
-          <t>{"id":"ew_tower","rebuildCp":3,"branches":["ew_tower.drone","ew_tower.spoof"],"fort":{"size":"Small"},"static":true,"armour":1,"hp":800,"speed":0,"turnRate":1,"turretTurnRate":60,"radius":1.8,"length":4,"width":4,"cp":0,"vision":50,"weapon":"none","jammer":30,"deathExplosion":{"damage":60,"radius":5,"delay":0.3,"tier":"Large"}}</t>
+          <t>{"id":"ew_tower","rebuildCp":3,"branches":["ew_tower.drone","ew_tower.spoof"],"fort":{"size":"Small"},"static":true,"armour":1,"hp":920,"speed":0,"turnRate":1,"turretTurnRate":60,"radius":1.8,"length":4,"width":4,"cp":0,"vision":50,"weapon":"none","jammer":30,"deathExplosion":{"damage":60,"radius":5,"delay":0.3,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -6187,10 +6331,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>800</v>
+        <v>920</v>
       </c>
       <c r="J24" t="n">
-        <v>1760</v>
+        <v>2024</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -6270,8 +6414,14 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN24" t="n">
+        <v>800</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>920</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
@@ -6380,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>800</v>
+        <v>920</v>
       </c>
       <c r="J25" t="n">
-        <v>1760</v>
+        <v>2024</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
@@ -6463,8 +6613,14 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN25" t="n">
+        <v>800</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>920</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
@@ -6583,10 +6739,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="J26" t="n">
-        <v>1001</v>
+        <v>1150.6</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -6670,8 +6826,14 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN26" t="n">
+        <v>455</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>523</v>
       </c>
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr"/>
@@ -6733,7 +6895,7 @@
         </is>
       </c>
       <c r="DA26" t="n">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="DD26" t="n">
         <v>3.6</v>
@@ -6785,7 +6947,7 @@
       </c>
       <c r="EN26" t="inlineStr">
         <is>
-          <t>{"id":"flare_searchlight_tower","model":"flare_searchlight_tower","modelSize":[3.6,3.6,5.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":455,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":1.8,"length":3.6,"width":3.6,"cp":0,"vision":55,"weapon":"illum_flare","flares":{"every":15,"range":40,"radius":25,"seconds":15},"deathExplosion":{"damage":25,"radius":4,"delay":0.2,"tier":"Large"}}</t>
+          <t>{"id":"flare_searchlight_tower","model":"flare_searchlight_tower","modelSize":[3.6,3.6,5.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":523,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":1.8,"length":3.6,"width":3.6,"cp":0,"vision":55,"weapon":"illum_flare","flares":{"every":15,"range":40,"radius":25,"seconds":15},"deathExplosion":{"damage":25,"radius":4,"delay":0.2,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -6817,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="J27" t="n">
-        <v>1001</v>
+        <v>1150.6</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -6904,8 +7066,14 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN27" t="n">
+        <v>455</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>523</v>
       </c>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr"/>
@@ -6967,7 +7135,7 @@
         </is>
       </c>
       <c r="DA27" t="n">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="DD27" t="n">
         <v>3.6</v>
@@ -7014,7 +7182,7 @@
       </c>
       <c r="EN27" t="inlineStr">
         <is>
-          <t>{"id":"flare_tower","modelSize":[3.6,3.6,5.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":455,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":1.8,"length":3.6,"width":3.6,"cp":0,"vision":60,"weapon":"illum_flare","flares":{"every":15,"range":40,"radius":30,"seconds":15},"deathExplosion":{"damage":30,"radius":4,"delay":0.2,"tier":"Large"}}</t>
+          <t>{"id":"flare_tower","modelSize":[3.6,3.6,5.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":523,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":1.8,"length":3.6,"width":3.6,"cp":0,"vision":60,"weapon":"illum_flare","flares":{"every":15,"range":40,"radius":30,"seconds":15},"deathExplosion":{"damage":30,"radius":4,"delay":0.2,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -7046,10 +7214,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="J28" t="n">
-        <v>1540</v>
+        <v>1848</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -7106,7 +7274,7 @@
         <v>3.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -7129,8 +7297,20 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN28" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>840</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.08</v>
       </c>
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr"/>
@@ -7197,10 +7377,13 @@
         </is>
       </c>
       <c r="DA28" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="DD28" t="n">
         <v>3.5</v>
+      </c>
+      <c r="DM28" t="n">
+        <v>1.08</v>
       </c>
       <c r="DO28" t="n">
         <v>1.8</v>
@@ -7248,7 +7431,7 @@
       </c>
       <c r="EN28" t="inlineStr">
         <is>
-          <t>{"id":"guard_tower","rebuildCp":5,"branches":["guard_tower.watch","guard_tower.nest"],"fort":{"size":"Small"},"static":true,"armour":1,"hp":700,"speed":0,"turnRate":1,"turretTurnRate":200,"radius":1.8,"length":3.5,"width":3.5,"cp":0,"vision":60,"revealStealth":true,"towerRangeAura":{"radius":25,"range":0.1},"weapon":"tower_hmg","secondary":[],"deathExplosion":{"damage":60,"radius":5,"delay":0.3,"tier":"Large"}}</t>
+          <t>{"id":"guard_tower","outgoingDamageMult":1.08,"rebuildCp":5,"branches":["guard_tower.watch","guard_tower.nest"],"fort":{"size":"Small"},"static":true,"armour":1,"hp":840,"speed":0,"turnRate":1,"turretTurnRate":200,"radius":1.8,"length":3.5,"width":3.5,"cp":0,"vision":60,"revealStealth":true,"towerRangeAura":{"radius":25,"range":0.1},"weapon":"tower_hmg","secondary":[],"deathExplosion":{"damage":60,"radius":5,"delay":0.3,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -7276,10 +7459,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="J29" t="n">
-        <v>1540</v>
+        <v>1848</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -7336,7 +7519,7 @@
         <v>3.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -7359,8 +7542,20 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN29" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>840</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.08</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
@@ -7474,10 +7669,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="J30" t="n">
-        <v>1540</v>
+        <v>1848</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -7534,7 +7729,7 @@
         <v>3.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -7557,8 +7752,20 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN30" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>840</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.08</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
@@ -7677,10 +7884,10 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="J31" t="n">
-        <v>3960</v>
+        <v>4950</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
@@ -7737,7 +7944,7 @@
         <v>3.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -7760,8 +7967,20 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN31" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2250</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr"/>
@@ -7828,10 +8047,13 @@
         </is>
       </c>
       <c r="DA31" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="DD31" t="n">
         <v>5</v>
+      </c>
+      <c r="DM31" t="n">
+        <v>1.1</v>
       </c>
       <c r="DO31" t="n">
         <v>2.5</v>
@@ -7870,7 +8092,7 @@
       </c>
       <c r="EN31" t="inlineStr">
         <is>
-          <t>{"id":"gun_turret","rebuildCp":11,"branches":["gun_turret.long","gun_turret.auto"],"fort":{"size":"Medium"},"static":true,"armour":3,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":28,"radius":2.5,"length":5,"width":5,"cp":0,"vision":42,"weapon":"turret_gun_120","secondary":[],"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"gun_turret","outgoingDamageMult":1.1,"rebuildCp":11,"branches":["gun_turret.long","gun_turret.auto"],"fort":{"size":"Medium"},"static":true,"armour":3,"hp":2250,"speed":0,"turnRate":1,"turretTurnRate":28,"radius":2.5,"length":5,"width":5,"cp":0,"vision":42,"weapon":"turret_gun_120","secondary":[],"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -7898,10 +8120,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="J32" t="n">
-        <v>3960</v>
+        <v>4950</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
@@ -7958,7 +8180,7 @@
         <v>3.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -7981,8 +8203,20 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN32" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>2250</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
@@ -8093,10 +8327,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1800</v>
+        <v>2250</v>
       </c>
       <c r="J33" t="n">
-        <v>3960</v>
+        <v>4950</v>
       </c>
       <c r="K33" t="n">
         <v>3</v>
@@ -8153,7 +8387,7 @@
         <v>3.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
@@ -8176,8 +8410,20 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN33" t="n">
+        <v>1800</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>2250</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
@@ -8292,10 +8538,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2800</v>
+        <v>3640</v>
       </c>
       <c r="J34" t="n">
-        <v>6160</v>
+        <v>8008</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -8352,7 +8598,7 @@
         <v>3.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
@@ -8375,8 +8621,20 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN34" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>3640</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr"/>
@@ -8452,10 +8710,13 @@
         </is>
       </c>
       <c r="DA34" t="n">
-        <v>2800</v>
+        <v>3640</v>
       </c>
       <c r="DD34" t="n">
         <v>8</v>
+      </c>
+      <c r="DM34" t="n">
+        <v>1.1</v>
       </c>
       <c r="DO34" t="n">
         <v>3.8</v>
@@ -8494,7 +8755,7 @@
       </c>
       <c r="EN34" t="inlineStr">
         <is>
-          <t>{"id":"heavy_turret","rebuildCp":18,"branches":["heavy_turret.coastal","heavy_turret.bastion"],"fort":{"size":"Large"},"static":true,"armour":[4,3,3,3],"hp":2800,"speed":0,"turnRate":1,"turretTurnRate":20,"radius":3.8,"length":8,"width":8,"cp":0,"vision":60,"weapon":"gun_155_twin_ap","secondary":[],"deathExplosion":{"damage":220,"radius":12,"delay":0.5,"tier":"Ultimate"}}</t>
+          <t>{"id":"heavy_turret","outgoingDamageMult":1.1,"rebuildCp":18,"branches":["heavy_turret.coastal","heavy_turret.bastion"],"fort":{"size":"Large"},"static":true,"armour":[4,3,3,3],"hp":3640,"speed":0,"turnRate":1,"turretTurnRate":20,"radius":3.8,"length":8,"width":8,"cp":0,"vision":60,"weapon":"gun_155_twin_ap","secondary":[],"deathExplosion":{"damage":220,"radius":12,"delay":0.5,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -8522,10 +8783,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4340</v>
+        <v>5642</v>
       </c>
       <c r="J35" t="n">
-        <v>9548</v>
+        <v>12412.4</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
@@ -8582,7 +8843,7 @@
         <v>3.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -8609,8 +8870,20 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN35" t="n">
+        <v>4340</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>5642</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
@@ -8669,7 +8942,7 @@
         </is>
       </c>
       <c r="DA35" t="n">
-        <v>4340</v>
+        <v>5642</v>
       </c>
       <c r="DB35" t="inlineStr">
         <is>
@@ -8691,7 +8964,7 @@
       </c>
       <c r="EN35" t="inlineStr">
         <is>
-          <t>{"id":"heavy_turret.bastion","rebuildCp":18,"towerRole":"fortress_close_defence","art":"heavy_turret_b","secondary":[{"weapon":"hmg_roof","slot":"gun","aim":"Free"},{"weapon":"hmg_roof","slot":"gun","aim":"Free"}],"inherits":"heavy_turret","branchOf":"heavy_turret","hp":4340}</t>
+          <t>{"id":"heavy_turret.bastion","rebuildCp":18,"towerRole":"fortress_close_defence","art":"heavy_turret_b","secondary":[{"weapon":"hmg_roof","slot":"gun","aim":"Free"},{"weapon":"hmg_roof","slot":"gun","aim":"Free"}],"inherits":"heavy_turret","branchOf":"heavy_turret","hp":5642}</t>
         </is>
       </c>
     </row>
@@ -8719,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2800</v>
+        <v>3640</v>
       </c>
       <c r="J36" t="n">
-        <v>6160</v>
+        <v>8008</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
@@ -8779,7 +9052,7 @@
         <v>3.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -8802,8 +9075,20 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>3640</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
@@ -8918,10 +9203,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1136</v>
+        <v>1306</v>
       </c>
       <c r="J37" t="n">
-        <v>2499.2</v>
+        <v>2873.2</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -9005,8 +9290,14 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN37" t="n">
+        <v>1136</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1306</v>
       </c>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
@@ -9073,7 +9364,7 @@
         </is>
       </c>
       <c r="DA37" t="n">
-        <v>1136</v>
+        <v>1306</v>
       </c>
       <c r="DD37" t="n">
         <v>5.5</v>
@@ -9123,7 +9414,7 @@
       </c>
       <c r="EN37" t="inlineStr">
         <is>
-          <t>{"id":"laser_ad_station","rebuildCp":5,"branches":["laser_ad_station.laser"],"modelSize":[6.0,3.85,6.6],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1136,"speed":0,"turnRate":1,"turretTurnRate":180,"radius":2.5,"length":5.5,"width":4.0,"cp":0,"vision":56,"weapon":"laser_50kw","aps":{"radius":40,"shells":0,"charges":1,"recharge":0.8,"rockets":true,"laser":true},"deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"laser_ad_station","rebuildCp":5,"branches":["laser_ad_station.laser"],"modelSize":[6.0,3.85,6.6],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1306,"speed":0,"turnRate":1,"turretTurnRate":180,"radius":2.5,"length":5.5,"width":4.0,"cp":0,"vision":56,"weapon":"laser_50kw","aps":{"radius":40,"shells":0,"charges":1,"recharge":0.8,"rockets":true,"laser":true},"deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -9151,10 +9442,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1136</v>
+        <v>1306</v>
       </c>
       <c r="J38" t="n">
-        <v>2499.2</v>
+        <v>2873.2</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -9344,10 +9635,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>545</v>
+        <v>654</v>
       </c>
       <c r="J39" t="n">
-        <v>1199</v>
+        <v>1438.8</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -9427,8 +9718,14 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN39" t="n">
+        <v>545</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>654</v>
       </c>
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
@@ -9476,7 +9773,7 @@
         </is>
       </c>
       <c r="DA39" t="n">
-        <v>545</v>
+        <v>654</v>
       </c>
       <c r="DD39" t="n">
         <v>3</v>
@@ -9528,7 +9825,7 @@
       </c>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>{"id":"manpads_tower","model":"manpads_tower","modelSize":[3.2,3.2,2.4],"fort":{"size":"Small"},"static":true,"armour":1,"hp":545,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":1.7,"length":3.0,"width":3.0,"cp":0,"vision":40,"weapon":"sam"}</t>
+          <t>{"id":"manpads_tower","model":"manpads_tower","modelSize":[3.2,3.2,2.4],"fort":{"size":"Small"},"static":true,"armour":1,"hp":654,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":1.7,"length":3.0,"width":3.0,"cp":0,"vision":40,"weapon":"sam"}</t>
         </is>
       </c>
     </row>
@@ -9560,10 +9857,10 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="J40" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
@@ -9620,7 +9917,7 @@
         <v>3.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.6086</v>
+        <v>0.6573</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -9650,6 +9947,12 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="AN40" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1800</v>
+      </c>
       <c r="BD40" t="inlineStr"/>
       <c r="BE40" t="inlineStr">
         <is>
@@ -9660,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.6086</v>
+        <v>0.6573</v>
       </c>
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
@@ -9740,13 +10043,13 @@
         </is>
       </c>
       <c r="DA40" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="DD40" t="n">
         <v>4</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.6086</v>
+        <v>0.6573</v>
       </c>
       <c r="DO40" t="n">
         <v>2</v>
@@ -9784,7 +10087,7 @@
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker","outgoingDamageMult":0.6086,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1500,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"},"secondary":[{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}]}</t>
+          <t>{"id":"mg_bunker","outgoingDamageMult":0.6573,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"},"secondary":[{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}]}</t>
         </is>
       </c>
     </row>
@@ -9812,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="J41" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="K41" t="n">
         <v>3</v>
@@ -9872,7 +10175,7 @@
         <v>3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.3248</v>
+        <v>0.3508</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -9898,11 +10201,17 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="AN41" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1800</v>
+      </c>
       <c r="BF41" t="n">
         <v>1</v>
       </c>
       <c r="BG41" t="n">
-        <v>0.3248</v>
+        <v>0.3508</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
@@ -9970,7 +10279,7 @@
         </is>
       </c>
       <c r="DM41" t="n">
-        <v>0.3248</v>
+        <v>0.3508</v>
       </c>
       <c r="DP41" t="n">
         <v>6</v>
@@ -9993,7 +10302,7 @@
       </c>
       <c r="EN41" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker.flame","outgoingDamageMult":0.3248,"rebuildCp":6,"towerRole":"flame_close","art":"mg_bunker_b","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_flame","secondary":[]}</t>
+          <t>{"id":"mg_bunker.flame","outgoingDamageMult":0.3508,"rebuildCp":6,"towerRole":"flame_close","art":"mg_bunker_b","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_flame","secondary":[]}</t>
         </is>
       </c>
     </row>
@@ -10021,10 +10330,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="J42" t="n">
-        <v>3300</v>
+        <v>3960</v>
       </c>
       <c r="K42" t="n">
         <v>3</v>
@@ -10081,7 +10390,7 @@
         <v>3.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.5036</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -10111,6 +10420,12 @@
           <t>doi</t>
         </is>
       </c>
+      <c r="AN42" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1800</v>
+      </c>
       <c r="BD42" t="inlineStr"/>
       <c r="BE42" t="inlineStr">
         <is>
@@ -10121,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5036</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
@@ -10189,7 +10504,7 @@
         </is>
       </c>
       <c r="DM42" t="n">
-        <v>0.5036</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="DP42" t="n">
         <v>6</v>
@@ -10211,7 +10526,7 @@
       </c>
       <c r="EN42" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker.twin","outgoingDamageMult":0.5036,"rebuildCp":6,"towerRole":"mg_twin","art":"mg_bunker_a","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_hmg_twin"}</t>
+          <t>{"id":"mg_bunker.twin","outgoingDamageMult":0.5439,"rebuildCp":6,"towerRole":"mg_twin","art":"mg_bunker_a","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_hmg_twin"}</t>
         </is>
       </c>
     </row>
@@ -10243,10 +10558,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1900</v>
+        <v>2470</v>
       </c>
       <c r="J43" t="n">
-        <v>4180</v>
+        <v>5434</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -10326,8 +10641,14 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN43" t="n">
+        <v>1900</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>2470</v>
       </c>
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr"/>
@@ -10397,7 +10718,7 @@
         </is>
       </c>
       <c r="DA43" t="n">
-        <v>1900</v>
+        <v>2470</v>
       </c>
       <c r="DD43" t="n">
         <v>7</v>
@@ -10439,7 +10760,7 @@
       </c>
       <c r="EN43" t="inlineStr">
         <is>
-          <t>{"id":"missile_battery","erectSeconds":1.2,"rebuildCp":13,"branches":["missile_battery.pac3","missile_battery.lrr"],"fort":{"size":"Large"},"static":true,"armour":1,"hp":1900,"speed":0,"turnRate":1,"turretTurnRate":70,"radius":3.8,"length":7,"width":9,"cp":0,"vision":95,"weapon":"patriot","secondary":[],"deathExplosion":{"damage":200,"radius":12,"delay":0.4,"tier":"Ultimate"}}</t>
+          <t>{"id":"missile_battery","erectSeconds":1.2,"rebuildCp":13,"branches":["missile_battery.pac3","missile_battery.lrr"],"fort":{"size":"Large"},"static":true,"armour":1,"hp":2470,"speed":0,"turnRate":1,"turretTurnRate":70,"radius":3.8,"length":7,"width":9,"cp":0,"vision":95,"weapon":"patriot","secondary":[],"deathExplosion":{"damage":200,"radius":12,"delay":0.4,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -10467,10 +10788,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1900</v>
+        <v>2470</v>
       </c>
       <c r="J44" t="n">
-        <v>4180</v>
+        <v>5434</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -10550,8 +10871,14 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN44" t="n">
+        <v>1900</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>2470</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
@@ -10668,10 +10995,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1900</v>
+        <v>2470</v>
       </c>
       <c r="J45" t="n">
-        <v>4180</v>
+        <v>5434</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -10753,8 +11080,14 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN45" t="n">
+        <v>1900</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>2470</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
@@ -10869,10 +11202,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>909</v>
+        <v>1136</v>
       </c>
       <c r="J46" t="n">
-        <v>1999.8</v>
+        <v>2499.2</v>
       </c>
       <c r="K46" t="n">
         <v>2</v>
@@ -10929,7 +11262,7 @@
         <v>3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
@@ -10952,8 +11285,20 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>909</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1136</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr"/>
@@ -11015,7 +11360,7 @@
         </is>
       </c>
       <c r="DA46" t="n">
-        <v>909</v>
+        <v>1136</v>
       </c>
       <c r="DD46" t="n">
         <v>4.8</v>
@@ -11034,6 +11379,9 @@
       <c r="DJ46" t="n">
         <v>4.8</v>
       </c>
+      <c r="DM46" t="n">
+        <v>1.1</v>
+      </c>
       <c r="DO46" t="n">
         <v>2.3</v>
       </c>
@@ -11067,7 +11415,7 @@
       </c>
       <c r="EN46" t="inlineStr">
         <is>
-          <t>{"id":"one_shot_atgm_tower","model":"one_shot_atgm_tower","modelSize":[4.8,4.8,3.6],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":909,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.8,"width":4.8,"cp":0,"vision":40,"weapon":"one_shot_kornet","deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"one_shot_atgm_tower","outgoingDamageMult":1.1,"model":"one_shot_atgm_tower","modelSize":[4.8,4.8,3.6],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1136,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.8,"width":4.8,"cp":0,"vision":40,"weapon":"one_shot_kornet","deathExplosion":{"damage":80,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -11099,10 +11447,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>545</v>
+        <v>654</v>
       </c>
       <c r="J47" t="n">
-        <v>1199</v>
+        <v>1438.8</v>
       </c>
       <c r="K47" t="n">
         <v>1</v>
@@ -11159,7 +11507,7 @@
         <v>3.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -11182,8 +11530,20 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN47" t="n">
+        <v>545</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>654</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>1.08</v>
       </c>
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr"/>
@@ -11245,7 +11605,7 @@
         </is>
       </c>
       <c r="DA47" t="n">
-        <v>545</v>
+        <v>654</v>
       </c>
       <c r="DD47" t="n">
         <v>3.5</v>
@@ -11264,6 +11624,9 @@
       <c r="DJ47" t="n">
         <v>4.2</v>
       </c>
+      <c r="DM47" t="n">
+        <v>1.08</v>
+      </c>
       <c r="DO47" t="n">
         <v>1.8</v>
       </c>
@@ -11297,7 +11660,7 @@
       </c>
       <c r="EN47" t="inlineStr">
         <is>
-          <t>{"id":"recoilless_gun_tower","model":"recoilless_gun_tower","modelSize":[4.2,4.2,3.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":545,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":1.8,"length":3.5,"width":3.5,"cp":0,"vision":32,"weapon":"spg9_73mm","deathExplosion":{"damage":40,"radius":5,"delay":0.25,"tier":"Large"}}</t>
+          <t>{"id":"recoilless_gun_tower","outgoingDamageMult":1.08,"model":"recoilless_gun_tower","modelSize":[4.2,4.2,3.0],"fort":{"size":"Small"},"static":true,"armour":1,"hp":654,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":1.8,"length":3.5,"width":3.5,"cp":0,"vision":32,"weapon":"spg9_73mm","deathExplosion":{"damage":40,"radius":5,"delay":0.25,"tier":"Large"}}</t>
         </is>
       </c>
     </row>
@@ -11329,10 +11692,10 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="J48" t="n">
-        <v>2420</v>
+        <v>3025</v>
       </c>
       <c r="K48" t="n">
         <v>1</v>
@@ -11389,7 +11752,7 @@
         <v>3.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -11412,8 +11775,20 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN48" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>1375</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr"/>
@@ -11480,10 +11855,13 @@
         </is>
       </c>
       <c r="DA48" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="DD48" t="n">
         <v>4.5</v>
+      </c>
+      <c r="DM48" t="n">
+        <v>1.1</v>
       </c>
       <c r="DO48" t="n">
         <v>2.3</v>
@@ -11522,7 +11900,7 @@
       </c>
       <c r="EN48" t="inlineStr">
         <is>
-          <t>{"id":"rocket_turret","rebuildCp":11,"branches":["rocket_turret.cluster","rocket_turret.guided"],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1100,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.5,"width":4.5,"cp":0,"vision":55,"weapon":"turret_rockets","secondary":[],"deathExplosion":{"damage":140,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"rocket_turret","outgoingDamageMult":1.1,"rebuildCp":11,"branches":["rocket_turret.cluster","rocket_turret.guided"],"fort":{"size":"Medium"},"static":true,"armour":1,"hp":1375,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":2.3,"length":4.5,"width":4.5,"cp":0,"vision":55,"weapon":"turret_rockets","secondary":[],"deathExplosion":{"damage":140,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -11550,10 +11928,10 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="J49" t="n">
-        <v>2420</v>
+        <v>3025</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
@@ -11610,7 +11988,7 @@
         <v>3.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -11633,8 +12011,20 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN49" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>1375</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
@@ -11745,10 +12135,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1100</v>
+        <v>1375</v>
       </c>
       <c r="J50" t="n">
-        <v>2420</v>
+        <v>3025</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
@@ -11805,7 +12195,7 @@
         <v>3.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
@@ -11828,8 +12218,20 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN50" t="n">
+        <v>1100</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1375</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>1.1</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
@@ -11947,10 +12349,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="J51" t="n">
-        <v>4400</v>
+        <v>4840</v>
       </c>
       <c r="K51" t="n">
         <v>2</v>
@@ -12030,8 +12432,14 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN51" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>2200</v>
       </c>
       <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr"/>
@@ -12107,7 +12515,7 @@
         </is>
       </c>
       <c r="DA51" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="DD51" t="n">
         <v>7</v>
@@ -12148,7 +12556,7 @@
       </c>
       <c r="EN51" t="inlineStr">
         <is>
-          <t>{"id":"shield_tower","rebuildCp":10,"branches":["shield_tower.bulwark","shield_tower.ward"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2000,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.2,"length":7,"width":7,"cp":0,"vision":40,"weapon":"none","dome":{"radius":25,"hp":3000,"recharge":30},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"shield_tower","rebuildCp":10,"branches":["shield_tower.bulwark","shield_tower.ward"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2200,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.2,"length":7,"width":7,"cp":0,"vision":40,"weapon":"none","dome":{"radius":25,"hp":3000,"recharge":30},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -12176,10 +12584,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="J52" t="n">
-        <v>4400</v>
+        <v>4840</v>
       </c>
       <c r="K52" t="n">
         <v>2</v>
@@ -12259,8 +12667,14 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN52" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>2200</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
@@ -12371,10 +12785,10 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="J53" t="n">
-        <v>4400</v>
+        <v>4840</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
@@ -12454,8 +12868,14 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN53" t="n">
+        <v>2000</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2200</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
@@ -12539,7 +12959,7 @@
         </is>
       </c>
       <c r="DA53" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="DD53" t="n">
         <v>7</v>
@@ -12599,7 +13019,7 @@
       </c>
       <c r="EN53" t="inlineStr">
         <is>
-          <t>{"id":"shield_tower.ward","rebuildCp":10,"towerRole":"tower_shields","art":"shield_tower_b","branchOf":"shield_tower","model":"shield_tower","fort":{"size":"Large"},"static":true,"armour":2,"hp":2000,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.2,"length":7,"width":7,"cp":0,"vision":40,"weapon":"none","wards":{"radius":28,"hp":1200,"recharge":6},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"shield_tower.ward","rebuildCp":10,"towerRole":"tower_shields","art":"shield_tower_b","branchOf":"shield_tower","model":"shield_tower","fort":{"size":"Large"},"static":true,"armour":2,"hp":2200,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.2,"length":7,"width":7,"cp":0,"vision":40,"weapon":"none","wards":{"radius":28,"hp":1200,"recharge":6},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -12849,10 +13269,10 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>5200</v>
+        <v>5980</v>
       </c>
       <c r="J55" t="n">
-        <v>11440</v>
+        <v>13156</v>
       </c>
       <c r="K55" t="n">
         <v>3</v>
@@ -12932,8 +13352,14 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN55" t="n">
+        <v>5200</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>5980</v>
       </c>
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr"/>
@@ -12985,7 +13411,7 @@
         </is>
       </c>
       <c r="DA55" t="n">
-        <v>5200</v>
+        <v>5980</v>
       </c>
       <c r="DD55" t="n">
         <v>8</v>
@@ -13031,7 +13457,7 @@
       </c>
       <c r="EN55" t="inlineStr">
         <is>
-          <t>{"id":"super_gun","class":"Defense","static":true,"model":"super_gun","scale":1.8,"armour":3,"hp":5200,"speed":0,"turnRate":1,"turretTurnRate":12,"radius":7,"length":8,"width":8,"cp":0,"vision":40,"weapon":"none","deathExplosion":{"damage":380,"radius":18,"delay":0.6,"tier":"Ultimate"}}</t>
+          <t>{"id":"super_gun","class":"Defense","static":true,"model":"super_gun","scale":1.8,"armour":3,"hp":5980,"speed":0,"turnRate":1,"turretTurnRate":12,"radius":7,"length":8,"width":8,"cp":0,"vision":40,"weapon":"none","deathExplosion":{"damage":380,"radius":18,"delay":0.6,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -13067,10 +13493,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="J56" t="n">
-        <v>1540</v>
+        <v>1848</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -13150,8 +13576,14 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN56" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>840</v>
       </c>
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr"/>
@@ -13203,7 +13635,7 @@
         </is>
       </c>
       <c r="DA56" t="n">
-        <v>700</v>
+        <v>840</v>
       </c>
       <c r="DD56" t="n">
         <v>8</v>
@@ -13241,7 +13673,7 @@
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>{"id":"targeting_station","class":"Defense","static":true,"armour":1,"hp":700,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.4,"length":8,"width":6.5,"cp":0,"vision":110,"weapon":"none","deathExplosion":{"damage":80,"radius":6,"delay":0.3,"tier":"Huge"}}</t>
+          <t>{"id":"targeting_station","class":"Defense","static":true,"armour":1,"hp":840,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.4,"length":8,"width":6.5,"cp":0,"vision":110,"weapon":"none","deathExplosion":{"damage":80,"radius":6,"delay":0.3,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -13273,10 +13705,10 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
       <c r="J57" t="n">
-        <v>3960</v>
+        <v>4752</v>
       </c>
       <c r="K57" t="n">
         <v>2</v>
@@ -13436,7 +13868,7 @@
         </is>
       </c>
       <c r="DA57" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
       <c r="DD57" t="n">
         <v>8</v>
@@ -13491,7 +13923,7 @@
       </c>
       <c r="EN57" t="inlineStr">
         <is>
-          <t>{"id":"vehicle_hangar","rebuildCp":8,"model":"vehicle_hangar_base","modelSize":[8.0,7.5,4.93],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_jeep","armored_car","light_tank"],"every":60,"alive":2,"budget":5,"post":20},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"vehicle_hangar","rebuildCp":8,"model":"vehicle_hangar_base","modelSize":[8.0,7.5,4.93],"fort":{"size":"Medium"},"static":true,"armour":2,"hp":2160,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":50,"weapon":"none","hangar":{"units":["scout_jeep","armored_car","light_tank"],"every":60,"alive":2,"budget":5,"post":20},"deathExplosion":{"damage":120,"radius":8,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -14081,10 +14513,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="J2" t="n">
-        <v>3520</v>
+        <v>4224</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -14164,8 +14596,14 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1920</v>
       </c>
       <c r="BH2" t="n">
         <v>1</v>
@@ -14195,7 +14633,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="BV2" t="n">
         <v>6</v>
@@ -14241,7 +14679,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>{"id":"airfield","fort":{"size":"Medium","kind":"Utility"},"model":"helipad","static":true,"passable":true,"armour":1,"hp":1600,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","aura":{"reach":"Aircraft","damage":0.1,"speed":0.1}}</t>
+          <t>{"id":"airfield","fort":{"size":"Medium","kind":"Utility"},"model":"helipad","static":true,"passable":true,"armour":1,"hp":1920,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","aura":{"reach":"Aircraft","damage":0.1,"speed":0.1}}</t>
         </is>
       </c>
     </row>
@@ -14273,10 +14711,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1136</v>
+        <v>1420</v>
       </c>
       <c r="J3" t="n">
-        <v>2499.2</v>
+        <v>3124</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -14356,8 +14794,14 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1136</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1420</v>
       </c>
       <c r="BH3" t="n">
         <v>1</v>
@@ -14401,7 +14845,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>1136</v>
+        <v>1420</v>
       </c>
       <c r="BV3" t="n">
         <v>6</v>
@@ -14448,7 +14892,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>{"id":"fire_control_centre","modelSize":[6.0,6.0,5.5],"fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":1,"hp":1136,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":40,"weapon":"none","aura":{"reach":"Structures","range":0.15,"hp":0.1},"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"fire_control_centre","modelSize":[6.0,6.0,5.5],"fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":1,"hp":1420,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":40,"weapon":"none","aura":{"reach":"Structures","range":0.15,"hp":0.1},"deathExplosion":{"damage":90,"radius":7,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -14480,10 +14924,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1400</v>
+        <v>1680</v>
       </c>
       <c r="J4" t="n">
-        <v>3080</v>
+        <v>3696</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -14563,8 +15007,14 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1680</v>
       </c>
       <c r="BH4" t="n">
         <v>1</v>
@@ -14597,7 +15047,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>1400</v>
+        <v>1680</v>
       </c>
       <c r="BV4" t="n">
         <v>6</v>
@@ -14638,7 +15088,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>{"id":"logistics_station","fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":1,"hp":1400,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","utility":{"supply":8},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
+          <t>{"id":"logistics_station","fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":1,"hp":1680,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","utility":{"supply":8},"deathExplosion":{"damage":160,"radius":9,"delay":0.4,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -14670,10 +15120,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="J5" t="n">
-        <v>3520</v>
+        <v>4224</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -14753,8 +15203,14 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1920</v>
       </c>
       <c r="BH5" t="n">
         <v>2</v>
@@ -14784,7 +15240,7 @@
         </is>
       </c>
       <c r="BU5" t="n">
-        <v>1600</v>
+        <v>1920</v>
       </c>
       <c r="BV5" t="n">
         <v>6</v>
@@ -14822,7 +15278,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>{"id":"repair_bay","fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":2,"hp":1600,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","aura":{"reach":"Ground","damage":0.1,"hp":0.1}}</t>
+          <t>{"id":"repair_bay","fort":{"size":"Medium","kind":"Utility"},"static":true,"armour":2,"hp":1920,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3,"length":6,"width":6,"cp":0,"vision":30,"weapon":"none","aura":{"reach":"Ground","damage":0.1,"hp":0.1}}</t>
         </is>
       </c>
     </row>
@@ -20962,10 +21418,10 @@
         <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>99.66666666666667</v>
+        <v>109.6333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H6" t="n">
         <v>10.81329019942361</v>
@@ -21034,10 +21490,10 @@
         <v>1.36</v>
       </c>
       <c r="F7" t="n">
-        <v>84.71666666666668</v>
+        <v>93.18833333333336</v>
       </c>
       <c r="G7" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H7" t="n">
         <v>10.81329019942361</v>
@@ -21106,10 +21562,10 @@
         <v>1.36</v>
       </c>
       <c r="F8" t="n">
-        <v>117.875</v>
+        <v>129.6625</v>
       </c>
       <c r="G8" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H8" t="n">
         <v>10.81329019942361</v>
@@ -21424,7 +21880,7 @@
         <v>1.36</v>
       </c>
       <c r="F13" t="n">
-        <v>69.33333333333334</v>
+        <v>76.26666666666668</v>
       </c>
       <c r="G13" t="n">
         <v>172.8789682539683</v>
@@ -21496,7 +21952,7 @@
         <v>1.36</v>
       </c>
       <c r="F14" t="n">
-        <v>94.25</v>
+        <v>103.675</v>
       </c>
       <c r="G14" t="n">
         <v>172.8789682539683</v>
@@ -21568,7 +22024,7 @@
         <v>1.36</v>
       </c>
       <c r="F15" t="n">
-        <v>92.15189873417722</v>
+        <v>101.367088607595</v>
       </c>
       <c r="G15" t="n">
         <v>172.8789682539683</v>
@@ -21802,7 +22258,7 @@
         <v>1.15</v>
       </c>
       <c r="F19" t="n">
-        <v>77.52</v>
+        <v>83.7216</v>
       </c>
       <c r="G19" t="n">
         <v>200</v>
@@ -21874,7 +22330,7 @@
         <v>1.15</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G20" t="n">
         <v>200</v>
@@ -21946,7 +22402,7 @@
         <v>1.15</v>
       </c>
       <c r="F21" t="n">
-        <v>80.26991345166496</v>
+        <v>86.69150652779817</v>
       </c>
       <c r="G21" t="n">
         <v>200</v>
@@ -22018,10 +22474,10 @@
         <v>1.04</v>
       </c>
       <c r="F22" t="n">
-        <v>92.54496840058339</v>
+        <v>101.7994652406417</v>
       </c>
       <c r="G22" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H22" t="n">
         <v>10.81329019942361</v>
@@ -22090,7 +22546,7 @@
         <v>1.04</v>
       </c>
       <c r="F23" t="n">
-        <v>93.33333333333333</v>
+        <v>102.6666666666667</v>
       </c>
       <c r="G23" t="n">
         <v>183.3333333333333</v>
@@ -22162,10 +22618,10 @@
         <v>1.04</v>
       </c>
       <c r="F24" t="n">
-        <v>81.27086698976845</v>
+        <v>89.3979536887453</v>
       </c>
       <c r="G24" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H24" t="n">
         <v>10.81329019942361</v>
@@ -22234,10 +22690,10 @@
         <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>71.41884222474461</v>
+        <v>78.56072644721908</v>
       </c>
       <c r="G25" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H25" t="n">
         <v>10.81329019942361</v>
@@ -22306,10 +22762,10 @@
         <v>0.7</v>
       </c>
       <c r="F26" t="n">
-        <v>134.9044715365465</v>
+        <v>148.3949186902012</v>
       </c>
       <c r="G26" t="n">
-        <v>328.4901960784314</v>
+        <v>339.2549019607844</v>
       </c>
       <c r="H26" t="n">
         <v>10.81329019942361</v>
@@ -22378,7 +22834,7 @@
         <v>0.7</v>
       </c>
       <c r="F27" t="n">
-        <v>51.67730052048679</v>
+        <v>56.84503057253548</v>
       </c>
       <c r="G27" t="n">
         <v>126.6920634920635</v>
@@ -22576,7 +23032,7 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>86.62070588902758</v>
+        <v>93.55207029388404</v>
       </c>
       <c r="G30" t="n">
         <v>200</v>
@@ -22648,7 +23104,7 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>49.69439999999999</v>
+        <v>53.6724</v>
       </c>
       <c r="G31" t="n">
         <v>200</v>
@@ -22720,7 +23176,7 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>82.61632637425784</v>
+        <v>89.2276011019834</v>
       </c>
       <c r="G32" t="n">
         <v>200</v>
@@ -23008,7 +23464,7 @@
         <v>1.6</v>
       </c>
       <c r="F36" t="n">
-        <v>60.39729729729729</v>
+        <v>66.43702702702703</v>
       </c>
       <c r="G36" t="n">
         <v>126.6920634920635</v>
@@ -23080,7 +23536,7 @@
         <v>1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>54.15727040816327</v>
+        <v>59.5729974489796</v>
       </c>
       <c r="G37" t="n">
         <v>126.6920634920635</v>
@@ -23152,7 +23608,7 @@
         <v>1.6</v>
       </c>
       <c r="F38" t="n">
-        <v>39</v>
+        <v>42.90000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>126.6920634920635</v>
@@ -26133,7 +26589,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.723586091328027</v>
+        <v>4.178655325421075</v>
       </c>
       <c r="G7" t="n">
         <v>0.8152408339324227</v>
@@ -26180,7 +26636,7 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.904482614160034</v>
+        <v>5.223319156776344</v>
       </c>
       <c r="G8" t="n">
         <v>1.019051042415528</v>
@@ -26227,7 +26683,7 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>6.790155006284038</v>
+        <v>6.006817030292795</v>
       </c>
       <c r="G9" t="n">
         <v>1.171908698777858</v>
@@ -26274,7 +26730,7 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.971051529116045</v>
+        <v>7.051480861648064</v>
       </c>
       <c r="G10" t="n">
         <v>1.375718907260963</v>
@@ -26321,7 +26777,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>9.151948051948052</v>
+        <v>8.096144693003334</v>
       </c>
       <c r="G11" t="n">
         <v>1.579529115744069</v>
@@ -26603,13 +27059,13 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2.718776550552251</v>
+        <v>2.938370041173779</v>
       </c>
       <c r="G17" t="n">
-        <v>1.140129403306974</v>
+        <v>1.341687994248742</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9317038102084829</v>
+        <v>0.9782890007189072</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -26650,13 +27106,13 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.718776550552251</v>
+        <v>2.938370041173779</v>
       </c>
       <c r="G18" t="n">
-        <v>2.116002875629044</v>
+        <v>2.49008195542775</v>
       </c>
       <c r="H18" t="n">
-        <v>1.125808770668584</v>
+        <v>1.182099209202013</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -26697,13 +27153,13 @@
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>2.718776550552251</v>
+        <v>2.938370041173779</v>
       </c>
       <c r="G19" t="n">
-        <v>3.043565780014378</v>
+        <v>3.581624730409777</v>
       </c>
       <c r="H19" t="n">
-        <v>1.397555715312724</v>
+        <v>1.467433501078361</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -26744,13 +27200,13 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>2.718776550552251</v>
+        <v>2.938370041173779</v>
       </c>
       <c r="G20" t="n">
-        <v>4.000115025161755</v>
+        <v>4.707278217109994</v>
       </c>
       <c r="H20" t="n">
-        <v>1.552839683680805</v>
+        <v>1.630481667864845</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -26791,13 +27247,13 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>2.718776550552251</v>
+        <v>2.938370041173779</v>
       </c>
       <c r="G21" t="n">
-        <v>5.101595974119339</v>
+        <v>6.003485262401151</v>
       </c>
       <c r="H21" t="n">
-        <v>1.669302659956865</v>
+        <v>1.752767792954708</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -50790,10 +51246,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>9000</v>
+        <v>9450</v>
       </c>
       <c r="J2" t="n">
-        <v>19800</v>
+        <v>20790</v>
       </c>
       <c r="K2" t="n">
         <v>4</v>
@@ -50877,8 +51333,14 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>giong</t>
-        </is>
+          <t>doi</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>9450</v>
       </c>
       <c r="BH2" t="n">
         <v>4</v>
@@ -50917,7 +51379,7 @@
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>9000</v>
+        <v>9450</v>
       </c>
       <c r="BT2" t="n">
         <v>12</v>
@@ -50963,7 +51425,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>{"id":"headquarters","class":"Defense","static":true,"model":"headquarters","armour":4,"hp":9000,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":6.8,"length":12,"width":14,"scale":1.0,"cp":0,"vision":50,"firesWhileMoving":true,"weapon":"bastion_gun","fort":{"points":0,"kind":"Hq"},"secondary":[{"weapon":"hq_flak","slot":"mg","aim":"Free"},{"weapon":"hq_flak","slot":"mg","aim":"Free"},{"weapon":"mg_coax","slot":"coax","aim":"Turret"}],"deathExplosion":{"damage":260,"radius":14,"delay":0.8,"tier":"Ultimate"}}</t>
+          <t>{"id":"headquarters","class":"Defense","static":true,"model":"headquarters","armour":4,"hp":9450,"speed":0,"turnRate":1,"turretTurnRate":90,"radius":6.8,"length":12,"width":14,"scale":1.0,"cp":0,"vision":50,"firesWhileMoving":true,"weapon":"bastion_gun","fort":{"points":0,"kind":"Hq"},"secondary":[{"weapon":"hq_flak","slot":"mg","aim":"Free"},{"weapon":"hq_flak","slot":"mg","aim":"Free"},{"weapon":"mg_coax","slot":"coax","aim":"Turret"}],"deathExplosion":{"damage":260,"radius":14,"delay":0.8,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -51003,10 +51465,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>9000</v>
+        <v>9450</v>
       </c>
       <c r="J3" t="n">
-        <v>19800</v>
+        <v>20790</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -51145,10 +51607,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>9000</v>
+        <v>9450</v>
       </c>
       <c r="J4" t="n">
-        <v>19800</v>
+        <v>20790</v>
       </c>
       <c r="K4" t="n">
         <v>4</v>
@@ -51287,10 +51749,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>9000</v>
+        <v>9450</v>
       </c>
       <c r="J5" t="n">
-        <v>19800</v>
+        <v>20790</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -5214,10 +5214,10 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="J19" t="n">
-        <v>6292</v>
+        <v>6050</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -5304,7 +5304,7 @@
         <v>2200</v>
       </c>
       <c r="AO19" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="BF19" t="n">
         <v>1</v>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="DA19" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="DD19" t="n">
         <v>8</v>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="EN19" t="inlineStr">
         <is>
-          <t>{"id":"drone_hangar","outgoingDamageMult":1.1,"rebuildCp":12,"branches":["drone_hangar.lancet","drone_hangar.swarm"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2860,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":60,"weapon":"fpv_hangar","mainSlot":"door_l","mainAim":"Hull","deathExplosion":{"damage":160,"radius":10,"delay":0.4,"tier":"Ultimate"}}</t>
+          <t>{"id":"drone_hangar","outgoingDamageMult":1.1,"rebuildCp":12,"branches":["drone_hangar.lancet","drone_hangar.swarm"],"fort":{"size":"Large"},"static":true,"armour":2,"hp":2750,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.6,"length":8,"width":8,"cp":0,"vision":60,"weapon":"fpv_hangar","mainSlot":"door_l","mainAim":"Hull","deathExplosion":{"damage":160,"radius":10,"delay":0.4,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="J20" t="n">
-        <v>6292</v>
+        <v>6050</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -5549,7 +5549,7 @@
         <v>2200</v>
       </c>
       <c r="AO20" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="BF20" t="n">
         <v>1</v>
@@ -5666,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="J21" t="n">
-        <v>6292</v>
+        <v>6050</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -5756,7 +5756,7 @@
         <v>2200</v>
       </c>
       <c r="AO21" t="n">
-        <v>2860</v>
+        <v>2750</v>
       </c>
       <c r="BF21" t="n">
         <v>1</v>
@@ -8538,10 +8538,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3640</v>
+        <v>3500</v>
       </c>
       <c r="J34" t="n">
-        <v>8008</v>
+        <v>7700</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -8628,7 +8628,7 @@
         <v>2800</v>
       </c>
       <c r="AO34" t="n">
-        <v>3640</v>
+        <v>3500</v>
       </c>
       <c r="BF34" t="n">
         <v>1</v>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="DA34" t="n">
-        <v>3640</v>
+        <v>3500</v>
       </c>
       <c r="DD34" t="n">
         <v>8</v>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="EN34" t="inlineStr">
         <is>
-          <t>{"id":"heavy_turret","outgoingDamageMult":1.1,"rebuildCp":18,"branches":["heavy_turret.coastal","heavy_turret.bastion"],"fort":{"size":"Large"},"static":true,"armour":[4,3,3,3],"hp":3640,"speed":0,"turnRate":1,"turretTurnRate":20,"radius":3.8,"length":8,"width":8,"cp":0,"vision":60,"weapon":"gun_155_twin_ap","secondary":[],"deathExplosion":{"damage":220,"radius":12,"delay":0.5,"tier":"Ultimate"}}</t>
+          <t>{"id":"heavy_turret","outgoingDamageMult":1.1,"rebuildCp":18,"branches":["heavy_turret.coastal","heavy_turret.bastion"],"fort":{"size":"Large"},"static":true,"armour":[4,3,3,3],"hp":3500,"speed":0,"turnRate":1,"turretTurnRate":20,"radius":3.8,"length":8,"width":8,"cp":0,"vision":60,"weapon":"gun_155_twin_ap","secondary":[],"deathExplosion":{"damage":220,"radius":12,"delay":0.5,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -8783,10 +8783,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>5642</v>
+        <v>5425</v>
       </c>
       <c r="J35" t="n">
-        <v>12412.4</v>
+        <v>11935</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
@@ -8877,7 +8877,7 @@
         <v>4340</v>
       </c>
       <c r="AO35" t="n">
-        <v>5642</v>
+        <v>5425</v>
       </c>
       <c r="BF35" t="n">
         <v>1</v>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="DA35" t="n">
-        <v>5642</v>
+        <v>5425</v>
       </c>
       <c r="DB35" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="EN35" t="inlineStr">
         <is>
-          <t>{"id":"heavy_turret.bastion","rebuildCp":18,"towerRole":"fortress_close_defence","art":"heavy_turret_b","secondary":[{"weapon":"hmg_roof","slot":"gun","aim":"Free"},{"weapon":"hmg_roof","slot":"gun","aim":"Free"}],"inherits":"heavy_turret","branchOf":"heavy_turret","hp":5642}</t>
+          <t>{"id":"heavy_turret.bastion","rebuildCp":18,"towerRole":"fortress_close_defence","art":"heavy_turret_b","secondary":[{"weapon":"hmg_roof","slot":"gun","aim":"Free"},{"weapon":"hmg_roof","slot":"gun","aim":"Free"}],"inherits":"heavy_turret","branchOf":"heavy_turret","hp":5425}</t>
         </is>
       </c>
     </row>
@@ -8992,10 +8992,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3640</v>
+        <v>3500</v>
       </c>
       <c r="J36" t="n">
-        <v>8008</v>
+        <v>7700</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
@@ -9082,7 +9082,7 @@
         <v>2800</v>
       </c>
       <c r="AO36" t="n">
-        <v>3640</v>
+        <v>3500</v>
       </c>
       <c r="BF36" t="n">
         <v>1</v>
@@ -9917,7 +9917,7 @@
         <v>3.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.6573</v>
+        <v>0.6695</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="BG40" t="n">
-        <v>0.6573</v>
+        <v>0.6695</v>
       </c>
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
@@ -10049,7 +10049,7 @@
         <v>4</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.6573</v>
+        <v>0.6695</v>
       </c>
       <c r="DO40" t="n">
         <v>2</v>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker","outgoingDamageMult":0.6573,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"},"secondary":[{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}]}</t>
+          <t>{"id":"mg_bunker","outgoingDamageMult":0.6695,"rebuildCp":6,"branches":["mg_bunker.twin","mg_bunker.flame"],"fort":{"size":"Small"},"static":true,"armour":[3,2,2,2],"hp":1800,"speed":0,"turnRate":1,"turretTurnRate":120,"radius":2.0,"length":4,"width":4,"cp":0,"vision":36,"weapon":"bunker_hmg","deathExplosion":{"damage":70,"radius":6,"delay":0.3,"tier":"Large"},"secondary":[{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[30,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[-90,40]},{"weapon":"bunker_pkm","slot":"mg","aim":"Free","arc":[90,40]}]}</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
         <v>3.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.3508</v>
+        <v>0.3573</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>1</v>
       </c>
       <c r="BG41" t="n">
-        <v>0.3508</v>
+        <v>0.3573</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         </is>
       </c>
       <c r="DM41" t="n">
-        <v>0.3508</v>
+        <v>0.3573</v>
       </c>
       <c r="DP41" t="n">
         <v>6</v>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="EN41" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker.flame","outgoingDamageMult":0.3508,"rebuildCp":6,"towerRole":"flame_close","art":"mg_bunker_b","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_flame","secondary":[]}</t>
+          <t>{"id":"mg_bunker.flame","outgoingDamageMult":0.3573,"rebuildCp":6,"towerRole":"flame_close","art":"mg_bunker_b","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_flame","secondary":[]}</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
         <v>3.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="BG42" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         </is>
       </c>
       <c r="DM42" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.554</v>
       </c>
       <c r="DP42" t="n">
         <v>6</v>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="EN42" t="inlineStr">
         <is>
-          <t>{"id":"mg_bunker.twin","outgoingDamageMult":0.5439,"rebuildCp":6,"towerRole":"mg_twin","art":"mg_bunker_a","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_hmg_twin"}</t>
+          <t>{"id":"mg_bunker.twin","outgoingDamageMult":0.554,"rebuildCp":6,"towerRole":"mg_twin","art":"mg_bunker_a","inherits":"mg_bunker","branchOf":"mg_bunker","weapon":"bunker_hmg_twin"}</t>
         </is>
       </c>
     </row>
@@ -10558,10 +10558,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="J43" t="n">
-        <v>5434</v>
+        <v>5225</v>
       </c>
       <c r="K43" t="n">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>1900</v>
       </c>
       <c r="AO43" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr"/>
@@ -10718,7 +10718,7 @@
         </is>
       </c>
       <c r="DA43" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="DD43" t="n">
         <v>7</v>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="EN43" t="inlineStr">
         <is>
-          <t>{"id":"missile_battery","erectSeconds":1.2,"rebuildCp":13,"branches":["missile_battery.pac3","missile_battery.lrr"],"fort":{"size":"Large"},"static":true,"armour":1,"hp":2470,"speed":0,"turnRate":1,"turretTurnRate":70,"radius":3.8,"length":7,"width":9,"cp":0,"vision":95,"weapon":"patriot","secondary":[],"deathExplosion":{"damage":200,"radius":12,"delay":0.4,"tier":"Ultimate"}}</t>
+          <t>{"id":"missile_battery","erectSeconds":1.2,"rebuildCp":13,"branches":["missile_battery.pac3","missile_battery.lrr"],"fort":{"size":"Large"},"static":true,"armour":1,"hp":2375,"speed":0,"turnRate":1,"turretTurnRate":70,"radius":3.8,"length":7,"width":9,"cp":0,"vision":95,"weapon":"patriot","secondary":[],"deathExplosion":{"damage":200,"radius":12,"delay":0.4,"tier":"Ultimate"}}</t>
         </is>
       </c>
     </row>
@@ -10788,10 +10788,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="J44" t="n">
-        <v>5434</v>
+        <v>5225</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -10878,7 +10878,7 @@
         <v>1900</v>
       </c>
       <c r="AO44" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
@@ -10995,10 +10995,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="J45" t="n">
-        <v>5434</v>
+        <v>5225</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
@@ -11087,7 +11087,7 @@
         <v>1900</v>
       </c>
       <c r="AO45" t="n">
-        <v>2470</v>
+        <v>2375</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
@@ -13493,10 +13493,10 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>840</v>
+        <v>805</v>
       </c>
       <c r="J56" t="n">
-        <v>1848</v>
+        <v>1771</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -13583,7 +13583,7 @@
         <v>700</v>
       </c>
       <c r="AO56" t="n">
-        <v>840</v>
+        <v>805</v>
       </c>
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr"/>
@@ -13635,7 +13635,7 @@
         </is>
       </c>
       <c r="DA56" t="n">
-        <v>840</v>
+        <v>805</v>
       </c>
       <c r="DD56" t="n">
         <v>8</v>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="EN56" t="inlineStr">
         <is>
-          <t>{"id":"targeting_station","class":"Defense","static":true,"armour":1,"hp":840,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.4,"length":8,"width":6.5,"cp":0,"vision":110,"weapon":"none","deathExplosion":{"damage":80,"radius":6,"delay":0.3,"tier":"Huge"}}</t>
+          <t>{"id":"targeting_station","class":"Defense","static":true,"armour":1,"hp":805,"speed":0,"turnRate":1,"turretTurnRate":1,"radius":3.4,"length":8,"width":6.5,"cp":0,"vision":110,"weapon":"none","deathExplosion":{"damage":80,"radius":6,"delay":0.3,"tier":"Huge"}}</t>
         </is>
       </c>
     </row>
@@ -19632,21 +19632,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gun_105_wheeled</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>369</v>
+        <v>121</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id gun_105_wheeled)</t>
+          <t>01_chien_dau/Vu_khi (id gun_57mm_lt)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -19654,21 +19654,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gun_105_wheeled_he</t>
+          <t>gun_105_wheeled</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>369</v>
+        <v>387.45</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id gun_105_wheeled_he)</t>
+          <t>01_chien_dau/Vu_khi (id gun_105_wheeled)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -19676,11 +19676,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gun_120_twin_he</t>
+          <t>gun_105_wheeled_he</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id gun_120_twin_he)</t>
+          <t>01_chien_dau/Vu_khi (id gun_105_wheeled_he)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -19698,7 +19698,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gun_120mm_he</t>
+          <t>gun_120_twin_he</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id gun_120mm_he)</t>
+          <t>01_chien_dau/Vu_khi (id gun_120_twin_he)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -19720,21 +19720,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gun_152</t>
+          <t>gun_120mm_he</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>457</v>
+        <v>343</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id gun_152)</t>
+          <t>01_chien_dau/Vu_khi (id gun_120mm_he)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -19742,21 +19742,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_152</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>457</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi (id ifv_30)</t>
+          <t>01_chien_dau/Vu_khi (id gun_152)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -19793,7 +19793,7 @@
         <v>314</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.5</v>
+        <v>56.9</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
@@ -19912,7 +19912,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>gun_105_wheeled</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id gun_105_wheeled)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_57mm_lt)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -19937,7 +19937,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gun_105_wheeled_he</t>
+          <t>gun_105_wheeled</t>
         </is>
       </c>
       <c r="B3" t="b">
@@ -19947,14 +19947,14 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id gun_105_wheeled_he)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_105_wheeled)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -19962,7 +19962,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gun_120_twin_he</t>
+          <t>gun_105_wheeled_he</t>
         </is>
       </c>
       <c r="B4" t="b">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id gun_120_twin_he)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_105_wheeled_he)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -19987,7 +19987,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gun_120mm_he</t>
+          <t>gun_120_twin_he</t>
         </is>
       </c>
       <c r="B5" t="b">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id gun_120mm_he)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_120_twin_he)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -20012,7 +20012,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gun_152</t>
+          <t>gun_120mm_he</t>
         </is>
       </c>
       <c r="B6" t="b">
@@ -20022,14 +20022,14 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id gun_152)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_120mm_he)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -20037,7 +20037,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_152</t>
         </is>
       </c>
       <c r="B7" t="b">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01_chien_dau/Vu_khi_suy_ra (id ifv_30)</t>
+          <t>01_chien_dau/Vu_khi_suy_ra (id gun_152)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -21349,10 +21349,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>172.8789682539683</v>
+        <v>176.8111111111111</v>
       </c>
       <c r="H5" t="n">
-        <v>11.53569659348897</v>
+        <v>10.79536830485198</v>
       </c>
       <c r="I5" t="n">
         <v>46</v>
@@ -21421,10 +21421,10 @@
         <v>109.6333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H6" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I6" t="n">
         <v>14</v>
@@ -21493,10 +21493,10 @@
         <v>93.18833333333336</v>
       </c>
       <c r="G7" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H7" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I7" t="n">
         <v>14</v>
@@ -21565,10 +21565,10 @@
         <v>129.6625</v>
       </c>
       <c r="G8" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H8" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I8" t="n">
         <v>14</v>
@@ -21883,10 +21883,10 @@
         <v>76.26666666666668</v>
       </c>
       <c r="G13" t="n">
-        <v>172.8789682539683</v>
+        <v>176.8111111111111</v>
       </c>
       <c r="H13" t="n">
-        <v>11.53569659348897</v>
+        <v>10.79536830485198</v>
       </c>
       <c r="I13" t="n">
         <v>46</v>
@@ -21955,10 +21955,10 @@
         <v>103.675</v>
       </c>
       <c r="G14" t="n">
-        <v>172.8789682539683</v>
+        <v>176.8111111111111</v>
       </c>
       <c r="H14" t="n">
-        <v>11.53569659348897</v>
+        <v>10.79536830485198</v>
       </c>
       <c r="I14" t="n">
         <v>46</v>
@@ -22027,10 +22027,10 @@
         <v>101.367088607595</v>
       </c>
       <c r="G15" t="n">
-        <v>172.8789682539683</v>
+        <v>176.8111111111111</v>
       </c>
       <c r="H15" t="n">
-        <v>11.53569659348897</v>
+        <v>10.79536830485198</v>
       </c>
       <c r="I15" t="n">
         <v>46</v>
@@ -22264,7 +22264,7 @@
         <v>200</v>
       </c>
       <c r="H19" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I19" t="n">
         <v>7</v>
@@ -22336,7 +22336,7 @@
         <v>200</v>
       </c>
       <c r="H20" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I20" t="n">
         <v>7</v>
@@ -22408,7 +22408,7 @@
         <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
@@ -22477,10 +22477,10 @@
         <v>101.7994652406417</v>
       </c>
       <c r="G22" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H22" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I22" t="n">
         <v>14</v>
@@ -22549,10 +22549,10 @@
         <v>102.6666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>183.3333333333333</v>
+        <v>183.3333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I23" t="n">
         <v>7</v>
@@ -22621,10 +22621,10 @@
         <v>89.3979536887453</v>
       </c>
       <c r="G24" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H24" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I24" t="n">
         <v>14</v>
@@ -22693,10 +22693,10 @@
         <v>78.56072644721908</v>
       </c>
       <c r="G25" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H25" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I25" t="n">
         <v>14</v>
@@ -22765,10 +22765,10 @@
         <v>148.3949186902012</v>
       </c>
       <c r="G26" t="n">
-        <v>339.2549019607844</v>
+        <v>319.8582352941177</v>
       </c>
       <c r="H26" t="n">
-        <v>10.81329019942361</v>
+        <v>10.91813319981659</v>
       </c>
       <c r="I26" t="n">
         <v>14</v>
@@ -22837,10 +22837,10 @@
         <v>56.84503057253548</v>
       </c>
       <c r="G27" t="n">
-        <v>126.6920634920635</v>
+        <v>127.5705357142857</v>
       </c>
       <c r="H27" t="n">
-        <v>10.16857873849875</v>
+        <v>9.909200409477291</v>
       </c>
       <c r="I27" t="n">
         <v>10</v>
@@ -23032,13 +23032,13 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>93.55207029388404</v>
+        <v>95.28846959037786</v>
       </c>
       <c r="G30" t="n">
         <v>200</v>
       </c>
       <c r="H30" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I30" t="n">
         <v>7</v>
@@ -23104,13 +23104,13 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>53.6724</v>
+        <v>54.6669</v>
       </c>
       <c r="G31" t="n">
         <v>200</v>
       </c>
       <c r="H31" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I31" t="n">
         <v>7</v>
@@ -23176,13 +23176,13 @@
         <v>0.7475000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>89.2276011019834</v>
+        <v>90.88452107096671</v>
       </c>
       <c r="G32" t="n">
         <v>200</v>
       </c>
       <c r="H32" t="n">
-        <v>27.07964301109967</v>
+        <v>22.0546244568591</v>
       </c>
       <c r="I32" t="n">
         <v>7</v>
@@ -23467,10 +23467,10 @@
         <v>66.43702702702703</v>
       </c>
       <c r="G36" t="n">
-        <v>126.6920634920635</v>
+        <v>127.5705357142857</v>
       </c>
       <c r="H36" t="n">
-        <v>10.16857873849875</v>
+        <v>9.909200409477291</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
@@ -23539,10 +23539,10 @@
         <v>59.5729974489796</v>
       </c>
       <c r="G37" t="n">
-        <v>126.6920634920635</v>
+        <v>127.5705357142857</v>
       </c>
       <c r="H37" t="n">
-        <v>10.16857873849875</v>
+        <v>9.909200409477291</v>
       </c>
       <c r="I37" t="n">
         <v>10</v>
@@ -23611,10 +23611,10 @@
         <v>42.90000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>126.6920634920635</v>
+        <v>127.5705357142857</v>
       </c>
       <c r="H38" t="n">
-        <v>10.16857873849875</v>
+        <v>9.909200409477291</v>
       </c>
       <c r="I38" t="n">
         <v>10</v>
@@ -23872,10 +23872,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>172.8789682539683</v>
+        <v>176.8111111111111</v>
       </c>
       <c r="H42" t="n">
-        <v>11.53569659348897</v>
+        <v>10.79536830485198</v>
       </c>
       <c r="I42" t="n">
         <v>46</v>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E2">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E3">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E4">
@@ -24570,7 +24570,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E12">
@@ -24786,7 +24786,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E16">
@@ -24843,7 +24843,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E17">
@@ -24900,7 +24900,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E18">
@@ -24957,7 +24957,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E19">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E20">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E21">
@@ -25552,7 +25552,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E30">
@@ -25609,7 +25609,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E31">
@@ -25666,7 +25666,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ifv_30</t>
+          <t>gun_57mm_lt</t>
         </is>
       </c>
       <c r="E32">
@@ -26354,10 +26354,10 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>3.029381260557367</v>
+        <v>2.747996435081602</v>
       </c>
       <c r="G2" t="n">
-        <v>1.477624011502516</v>
+        <v>1.340374540790818</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -26401,10 +26401,10 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.760611220002248</v>
+        <v>3.411305919411643</v>
       </c>
       <c r="G3" t="n">
-        <v>1.834291876347951</v>
+        <v>1.663913223050671</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -26448,10 +26448,10 @@
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>4.387379756669289</v>
+        <v>3.979856905980251</v>
       </c>
       <c r="G4" t="n">
-        <v>2.14000718907261</v>
+        <v>1.941232093559116</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -26495,10 +26495,10 @@
         <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>5.118609716114171</v>
+        <v>4.643166390310292</v>
       </c>
       <c r="G5" t="n">
-        <v>2.496675053918044</v>
+        <v>2.264770775818969</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -26542,10 +26542,10 @@
         <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>5.745378252781214</v>
+        <v>5.211717376878902</v>
       </c>
       <c r="G6" t="n">
-        <v>2.802390366642703</v>
+        <v>2.542089646327414</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -26589,10 +26589,10 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>4.178655325421075</v>
+        <v>4.107466166372197</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8152408339324227</v>
+        <v>0.7395169880225203</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -26636,10 +26636,10 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>5.223319156776344</v>
+        <v>5.134332707965247</v>
       </c>
       <c r="G8" t="n">
-        <v>1.019051042415528</v>
+        <v>0.9243962350281504</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -26683,10 +26683,10 @@
         <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>6.006817030292795</v>
+        <v>5.904482614160034</v>
       </c>
       <c r="G9" t="n">
-        <v>1.171908698777858</v>
+        <v>1.063055670282373</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -26730,10 +26730,10 @@
         <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.051480861648064</v>
+        <v>6.931349155753083</v>
       </c>
       <c r="G10" t="n">
-        <v>1.375718907260963</v>
+        <v>1.247934917288003</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -26777,10 +26777,10 @@
         <v>9</v>
       </c>
       <c r="F11" t="n">
-        <v>8.096144693003334</v>
+        <v>7.958215697346133</v>
       </c>
       <c r="G11" t="n">
-        <v>1.579529115744069</v>
+        <v>1.432814164293633</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -26824,10 +26824,10 @@
         <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -26871,10 +26871,10 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -26918,10 +26918,10 @@
         <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.999999999999999</v>
+        <v>8.000000000000002</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -27012,10 +27012,10 @@
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>7.058823529411764</v>
+        <v>7.764705882352941</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -27059,13 +27059,13 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2.938370041173779</v>
+        <v>2.71286655218138</v>
       </c>
       <c r="G17" t="n">
-        <v>1.341687994248742</v>
+        <v>1.217064974023434</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9782890007189072</v>
+        <v>0.8874203856270244</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -27106,13 +27106,13 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.938370041173779</v>
+        <v>2.71286655218138</v>
       </c>
       <c r="G18" t="n">
-        <v>2.49008195542775</v>
+        <v>2.258790078907897</v>
       </c>
       <c r="H18" t="n">
-        <v>1.182099209202013</v>
+        <v>1.072299632632655</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -27153,13 +27153,13 @@
         <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>2.938370041173779</v>
+        <v>2.71286655218138</v>
       </c>
       <c r="G19" t="n">
-        <v>3.581624730409777</v>
+        <v>3.248944634045606</v>
       </c>
       <c r="H19" t="n">
-        <v>1.467433501078361</v>
+        <v>1.331130578440536</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -27200,13 +27200,13 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>2.938370041173779</v>
+        <v>2.71286655218138</v>
       </c>
       <c r="G20" t="n">
-        <v>4.707278217109994</v>
+        <v>4.270041519031368</v>
       </c>
       <c r="H20" t="n">
-        <v>1.630481667864845</v>
+        <v>1.479033976045041</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -27247,13 +27247,13 @@
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>2.938370041173779</v>
+        <v>2.71286655218138</v>
       </c>
       <c r="G21" t="n">
-        <v>6.003485262401151</v>
+        <v>5.445850053257398</v>
       </c>
       <c r="H21" t="n">
-        <v>1.752767792954708</v>
+        <v>1.589961524248418</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -35492,18 +35492,18 @@
         <v>2</v>
       </c>
       <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (ATGM): tỷ lệ khe 0.278 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L7">
         <f>IF(ISNUMBER($H$7),AND(NOT($J$7),OR($G$7&lt;$H$7,$G$7&gt;$I$7)),FALSE)</f>
         <v/>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>TC0113</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_9m133_kornet;W_wikipedia_bai_cua_tung_ten_lua_bang_warhead;R_machine_brigade_can_bang</t>
@@ -35565,18 +35565,18 @@
         <v>2</v>
       </c>
       <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (ATGM): tỷ lệ khe 0.26 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L8">
         <f>IF(ISNUMBER($H$8),AND(NOT($J$8),OR($G$8&lt;$H$8,$G$8&gt;$I$8)),FALSE)</f>
         <v/>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>TC0114</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_9m133_kornet;W_wikipedia_bai_cua_tung_ten_lua_bang_warhead;R_machine_brigade_can_bang</t>
@@ -35638,18 +35638,18 @@
         <v>2</v>
       </c>
       <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (ATGM): tỷ lệ khe 0.278 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L9">
         <f>IF(ISNUMBER($H$9),AND(NOT($J$9),OR($G$9&lt;$H$9,$G$9&gt;$I$9)),FALSE)</f>
         <v/>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>TC0115</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_9m133_kornet;W_wikipedia_bai_cua_tung_ten_lua_bang_warhead;R_machine_brigade_can_bang</t>
@@ -35780,18 +35780,18 @@
         <v>2</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>TOO_SLOW_FOR_CLASS (tên lửa): tỷ lệ khe 6.83 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L11">
         <f>IF(ISNUMBER($H$11),AND(NOT($J$11),OR($G$11&lt;$H$11,$G$11&gt;$I$11)),FALSE)</f>
         <v/>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>TC0116</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;R_decisions;R_machine_brigade_can_bang</t>
@@ -35926,18 +35926,18 @@
         <v>2</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (pháo nòng dài (khe thật x1/0,7)): tỷ lệ khe 0.295 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L13">
         <f>IF(ISNUMBER($H$13),AND(NOT($J$13),OR($G$13&lt;$H$13,$G$13&gt;$I$13)),FALSE)</f>
         <v/>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>TC0117</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;D_us_army_m109a7_fact_file;R_machine_brigade_can_bang</t>
@@ -36210,18 +36210,18 @@
         <v>2</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (pháo nòng dài (khe thật x1/0,7)): tỷ lệ khe 0.52 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L17">
         <f>IF(ISNUMBER($H$17),AND(NOT($J$17),OR($G$17&lt;$H$17,$G$17&gt;$I$17)),FALSE)</f>
         <v/>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>TC0118</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_rheinmetall_120_mm_gun;R_machine_brigade_can_bang</t>
@@ -36283,18 +36283,18 @@
         <v>2</v>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (pháo nòng dài (khe thật x1/0,7)): tỷ lệ khe 0.384 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L18">
         <f>IF(ISNUMBER($H$18),AND(NOT($J$18),OR($G$18&lt;$H$18,$G$18&gt;$I$18)),FALSE)</f>
         <v/>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>TC0119</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_rheinmetall_120_mm_gun;R_machine_brigade_can_bang</t>
@@ -36425,18 +36425,18 @@
         <v>2</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (pháo nòng dài (khe thật x1/0,7)): tỷ lệ khe 0.37 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L20">
         <f>IF(ISNUMBER($H$20),AND(NOT($J$20),OR($G$20&lt;$H$20,$G$20&gt;$I$20)),FALSE)</f>
         <v/>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>TC0120</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;D_us_army_m109a7_fact_file;R_machine_brigade_can_bang</t>
@@ -36498,18 +36498,18 @@
         <v>2</v>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (pháo nòng dài (khe thật x1/0,7)): tỷ lệ khe 0.37 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L21">
         <f>IF(ISNUMBER($H$21),AND(NOT($J$21),OR($G$21&lt;$H$21,$G$21&gt;$I$21)),FALSE)</f>
         <v/>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>TC0121</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;D_us_army_m109a7_fact_file</t>
@@ -36920,18 +36920,18 @@
         <v>2</v>
       </c>
       <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (tên lửa): tỷ lệ khe 0.533 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L27">
         <f>IF(ISNUMBER($H$27),AND(NOT($J$27),OR($G$27&lt;$H$27,$G$27&gt;$I$27)),FALSE)</f>
         <v/>
       </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>TC0122</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_mim_104_patriot;R_machine_brigade_can_bang</t>
@@ -36993,18 +36993,18 @@
         <v>2</v>
       </c>
       <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (ATGM): tỷ lệ khe 0.06 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L28">
         <f>IF(ISNUMBER($H$28),AND(NOT($J$28),OR($G$28&lt;$H$28,$G$28&gt;$I$28)),FALSE)</f>
         <v/>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>TC0123</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_9m133_kornet;W_wikipedia_bai_cua_tung_ten_lua_bang_warhead</t>
@@ -37204,18 +37204,18 @@
         <v>2</v>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>TOO_FAST_FOR_CLASS (rốc-két (khoảng trong loạt)): tỷ lệ khe 0.1 ngoài ngưỡng [0.6;2] của bản kiểm nhịp bắn; chưa có lý do riêng trong fix_weapon_reasons.json</t>
+        </is>
+      </c>
       <c r="L31">
         <f>IF(ISNUMBER($H$31),AND(NOT($J$31),OR($G$31&lt;$H$31,$G$31&gt;$I$31)),FALSE)</f>
         <v/>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>TC0124</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>R_balance;R_full_weapon_audit;W_wikipedia_m270_mlrs;R_machine_brigade_can_bang</t>

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -4927,7 +4927,7 @@
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[158]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[175]</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">

--- a/Docs/export/current/03_can_cu.xlsx
+++ b/Docs/export/current/03_can_cu.xlsx
@@ -72,7 +72,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="28" hidden="1">'Anh_can_cu'!$A$1:$X$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="29" hidden="1">'Anh_can_cu_vien'!$A$1:$G$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'Anh_can_cu_mui_ten'!$A$1:$J$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Hang_so_can_cu'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="31" hidden="1">'Hang_so_can_cu'!$A$1:$K$133</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="EM17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[175]</t>
+          <t>Assets/MachineBrigade/Resources/Data/balance.json: vehicles[176]</t>
         </is>
       </c>
       <c r="EN17" t="inlineStr">
@@ -48553,15 +48553,15 @@
   </sheetPr>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="54" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
@@ -48726,30 +48726,30 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bases.baseSystem.lookEvery</t>
+          <t>bases.baseRules.parseFallback</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>baseSystem</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lookEvery</t>
+          <t>parseFallback</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>ban_kinh</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -48759,47 +48759,47 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BaseSystem.LookEvery</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:245)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.lookEvery</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.parseFallback</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>{"value":0.25,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseSystem.LookEvery"}</t>
+          <t>{"value":3,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:245)"}</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bases.blastWall.coneDeg</t>
+          <t>bases.baseRules.parseIntMax</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>blastWall</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>coneDeg</t>
+          <t>parseIntMax</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>gioi_han_thuc_the</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -48809,47 +48809,47 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:220)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.coneDeg</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.parseIntMax</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>{"value":50.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)"}</t>
+          <t>{"value":5,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:220)"}</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bases.blastWall.cutShare</t>
+          <t>bases.baseRules.rebuild1Cooldown</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>blastWall</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cutShare</t>
+          <t>rebuild1Cooldown</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.3</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -48859,47 +48859,47 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.cutShare</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild1Cooldown</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>{"value":0.3,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
+          <t>{"value":25.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bases.blastWall.radiusM</t>
+          <t>bases.baseRules.rebuild1Cp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>blastWall</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>radiusM</t>
+          <t>rebuild1Cp</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -48909,47 +48909,47 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.radiusM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild1Cp</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>{"value":8.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
+          <t>{"value":2,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bases.droneHunt.reachM</t>
+          <t>bases.baseRules.rebuild2Cooldown</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>droneHunt</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>reachM</t>
+          <t>rebuild2Cooldown</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -48959,47 +48959,47 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.droneHunt.reachM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild2Cooldown</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)"}</t>
+          <t>{"value":40.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bases.fireControl.damageShare</t>
+          <t>bases.baseRules.rebuild2Cp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fireControl</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>damageShare</t>
+          <t>rebuild2Cp</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.12</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -49009,47 +49009,47 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.damageShare</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild2Cp</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>{"value":0.12,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+          <t>{"value":4,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bases.fireControl.focus</t>
+          <t>bases.baseRules.rebuild3Cooldown</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fireControl</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>focus</t>
+          <t>rebuild3Cooldown</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -49059,47 +49059,47 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.focus</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild3Cooldown</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>{"value":2.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+          <t>{"value":60.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bases.fireControl.radiusM</t>
+          <t>bases.baseRules.rebuild3Cp</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fireControl</t>
+          <t>baseRules</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>radiusM</t>
+          <t>rebuild3Cp</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -49109,47 +49109,47 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+          <t>BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.radiusM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseRules.rebuild3Cp</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+          <t>{"value":7,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseRules (pack 2 pass 2, was Sim/Content/BaseRules.cs:96)"}</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bases.flareTower.everySeconds</t>
+          <t>bases.baseStrength.qualityDamageTakenFloor</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flareTower</t>
+          <t>baseStrength</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>everySeconds</t>
+          <t>qualityDamageTakenFloor</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>0.05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>sat_thuong</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -49159,47 +49159,47 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+          <t>BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:26)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.everySeconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseStrength.qualityDamageTakenFloor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+          <t>{"value":0.05,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:26)"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>bases.flareTower.radiusM</t>
+          <t>bases.baseStrength.referenceLevel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>flareTower</t>
+          <t>baseStrength</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>radiusM</t>
+          <t>referenceLevel</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>nguong</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -49209,47 +49209,47 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+          <t>BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:80)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.radiusM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseStrength.referenceLevel</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+          <t>{"value":3,"unit":"x","kind":"nguong","linh_vuc":"04","code":"BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:80)"}</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bases.flareTower.rangeM</t>
+          <t>bases.baseStrength.scoreDamageTakenFloor</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flareTower</t>
+          <t>baseStrength</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rangeM</t>
+          <t>scoreDamageTakenFloor</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>0.05</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>sat_thuong</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -49259,47 +49259,47 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+          <t>BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:70)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.rangeM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseStrength.scoreDamageTakenFloor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>{"value":40.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+          <t>{"value":0.05,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:70)"}</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bases.flareTower.seconds</t>
+          <t>bases.baseStrength.waveScaleScoreDivisor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flareTower</t>
+          <t>baseStrength</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>waveScaleScoreDivisor</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>gioi_han_thuc_the</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -49309,47 +49309,47 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+          <t>BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:105)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.seconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseStrength.waveScaleScoreDivisor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+          <t>{"value":100.0,"unit":"x","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:105)"}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>bases.gear.bulwarkShare</t>
+          <t>bases.baseStrength.waveScaleScoreFloor</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gear</t>
+          <t>baseStrength</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bulwarkShare</t>
+          <t>waveScaleScoreFloor</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>count</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>nguong</t>
+          <t>gioi_han_thuc_the</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -49359,42 +49359,42 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Gear.BulwarkShare</t>
+          <t>BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:105)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gear.bulwarkShare</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseStrength.waveScaleScoreFloor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>{"value":0.35,"unit":"share","kind":"nguong","linh_vuc":"04","code":"Gear.BulwarkShare"}</t>
+          <t>{"value":0.01,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseStrength (pack 2 pass 2, was Sim/Modes/BaseStrength.cs:105)"}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bases.hangar.alive</t>
+          <t>bases.baseSystem.establishAwayScale</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hangar</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>alive</t>
+          <t>establishAwayScale</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -49409,47 +49409,47 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:178)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.alive</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.establishAwayScale</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>{"value":2,"unit":"count","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+          <t>{"value":12.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:178)"}</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>bases.hangar.budget</t>
+          <t>bases.baseSystem.garrisonRadiusAdd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hangar</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>budget</t>
+          <t>garrisonRadiusAdd</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>ban_kinh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -49459,47 +49459,47 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:195)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.budget</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.garrisonRadiusAdd</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>{"value":0.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+          <t>{"value":5.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:195)"}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bases.hangar.everySeconds</t>
+          <t>bases.baseSystem.garrisonRadiusScale</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hangar</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>everySeconds</t>
+          <t>garrisonRadiusScale</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>ban_kinh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -49509,38 +49509,38 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:189)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.everySeconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.garrisonRadiusScale</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>{"value":60.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+          <t>{"value":0.5,"unit":"x","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:189)"}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>bases.hangar.postM</t>
+          <t>bases.baseSystem.hangarPostRadiusAdd</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hangar</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>postM</t>
+          <t>hangarPostRadiusAdd</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -49559,47 +49559,47 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.Hangars.cs:101)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.postM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.hangarPostRadiusAdd</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>{"value":20.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.Hangars.cs:101)"}</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bases.microwave.arcDeg</t>
+          <t>bases.baseSystem.lookEvery</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>microwave</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arcDeg</t>
+          <t>lookEvery</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>0.25</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -49609,47 +49609,47 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+          <t>BaseSystem.LookEvery</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.arcDeg</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.lookEvery</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>{"value":60.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+          <t>{"value":0.25,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseSystem.LookEvery"}</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>bases.microwave.cooldownSeconds</t>
+          <t>bases.baseSystem.marksShareMax</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>microwave</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cooldownSeconds</t>
+          <t>marksShareMax</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>nguong</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -49659,47 +49659,47 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:139)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.cooldownSeconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.marksShareMax</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>{"value":8.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)"}</t>
+          <t>{"value":0.5,"unit":"x","kind":"nguong","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:139)"}</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>bases.microwave.rangeM</t>
+          <t>bases.baseSystem.setUpHqHqLevelMax</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>microwave</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rangeM</t>
+          <t>setUpHqHqLevelMax</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>nguong</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -49709,38 +49709,38 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:88)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.rangeM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.setUpHqHqLevelMax</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+          <t>{"value":5,"unit":"x","kind":"nguong","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:88)"}</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>bases.paradrop.baseKeepOutM</t>
+          <t>bases.baseSystem.stepHangarsRadiusAdd</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>paradrop</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>baseKeepOutM</t>
+          <t>stepHangarsRadiusAdd</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -49759,47 +49759,47 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.Hangars.cs:62)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.baseKeepOutM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.stepHangarsRadiusAdd</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>{"value":45.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)"}</t>
+          <t>{"value":4.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.Hangars.cs:62)"}</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bases.paradrop.fallSeconds</t>
+          <t>bases.baseSystem.tryGetDropZoneScale</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>paradrop</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fallSeconds</t>
+          <t>tryGetDropZoneScale</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>ban_kinh</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -49809,38 +49809,38 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:567)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.fallSeconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.tryGetDropZoneScale</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>{"value":6.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+          <t>{"value":7.0,"unit":"x","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:567)"}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>bases.paradrop.heightM</t>
+          <t>bases.baseSystem.turnOutHqRadiusAdd</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>paradrop</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>heightM</t>
+          <t>turnOutHqRadiusAdd</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -49859,47 +49859,47 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:245)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.heightM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.turnOutHqRadiusAdd</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+          <t>{"value":6.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:245)"}</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bases.reconPass.seconds</t>
+          <t>bases.baseSystem.turnOutKScale</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reconPass</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>seconds</t>
+          <t>turnOutKScale</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>thoi_gian</t>
+          <t>gioi_han_thuc_the</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -49909,38 +49909,38 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:250)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.seconds</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.turnOutKScale</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>{"value":20.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+          <t>{"value":5.0,"unit":"x","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:250)"}</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bases.reconPass.widthM</t>
+          <t>bases.baseSystem.turnOutTryGetVehicleFalse</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reconPass</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>widthM</t>
+          <t>turnOutTryGetVehicleFalse</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -49959,47 +49959,47 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:244)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.widthM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.turnOutTryGetVehicleFalse</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+          <t>{"value":6.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.HqTypes.cs:244)"}</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bases.searchlight.dazzleShare</t>
+          <t>bases.baseSystem.watchTowerFalse</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>searchlight</t>
+          <t>baseSystem</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>dazzleShare</t>
+          <t>watchTowerFalse</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2</v>
+        <v>30</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>share</t>
+          <t>s</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>khac</t>
+          <t>thoi_gian</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -50009,47 +50009,47 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+          <t>BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:629)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.dazzleShare</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.baseSystem.watchTowerFalse</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>{"value":0.2,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+          <t>{"value":30.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"BaseSystem (pack 2 pass 2, was Sim/Modes/BaseSystem.cs:629)"}</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bases.searchlight.radiusM</t>
+          <t>bases.blastWall.coneDeg</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>searchlight</t>
+          <t>blastWall</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>radiusM</t>
+          <t>coneDeg</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>ban_kinh</t>
+          <t>khac</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -50059,29 +50059,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.radiusM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.coneDeg</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>{"value":35.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+          <t>{"value":50.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:271)"}</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bases.shelter.cutShare</t>
+          <t>bases.blastWall.cutShare</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>shelter</t>
+          <t>blastWall</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -50090,7 +50090,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -50109,29 +50109,29 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.cutShare</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.cutShare</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>{"value":0.5,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+          <t>{"value":0.3,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bases.shelter.radiusM</t>
+          <t>bases.blastWall.radiusM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>shelter</t>
+          <t>blastWall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -50140,7 +50140,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -50159,38 +50159,38 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.radiusM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.blastWall.radiusM</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+          <t>{"value":8.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:270)"}</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>bases.sightJammer.closeM</t>
+          <t>bases.droneHunt.reachM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sightJammer</t>
+          <t>droneHunt</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>closeM</t>
+          <t>reachM</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -50209,72 +50209,5022 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)</t>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.sightJammer.closeM</t>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.droneHunt.reachM</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)"}</t>
+          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:344)"}</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>bases.fireControl.damageShare</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>damageShare</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.damageShare</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>bases.fireControl.focus</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>focus</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.focus</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>{"value":2.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>bases.fireControl.radiusM</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fireControl</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fireControl.radiusM</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:282)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>bases.flareTower.everySeconds</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>everySeconds</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.everySeconds</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bases.flareTower.radiusM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>30</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.radiusM</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bases.flareTower.rangeM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>rangeM</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.rangeM</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>{"value":40.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:331)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>bases.flareTower.seconds</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>flareTower</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.flareTower.seconds</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:332)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bases.fortressDef.layeredCountMin</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fortressDef</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>layeredCountMin</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>FortressDef (pack 2 pass 2, was Sim/Content/FortressDef.cs:86)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.fortressDef.layeredCountMin</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>{"value":2,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"FortressDef (pack 2 pass 2, was Sim/Content/FortressDef.cs:86)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bases.gear.bulwarkShare</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gear</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>bulwarkShare</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>nguong</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Gear.BulwarkShare</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gear.bulwarkShare</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>{"value":0.35,"unit":"share","kind":"nguong","linh_vuc":"04","code":"Gear.BulwarkShare"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.airburstShellsTop1</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>airburstShellsTop1</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.airburstShellsTop1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>{"value":0.05,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.airburstShellsTop2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>airburstShellsTop2</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.airburstShellsTop2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>{"value":0.08,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.airburstShellsTop3</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>airburstShellsTop3</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.airburstShellsTop3</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.airburstShellsTop4</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>airburstShellsTop4</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.airburstShellsTop4</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>{"value":0.16,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.airburstShellsTop5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>airburstShellsTop5</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.airburstShellsTop5</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>{"value":0.2,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:25)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHandlingTop2N1</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ammoHandlingTop2N1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHandlingTop2N1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>{"value":0.07,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHandlingTop2N2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ammoHandlingTop2N2</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHandlingTop2N2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>{"value":0.1,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHandlingTop2N3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ammoHandlingTop2N3</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHandlingTop2N3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHandlingTop2N4</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ammoHandlingTop2N4</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHandlingTop2N4</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>{"value":0.14,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHandlingTop2N5</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ammoHandlingTop2N5</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHandlingTop2N5</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>{"value":0.16,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:45)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHoistTop1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ammoHoistTop1</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHoistTop1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>{"value":0.06,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHoistTop2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ammoHoistTop2</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHoistTop2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>{"value":0.09,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHoistTop3</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ammoHoistTop3</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHoistTop3</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHoistTop4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ammoHoistTop4</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHoistTop4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>{"value":0.15,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.ammoHoistTop5</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ammoHoistTop5</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.ammoHoistTop5</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>{"value":0.18,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:27)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.blastWallsTop1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>blastWallsTop1</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.blastWallsTop1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>{"value":0.06,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.blastWallsTop2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>blastWallsTop2</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.blastWallsTop2</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>{"value":0.09,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.blastWallsTop3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>blastWallsTop3</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.blastWallsTop3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>{"value":0.13,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.blastWallsTop4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>blastWallsTop4</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.blastWallsTop4</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>{"value":0.17,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.blastWallsTop5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>blastWallsTop5</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.blastWallsTop5</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>{"value":0.22,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:32)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.buildTowerCapsCaps</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>buildTowerCapsCaps</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:106)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.buildTowerCapsCaps</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>{"value":0.1,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:106)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.engineerBayTop2</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>engineerBayTop2</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.engineerBayTop2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>{"value":1.5,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.engineerBayTop3</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>engineerBayTop3</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.engineerBayTop3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>{"value":2.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.engineerBayTop4</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>engineerBayTop4</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.engineerBayTop4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>{"value":2.5,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.engineerBayTop5</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>engineerBayTop5</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.engineerBayTop5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>{"value":3.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:34)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.flakProximityFuzeTop1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>flakProximityFuzeTop1</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.flakProximityFuzeTop1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>{"value":0.05,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.flakProximityFuzeTop2</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>flakProximityFuzeTop2</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.flakProximityFuzeTop2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>{"value":0.08,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.flakProximityFuzeTop3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>flakProximityFuzeTop3</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.flakProximityFuzeTop3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.flakProximityFuzeTop4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>flakProximityFuzeTop4</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.flakProximityFuzeTop4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>{"value":0.16,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.flakProximityFuzeTop5</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>flakProximityFuzeTop5</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.flakProximityFuzeTop5</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>{"value":0.2,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:24)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.fortressBarrelTop1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>fortressBarrelTop1</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.fortressBarrelTop1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>{"value":0.02,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.fortressBarrelTop2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>fortressBarrelTop2</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.fortressBarrelTop2</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>{"value":0.03,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.fortressBarrelTop3</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>fortressBarrelTop3</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.fortressBarrelTop3</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>{"value":0.04,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.fortressBarrelTop4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>fortressBarrelTop4</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.fortressBarrelTop4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>{"value":0.06,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.fortressBarrelTop5</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>fortressBarrelTop5</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.fortressBarrelTop5</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>{"value":0.08,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:21)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.sabotRoundsTop1</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sabotRoundsTop1</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.sabotRoundsTop1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>{"value":0.4,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.sabotRoundsTop2</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sabotRoundsTop2</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.sabotRoundsTop2</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>{"value":0.55,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.sabotRoundsTop3</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sabotRoundsTop3</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.sabotRoundsTop3</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>{"value":0.7,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.sabotRoundsTop4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sabotRoundsTop4</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.sabotRoundsTop4</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>{"value":0.85,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:23)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.towerCounterBatteryEpic1</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>towerCounterBatteryEpic1</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:66)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.towerCounterBatteryEpic1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>{"value":4.0,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:66)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.towerCounterBatteryLegendary1</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>towerCounterBatteryLegendary1</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:66)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.towerCounterBatteryLegendary1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>{"value":6.0,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:66)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bases.gearCatalog.traverseMotorsMainScale</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>gearCatalog</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>traverseMotorsMainScale</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:41)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.gearCatalog.traverseMotorsMainScale</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>{"value":1.5,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"GearCatalog (pack 2 pass 2, was Game/Match/GearCatalog.Tower.cs:41)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>bases.hangar.alive</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>alive</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.alive</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>{"value":2,"unit":"count","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>bases.hangar.budget</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.budget</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>{"value":0.0,"unit":"x","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>bases.hangar.everySeconds</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>everySeconds</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>60</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.everySeconds</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:290)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>bases.hangar.postM</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>postM</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>20</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hangar.postM</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>{"value":20.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:291)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>bases.hardpointDef.acrossSizeValue</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hardpointDef</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>acrossSizeValue</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>5</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hardpointDef.acrossSizeValue</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>{"value":5.0,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>bases.hardpointDef.acrossSizeValue2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>hardpointDef</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>acrossSizeValue2</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hardpointDef.acrossSizeValue2</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>{"value":6.5,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>bases.hardpointDef.acrossSizeValue3</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>hardpointDef</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>acrossSizeValue3</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>9</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>gioi_han_thuc_the</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hardpointDef.acrossSizeValue3</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>{"value":9.0,"unit":"count","kind":"gioi_han_thuc_the","linh_vuc":"04","code":"BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:55)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>bases.hardpointDef.classOfMetresMax</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>hardpointDef</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>classOfMetresMax</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:58)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hardpointDef.classOfMetresMax</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>{"value":5.5,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:58)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>bases.hardpointDef.classOfMetresMax2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>hardpointDef</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>classOfMetresMax2</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:58)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hardpointDef.classOfMetresMax2</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>{"value":7.5,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"BaseSites (pack 2 pass 2, was Sim/Content/BaseSites.cs:58)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.dome1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dome1</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.dome1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>{"value":0.08,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.dome2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>dome2</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.dome2</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>{"value":0.1,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.dome3</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>dome3</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.dome3</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>{"value":0.12,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.dome4</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>dome4</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.dome4</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>{"value":0.15,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.dome5</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>dome5</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.dome5</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>{"value":0.18,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:116)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonCaps1</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>garrisonCaps1</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonCaps1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>{"value":6,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonCaps2</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>garrisonCaps2</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonCaps2</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>{"value":8,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonCaps3</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>garrisonCaps3</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonCaps3</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>{"value":10,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonCaps4</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>garrisonCaps4</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonCaps4</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>{"value":12,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonCaps5</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>garrisonCaps5</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>15</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonCaps5</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>{"value":15,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:98)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonEvery1</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>garrisonEvery1</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>60</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonEvery1</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonEvery2</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>garrisonEvery2</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>60</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonEvery2</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonEvery3</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>garrisonEvery3</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>60</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonEvery3</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonEvery4</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>garrisonEvery4</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>60</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonEvery4</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.garrisonEvery5</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>garrisonEvery5</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>60</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>tan_suat</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.garrisonEvery5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"x","kind":"tan_suat","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:67)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.parseFloatFloor2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>parseFloatFloor2</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:179)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.parseFloatFloor2</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>{"value":5.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:179)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.parseFloatFloor4</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>parseFloatFloor4</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:228)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.parseFloatFloor4</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>{"value":0.5,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:228)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.regen1</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>regen1</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.regen1</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>{"value":0.002,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.regen2</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>regen2</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.regen2</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>{"value":0.0025,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.regen3</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>regen3</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.regen3</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>{"value":0.003,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.regen4</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>regen4</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.regen4</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>{"value":0.0035,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>bases.hqTypeRules.regen5</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>hqTypeRules</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>regen5</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.hqTypeRules.regen5</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>{"value":0.004,"unit":"x","kind":"khac","linh_vuc":"04","code":"HqTypeRules (pack 2 pass 2, was Sim/Content/HqTypeRules.cs:113)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>bases.microwave.arcDeg</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>arcDeg</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>60</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.arcDeg</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"deg","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>bases.microwave.cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>8</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.cooldownSeconds</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>{"value":8.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:341)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>bases.microwave.rangeM</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>microwave</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>rangeM</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>30</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.microwave.rangeM</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:340)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>bases.paradrop.baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>45</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.baseKeepOutM</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>{"value":45.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:351)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>bases.paradrop.fallSeconds</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>fallSeconds</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.fallSeconds</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>{"value":6.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>bases.paradrop.heightM</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>paradrop</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>heightM</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>30</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.paradrop.heightM</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>{"value":30.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:350)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>bases.reconPass.seconds</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>reconPass</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>20</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>thoi_gian</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.seconds</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>{"value":20.0,"unit":"s","kind":"thoi_gian","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>bases.reconPass.widthM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>reconPass</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>widthM</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>60</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.reconPass.widthM</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>{"value":60.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:357)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>bases.searchlight.dazzleShare</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>searchlight</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>dazzleShare</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.dazzleShare</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>{"value":0.2,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>bases.searchlight.radiusM</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>searchlight</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>35</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.searchlight.radiusM</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>{"value":35.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:309)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>bases.shelter.cutShare</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>cutShare</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>khac</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.cutShare</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>{"value":0.5,"unit":"share","kind":"khac","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>bases.shelter.radiusM</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>shelter</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>radiusM</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>15</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.shelter.radiusM</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:324)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>bases.sightJammer.closeM</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>sightJammer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>closeM</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>15</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.sightJammer.closeM</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>{"value":15.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>bases.sightJammer.radiusM</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>sightJammer</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>radiusM</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D129" t="n">
         <v>35</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>ban_kinh</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.sightJammer.radiusM</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K129" t="inlineStr">
         <is>
           <t>{"value":35.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"Catalog (pack 2, was Sim/Content/Catalog.P25A.cs:319)"}</t>
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>bases.wallSegmentDef.outMinScale</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>wallSegmentDef</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>outMinScale</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>WallRules (pack 2 pass 2, was Sim/Content/WallRules.cs:185)</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.wallSegmentDef.outMinScale</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>{"value":0.5,"unit":"x","kind":"ban_kinh","linh_vuc":"04","code":"WallRules (pack 2 pass 2, was Sim/Content/WallRules.cs:185)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>bases.wallSystem.keepsAnchorsMaxRings</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>wallSystem</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>keepsAnchorsMaxRings</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>5</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:185)</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.wallSystem.keepsAnchorsMaxRings</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>{"value":5,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:185)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>bases.wallSystem.regionNearMaxRings</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>wallSystem</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>regionNearMaxRings</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>sat_thuong</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:300)</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.wallSystem.regionNearMaxRings</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>{"value":2,"unit":"x","kind":"sat_thuong","linh_vuc":"04","code":"WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:300)"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>bases.wallSystem.rubbleRouteMinAdd</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>wallSystem</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>rubbleRouteMinAdd</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>ban_kinh</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:285)</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Assets/MachineBrigade/Resources/Data/tunables.json: bases.wallSystem.rubbleRouteMinAdd</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>{"value":3.0,"unit":"m","kind":"ban_kinh","linh_vuc":"04","code":"WallSystem (pack 2 pass 2, was Sim/Modes/WallSystem.cs:285)"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K133"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
